--- a/scripts/test-motor-ia/output/test_results.xlsx
+++ b/scripts/test-motor-ia/output/test_results.xlsx
@@ -467,7 +467,7 @@
         <v>200</v>
       </c>
       <c r="E2">
-        <v>12947</v>
+        <v>11659</v>
       </c>
       <c r="F2" t="str">
         <v>OK_MIXTO</v>
@@ -505,25 +505,25 @@
         <v>200</v>
       </c>
       <c r="E3">
-        <v>18556</v>
+        <v>28714</v>
       </c>
       <c r="F3" t="str">
-        <v>OK_MIXTO</v>
+        <v>VACIO</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" t="str">
-        <v>fontaneria</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -543,7 +543,7 @@
         <v>200</v>
       </c>
       <c r="E4">
-        <v>12328</v>
+        <v>11661</v>
       </c>
       <c r="F4" t="str">
         <v>OK_MIXTO</v>
@@ -581,19 +581,19 @@
         <v>200</v>
       </c>
       <c r="E5">
-        <v>12334</v>
+        <v>12023</v>
       </c>
       <c r="F5" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" t="str">
         <v>fontaneria</v>
@@ -619,19 +619,19 @@
         <v>200</v>
       </c>
       <c r="E6">
-        <v>18556</v>
+        <v>17141</v>
       </c>
       <c r="F6" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" t="str">
         <v>fontaneria</v>
@@ -657,19 +657,19 @@
         <v>200</v>
       </c>
       <c r="E7">
-        <v>22342</v>
+        <v>23799</v>
       </c>
       <c r="F7" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J7" t="str">
         <v>fontaneria</v>
@@ -695,7 +695,7 @@
         <v>200</v>
       </c>
       <c r="E8">
-        <v>23658</v>
+        <v>25516</v>
       </c>
       <c r="F8" t="str">
         <v>VACIO</v>
@@ -733,19 +733,19 @@
         <v>200</v>
       </c>
       <c r="E9">
-        <v>18236</v>
+        <v>14066</v>
       </c>
       <c r="F9" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9">
         <v>7</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="str">
         <v>climatizacion</v>
@@ -771,16 +771,16 @@
         <v>200</v>
       </c>
       <c r="E10">
-        <v>18229</v>
+        <v>19354</v>
       </c>
       <c r="F10" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10">
         <v>3</v>
@@ -809,7 +809,7 @@
         <v>200</v>
       </c>
       <c r="E11">
-        <v>13414</v>
+        <v>15011</v>
       </c>
       <c r="F11" t="str">
         <v>OK_MIXTO</v>
@@ -818,10 +818,10 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="str">
         <v>fontaneria</v>
@@ -847,7 +847,7 @@
         <v>200</v>
       </c>
       <c r="E12">
-        <v>12801</v>
+        <v>13147</v>
       </c>
       <c r="F12" t="str">
         <v>OK_MIXTO</v>
@@ -856,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="str">
         <v>fontaneria</v>
@@ -885,16 +885,16 @@
         <v>200</v>
       </c>
       <c r="E13">
-        <v>16217</v>
+        <v>16867</v>
       </c>
       <c r="F13" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -923,19 +923,19 @@
         <v>200</v>
       </c>
       <c r="E14">
-        <v>17405</v>
+        <v>14924</v>
       </c>
       <c r="F14" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" t="str">
         <v>fontaneria</v>
@@ -961,19 +961,19 @@
         <v>200</v>
       </c>
       <c r="E15">
-        <v>12489</v>
+        <v>11529</v>
       </c>
       <c r="F15" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="str">
         <v>mantenimiento_general</v>
@@ -999,19 +999,19 @@
         <v>200</v>
       </c>
       <c r="E16">
-        <v>18426</v>
+        <v>15276</v>
       </c>
       <c r="F16" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G16">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J16" t="str">
         <v>fontaneria</v>
@@ -1037,7 +1037,7 @@
         <v>200</v>
       </c>
       <c r="E17">
-        <v>26752</v>
+        <v>24893</v>
       </c>
       <c r="F17" t="str">
         <v>OK_MIXTO</v>
@@ -1046,10 +1046,10 @@
         <v>12</v>
       </c>
       <c r="H17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J17" t="str">
         <v>climatizacion</v>
@@ -1075,19 +1075,19 @@
         <v>200</v>
       </c>
       <c r="E18">
-        <v>25404</v>
+        <v>21598</v>
       </c>
       <c r="F18" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="str">
         <v>fontaneria</v>
@@ -1113,19 +1113,19 @@
         <v>200</v>
       </c>
       <c r="E19">
-        <v>18420</v>
+        <v>13569</v>
       </c>
       <c r="F19" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G19">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J19" t="str">
         <v>fontaneria</v>
@@ -1151,16 +1151,16 @@
         <v>200</v>
       </c>
       <c r="E20">
-        <v>15114</v>
+        <v>14070</v>
       </c>
       <c r="F20" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>3</v>
@@ -1189,7 +1189,7 @@
         <v>200</v>
       </c>
       <c r="E21">
-        <v>11336</v>
+        <v>11927</v>
       </c>
       <c r="F21" t="str">
         <v>OK_MIXTO</v>
@@ -1227,16 +1227,16 @@
         <v>200</v>
       </c>
       <c r="E22">
-        <v>16543</v>
+        <v>15336</v>
       </c>
       <c r="F22" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -1265,19 +1265,19 @@
         <v>200</v>
       </c>
       <c r="E23">
-        <v>21356</v>
+        <v>15333</v>
       </c>
       <c r="F23" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J23" t="str">
         <v>electricidad</v>
@@ -1303,16 +1303,16 @@
         <v>200</v>
       </c>
       <c r="E24">
-        <v>23714</v>
+        <v>21568</v>
       </c>
       <c r="F24" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -1341,25 +1341,25 @@
         <v>200</v>
       </c>
       <c r="E25">
-        <v>20559</v>
+        <v>17156</v>
       </c>
       <c r="F25" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25" t="str">
-        <v>energia_solar</v>
+        <v>electricidad</v>
       </c>
       <c r="K25" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1379,19 +1379,19 @@
         <v>200</v>
       </c>
       <c r="E26">
-        <v>12221</v>
+        <v>11756</v>
       </c>
       <c r="F26" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J26" t="str">
         <v>electricidad</v>
@@ -1417,16 +1417,16 @@
         <v>200</v>
       </c>
       <c r="E27">
-        <v>14550</v>
+        <v>14016</v>
       </c>
       <c r="F27" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27">
         <v>3</v>
@@ -1455,7 +1455,7 @@
         <v>200</v>
       </c>
       <c r="E28">
-        <v>18293</v>
+        <v>15074</v>
       </c>
       <c r="F28" t="str">
         <v>OK_MIXTO</v>
@@ -1493,7 +1493,7 @@
         <v>200</v>
       </c>
       <c r="E29">
-        <v>21523</v>
+        <v>25369</v>
       </c>
       <c r="F29" t="str">
         <v>OK_MIXTO</v>
@@ -1531,7 +1531,7 @@
         <v>200</v>
       </c>
       <c r="E30">
-        <v>10272</v>
+        <v>11055</v>
       </c>
       <c r="F30" t="str">
         <v>OK_MIXTO</v>
@@ -1569,7 +1569,7 @@
         <v>200</v>
       </c>
       <c r="E31">
-        <v>19536</v>
+        <v>20140</v>
       </c>
       <c r="F31" t="str">
         <v>OK_MIXTO</v>
@@ -1578,10 +1578,10 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" t="str">
         <v>electricidad</v>
@@ -1607,16 +1607,16 @@
         <v>200</v>
       </c>
       <c r="E32">
-        <v>22707</v>
+        <v>18884</v>
       </c>
       <c r="F32" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>3</v>
@@ -1645,19 +1645,19 @@
         <v>200</v>
       </c>
       <c r="E33">
-        <v>14205</v>
+        <v>14288</v>
       </c>
       <c r="F33" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H33">
         <v>1</v>
       </c>
       <c r="I33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J33" t="str">
         <v>cerrajeria</v>
@@ -1683,7 +1683,7 @@
         <v>200</v>
       </c>
       <c r="E34">
-        <v>17251</v>
+        <v>16142</v>
       </c>
       <c r="F34" t="str">
         <v>OK_MIXTO</v>
@@ -1721,16 +1721,16 @@
         <v>200</v>
       </c>
       <c r="E35">
-        <v>20145</v>
+        <v>22223</v>
       </c>
       <c r="F35" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>4</v>
@@ -1759,19 +1759,19 @@
         <v>200</v>
       </c>
       <c r="E36">
-        <v>14958</v>
+        <v>18978</v>
       </c>
       <c r="F36" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J36" t="str">
         <v>electricidad</v>
@@ -1797,7 +1797,7 @@
         <v>200</v>
       </c>
       <c r="E37">
-        <v>13074</v>
+        <v>12122</v>
       </c>
       <c r="F37" t="str">
         <v>OK_MIXTO</v>
@@ -1835,19 +1835,19 @@
         <v>200</v>
       </c>
       <c r="E38">
-        <v>17021</v>
+        <v>18953</v>
       </c>
       <c r="F38" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J38" t="str">
         <v>electricidad</v>
@@ -1873,19 +1873,19 @@
         <v>200</v>
       </c>
       <c r="E39">
-        <v>16594</v>
+        <v>15463</v>
       </c>
       <c r="F39" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J39" t="str">
         <v>electricidad</v>
@@ -1911,7 +1911,7 @@
         <v>200</v>
       </c>
       <c r="E40">
-        <v>20601</v>
+        <v>13826</v>
       </c>
       <c r="F40" t="str">
         <v>OK_MIXTO</v>
@@ -1920,10 +1920,10 @@
         <v>5</v>
       </c>
       <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
         <v>2</v>
-      </c>
-      <c r="I40">
-        <v>3</v>
       </c>
       <c r="J40" t="str">
         <v>telecomunicaciones</v>
@@ -1949,7 +1949,7 @@
         <v>200</v>
       </c>
       <c r="E41">
-        <v>10755</v>
+        <v>9872</v>
       </c>
       <c r="F41" t="str">
         <v>OK_MIXTO</v>
@@ -1987,19 +1987,19 @@
         <v>200</v>
       </c>
       <c r="E42">
-        <v>20601</v>
+        <v>19563</v>
       </c>
       <c r="F42" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J42" t="str">
         <v>carpinteria</v>
@@ -2025,16 +2025,16 @@
         <v>200</v>
       </c>
       <c r="E43">
-        <v>13001</v>
+        <v>13030</v>
       </c>
       <c r="F43" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G43">
+        <v>6</v>
+      </c>
+      <c r="H43">
         <v>4</v>
-      </c>
-      <c r="H43">
-        <v>2</v>
       </c>
       <c r="I43">
         <v>2</v>
@@ -2063,7 +2063,7 @@
         <v>200</v>
       </c>
       <c r="E44">
-        <v>18395</v>
+        <v>16569</v>
       </c>
       <c r="F44" t="str">
         <v>OK_MIXTO</v>
@@ -2101,19 +2101,19 @@
         <v>200</v>
       </c>
       <c r="E45">
-        <v>12672</v>
+        <v>12555</v>
       </c>
       <c r="F45" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H45">
         <v>4</v>
       </c>
       <c r="I45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" t="str">
         <v>carpinteria</v>
@@ -2139,7 +2139,7 @@
         <v>200</v>
       </c>
       <c r="E46">
-        <v>13697</v>
+        <v>18311</v>
       </c>
       <c r="F46" t="str">
         <v>OK_MIXTO</v>
@@ -2148,10 +2148,10 @@
         <v>6</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J46" t="str">
         <v>suelos_tarimas</v>
@@ -2177,16 +2177,16 @@
         <v>200</v>
       </c>
       <c r="E47">
-        <v>19224</v>
+        <v>19027</v>
       </c>
       <c r="F47" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G47">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I47">
         <v>4</v>
@@ -2215,7 +2215,7 @@
         <v>200</v>
       </c>
       <c r="E48">
-        <v>15218</v>
+        <v>15847</v>
       </c>
       <c r="F48" t="str">
         <v>OK_MIXTO</v>
@@ -2224,10 +2224,10 @@
         <v>5</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J48" t="str">
         <v>carpinteria</v>
@@ -2253,7 +2253,7 @@
         <v>200</v>
       </c>
       <c r="E49">
-        <v>14001</v>
+        <v>13858</v>
       </c>
       <c r="F49" t="str">
         <v>OK_MIXTO</v>
@@ -2291,7 +2291,7 @@
         <v>200</v>
       </c>
       <c r="E50">
-        <v>19849</v>
+        <v>17821</v>
       </c>
       <c r="F50" t="str">
         <v>OK_MIXTO</v>
@@ -2300,10 +2300,10 @@
         <v>7</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J50" t="str">
         <v>carpinteria</v>
@@ -2329,19 +2329,19 @@
         <v>200</v>
       </c>
       <c r="E51">
-        <v>21802</v>
+        <v>19239</v>
       </c>
       <c r="F51" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G51">
         <v>7</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J51" t="str">
         <v>carpinteria</v>
@@ -2367,16 +2367,16 @@
         <v>200</v>
       </c>
       <c r="E52">
-        <v>15137</v>
+        <v>16422</v>
       </c>
       <c r="F52" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52">
         <v>3</v>
@@ -2405,16 +2405,16 @@
         <v>200</v>
       </c>
       <c r="E53">
-        <v>16058</v>
+        <v>20386</v>
       </c>
       <c r="F53" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G53">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>6</v>
@@ -2443,19 +2443,19 @@
         <v>200</v>
       </c>
       <c r="E54">
-        <v>13393</v>
+        <v>17062</v>
       </c>
       <c r="F54" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J54" t="str">
         <v>carpinteria</v>
@@ -2481,19 +2481,19 @@
         <v>200</v>
       </c>
       <c r="E55">
-        <v>14357</v>
+        <v>22926</v>
       </c>
       <c r="F55" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G55">
+        <v>10</v>
+      </c>
+      <c r="H55">
+        <v>3</v>
+      </c>
+      <c r="I55">
         <v>7</v>
-      </c>
-      <c r="H55">
-        <v>2</v>
-      </c>
-      <c r="I55">
-        <v>5</v>
       </c>
       <c r="J55" t="str">
         <v>carpinteria</v>
@@ -2519,7 +2519,7 @@
         <v>200</v>
       </c>
       <c r="E56">
-        <v>12696</v>
+        <v>15162</v>
       </c>
       <c r="F56" t="str">
         <v>OK_MIXTO</v>
@@ -2557,19 +2557,19 @@
         <v>200</v>
       </c>
       <c r="E57">
-        <v>15051</v>
+        <v>12397</v>
       </c>
       <c r="F57" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G57">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I57">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J57" t="str">
         <v>carpinteria</v>
@@ -2595,7 +2595,7 @@
         <v>200</v>
       </c>
       <c r="E58">
-        <v>15599</v>
+        <v>13244</v>
       </c>
       <c r="F58" t="str">
         <v>OK_MIXTO</v>
@@ -2604,10 +2604,10 @@
         <v>6</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J58" t="str">
         <v>carpinteria</v>
@@ -2633,19 +2633,19 @@
         <v>200</v>
       </c>
       <c r="E59">
-        <v>22831</v>
+        <v>19177</v>
       </c>
       <c r="F59" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G59">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J59" t="str">
         <v>carpinteria</v>
@@ -2671,16 +2671,16 @@
         <v>200</v>
       </c>
       <c r="E60">
-        <v>15600</v>
+        <v>13551</v>
       </c>
       <c r="F60" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G60">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I60">
         <v>2</v>
@@ -2709,19 +2709,19 @@
         <v>200</v>
       </c>
       <c r="E61">
-        <v>17172</v>
+        <v>16813</v>
       </c>
       <c r="F61" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G61">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J61" t="str">
         <v>carpinteria</v>
@@ -2747,7 +2747,7 @@
         <v>200</v>
       </c>
       <c r="E62">
-        <v>11675</v>
+        <v>10926</v>
       </c>
       <c r="F62" t="str">
         <v>OK_MIXTO</v>
@@ -2756,10 +2756,10 @@
         <v>6</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" t="str">
         <v>pintura</v>
@@ -2785,7 +2785,7 @@
         <v>200</v>
       </c>
       <c r="E63">
-        <v>14752</v>
+        <v>13317</v>
       </c>
       <c r="F63" t="str">
         <v>OK_MIXTO</v>
@@ -2794,10 +2794,10 @@
         <v>6</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="str">
         <v>pintura</v>
@@ -2823,16 +2823,16 @@
         <v>200</v>
       </c>
       <c r="E64">
-        <v>21000</v>
+        <v>18852</v>
       </c>
       <c r="F64" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G64">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>4</v>
@@ -2861,19 +2861,19 @@
         <v>200</v>
       </c>
       <c r="E65">
-        <v>17617</v>
+        <v>21880</v>
       </c>
       <c r="F65" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G65">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J65" t="str">
         <v>impermeabilizacion</v>
@@ -2899,19 +2899,19 @@
         <v>200</v>
       </c>
       <c r="E66">
-        <v>12293</v>
+        <v>15344</v>
       </c>
       <c r="F66" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H66">
         <v>2</v>
       </c>
       <c r="I66">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J66" t="str">
         <v>pintura</v>
@@ -2937,19 +2937,19 @@
         <v>200</v>
       </c>
       <c r="E67">
-        <v>12301</v>
+        <v>11082</v>
       </c>
       <c r="F67" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H67">
         <v>3</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67" t="str">
         <v>pintura</v>
@@ -2975,7 +2975,7 @@
         <v>200</v>
       </c>
       <c r="E68">
-        <v>14020</v>
+        <v>20687</v>
       </c>
       <c r="F68" t="str">
         <v>OK_MIXTO</v>
@@ -2984,10 +2984,10 @@
         <v>6</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J68" t="str">
         <v>pintura</v>
@@ -3013,7 +3013,7 @@
         <v>200</v>
       </c>
       <c r="E69">
-        <v>16229</v>
+        <v>12518</v>
       </c>
       <c r="F69" t="str">
         <v>OK_MIXTO</v>
@@ -3022,10 +3022,10 @@
         <v>6</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="str">
         <v>pintura</v>
@@ -3051,7 +3051,7 @@
         <v>200</v>
       </c>
       <c r="E70">
-        <v>13542</v>
+        <v>13826</v>
       </c>
       <c r="F70" t="str">
         <v>OK_MIXTO</v>
@@ -3060,10 +3060,10 @@
         <v>6</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J70" t="str">
         <v>pintura</v>
@@ -3089,19 +3089,19 @@
         <v>200</v>
       </c>
       <c r="E71">
-        <v>15036</v>
+        <v>15462</v>
       </c>
       <c r="F71" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G71">
         <v>6</v>
       </c>
       <c r="H71">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J71" t="str">
         <v>pintura</v>
@@ -3127,7 +3127,7 @@
         <v>200</v>
       </c>
       <c r="E72">
-        <v>12214</v>
+        <v>13048</v>
       </c>
       <c r="F72" t="str">
         <v>OK_MIXTO</v>
@@ -3165,7 +3165,7 @@
         <v>200</v>
       </c>
       <c r="E73">
-        <v>16225</v>
+        <v>16325</v>
       </c>
       <c r="F73" t="str">
         <v>OK_MIXTO</v>
@@ -3174,10 +3174,10 @@
         <v>6</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" t="str">
         <v>pintura</v>
@@ -3203,7 +3203,7 @@
         <v>200</v>
       </c>
       <c r="E74">
-        <v>16404</v>
+        <v>16531</v>
       </c>
       <c r="F74" t="str">
         <v>OK_MIXTO</v>
@@ -3212,10 +3212,10 @@
         <v>6</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="str">
         <v>pintura</v>
@@ -3241,19 +3241,19 @@
         <v>200</v>
       </c>
       <c r="E75">
-        <v>18585</v>
+        <v>16528</v>
       </c>
       <c r="F75" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G75">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J75" t="str">
         <v>albanileria</v>
@@ -3279,19 +3279,19 @@
         <v>200</v>
       </c>
       <c r="E76">
-        <v>14271</v>
+        <v>14751</v>
       </c>
       <c r="F76" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H76">
         <v>2</v>
       </c>
       <c r="I76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J76" t="str">
         <v>pintura</v>
@@ -3317,7 +3317,7 @@
         <v>200</v>
       </c>
       <c r="E77">
-        <v>11610</v>
+        <v>13785</v>
       </c>
       <c r="F77" t="str">
         <v>OK_MIXTO</v>
@@ -3355,7 +3355,7 @@
         <v>200</v>
       </c>
       <c r="E78">
-        <v>14269</v>
+        <v>13447</v>
       </c>
       <c r="F78" t="str">
         <v>OK_MIXTO</v>
@@ -3364,10 +3364,10 @@
         <v>5</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J78" t="str">
         <v>fachadas</v>
@@ -3393,19 +3393,19 @@
         <v>200</v>
       </c>
       <c r="E79">
-        <v>13624</v>
+        <v>14957</v>
       </c>
       <c r="F79" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H79">
         <v>2</v>
       </c>
       <c r="I79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J79" t="str">
         <v>pintura</v>
@@ -3431,19 +3431,19 @@
         <v>200</v>
       </c>
       <c r="E80">
-        <v>15341</v>
+        <v>12762</v>
       </c>
       <c r="F80" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G80">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H80">
         <v>3</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80" t="str">
         <v>albanileria</v>
@@ -3469,7 +3469,7 @@
         <v>200</v>
       </c>
       <c r="E81">
-        <v>14971</v>
+        <v>10609</v>
       </c>
       <c r="F81" t="str">
         <v>OK_MIXTO</v>
@@ -3478,10 +3478,10 @@
         <v>5</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J81" t="str">
         <v>pintura</v>
@@ -3507,19 +3507,19 @@
         <v>200</v>
       </c>
       <c r="E82">
-        <v>20769</v>
+        <v>16137</v>
       </c>
       <c r="F82" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G82">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="str">
         <v>albanileria</v>
@@ -3545,19 +3545,19 @@
         <v>200</v>
       </c>
       <c r="E83">
-        <v>16914</v>
+        <v>14192</v>
       </c>
       <c r="F83" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H83">
         <v>3</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J83" t="str">
         <v>albanileria</v>
@@ -3583,19 +3583,19 @@
         <v>200</v>
       </c>
       <c r="E84">
-        <v>18418</v>
+        <v>13576</v>
       </c>
       <c r="F84" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G84">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H84">
         <v>3</v>
       </c>
       <c r="I84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J84" t="str">
         <v>fachadas</v>
@@ -3621,19 +3621,19 @@
         <v>200</v>
       </c>
       <c r="E85">
-        <v>14973</v>
+        <v>19315</v>
       </c>
       <c r="F85" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H85">
         <v>4</v>
       </c>
       <c r="I85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J85" t="str">
         <v>albanileria</v>
@@ -3659,19 +3659,19 @@
         <v>200</v>
       </c>
       <c r="E86">
-        <v>17545</v>
+        <v>24057</v>
       </c>
       <c r="F86" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G86">
+        <v>12</v>
+      </c>
+      <c r="H86">
+        <v>4</v>
+      </c>
+      <c r="I86">
         <v>8</v>
-      </c>
-      <c r="H86">
-        <v>1</v>
-      </c>
-      <c r="I86">
-        <v>7</v>
       </c>
       <c r="J86" t="str">
         <v>suelos_alicatados</v>
@@ -3697,7 +3697,7 @@
         <v>200</v>
       </c>
       <c r="E87">
-        <v>20447</v>
+        <v>20472</v>
       </c>
       <c r="F87" t="str">
         <v>OK_MIXTO</v>
@@ -3735,7 +3735,7 @@
         <v>200</v>
       </c>
       <c r="E88">
-        <v>17033</v>
+        <v>14940</v>
       </c>
       <c r="F88" t="str">
         <v>OK_MIXTO</v>
@@ -3773,7 +3773,7 @@
         <v>200</v>
       </c>
       <c r="E89">
-        <v>13038</v>
+        <v>13204</v>
       </c>
       <c r="F89" t="str">
         <v>OK_MIXTO</v>
@@ -3811,19 +3811,19 @@
         <v>200</v>
       </c>
       <c r="E90">
-        <v>20397</v>
+        <v>21714</v>
       </c>
       <c r="F90" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H90">
         <v>0</v>
       </c>
       <c r="I90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J90" t="str">
         <v>albanileria</v>
@@ -3849,7 +3849,7 @@
         <v>200</v>
       </c>
       <c r="E91">
-        <v>16070</v>
+        <v>14943</v>
       </c>
       <c r="F91" t="str">
         <v>OK_MIXTO</v>
@@ -3887,16 +3887,16 @@
         <v>200</v>
       </c>
       <c r="E92">
-        <v>15180</v>
+        <v>19869</v>
       </c>
       <c r="F92" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G92">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I92">
         <v>8</v>
@@ -3925,7 +3925,7 @@
         <v>200</v>
       </c>
       <c r="E93">
-        <v>13236</v>
+        <v>17927</v>
       </c>
       <c r="F93" t="str">
         <v>OK_MIXTO</v>
@@ -3963,19 +3963,19 @@
         <v>200</v>
       </c>
       <c r="E94">
-        <v>41285</v>
+        <v>38859</v>
       </c>
       <c r="F94" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G94">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H94">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I94">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J94" t="str">
         <v>albanileria</v>
@@ -4001,7 +4001,7 @@
         <v>200</v>
       </c>
       <c r="E95">
-        <v>17940</v>
+        <v>17283</v>
       </c>
       <c r="F95" t="str">
         <v>OK_MIXTO</v>
@@ -4010,10 +4010,10 @@
         <v>6</v>
       </c>
       <c r="H95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J95" t="str">
         <v>impermeabilizacion</v>
@@ -4039,19 +4039,19 @@
         <v>200</v>
       </c>
       <c r="E96">
-        <v>24900</v>
+        <v>18639</v>
       </c>
       <c r="F96" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G96">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H96">
+        <v>3</v>
+      </c>
+      <c r="I96">
         <v>5</v>
-      </c>
-      <c r="I96">
-        <v>8</v>
       </c>
       <c r="J96" t="str">
         <v>suelos_alicatados</v>
@@ -4077,16 +4077,16 @@
         <v>200</v>
       </c>
       <c r="E97">
-        <v>20190</v>
+        <v>22668</v>
       </c>
       <c r="F97" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G97">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H97">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I97">
         <v>4</v>
@@ -4115,7 +4115,7 @@
         <v>200</v>
       </c>
       <c r="E98">
-        <v>13936</v>
+        <v>13097</v>
       </c>
       <c r="F98" t="str">
         <v>OK_MIXTO</v>
@@ -4124,10 +4124,10 @@
         <v>6</v>
       </c>
       <c r="H98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J98" t="str">
         <v>albanileria</v>
@@ -4153,7 +4153,7 @@
         <v>200</v>
       </c>
       <c r="E99">
-        <v>28761</v>
+        <v>29537</v>
       </c>
       <c r="F99" t="str">
         <v>OK_MIXTO</v>
@@ -4162,10 +4162,10 @@
         <v>10</v>
       </c>
       <c r="H99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I99">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J99" t="str">
         <v>reforma_integral</v>
@@ -4191,7 +4191,7 @@
         <v>200</v>
       </c>
       <c r="E100">
-        <v>17594</v>
+        <v>16770</v>
       </c>
       <c r="F100" t="str">
         <v>OK_MIXTO</v>
@@ -4200,10 +4200,10 @@
         <v>7</v>
       </c>
       <c r="H100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J100" t="str">
         <v>suelos_alicatados</v>
@@ -4229,16 +4229,16 @@
         <v>200</v>
       </c>
       <c r="E101">
-        <v>20364</v>
+        <v>20054</v>
       </c>
       <c r="F101" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G101">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H101">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I101">
         <v>5</v>
@@ -4267,7 +4267,7 @@
         <v>200</v>
       </c>
       <c r="E102">
-        <v>18413</v>
+        <v>18479</v>
       </c>
       <c r="F102" t="str">
         <v>OK_MIXTO</v>
@@ -4305,25 +4305,25 @@
         <v>200</v>
       </c>
       <c r="E103">
-        <v>35665</v>
+        <v>36496</v>
       </c>
       <c r="F103" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G103">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H103">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I103">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J103" t="str">
-        <v>reforma_integral</v>
+        <v>climatizacion</v>
       </c>
       <c r="K103" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -4343,16 +4343,16 @@
         <v>200</v>
       </c>
       <c r="E104">
-        <v>22475</v>
+        <v>32055</v>
       </c>
       <c r="F104" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G104">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I104">
         <v>8</v>
@@ -4381,7 +4381,7 @@
         <v>200</v>
       </c>
       <c r="E105">
-        <v>15816</v>
+        <v>17314</v>
       </c>
       <c r="F105" t="str">
         <v>OK_MIXTO</v>
@@ -4390,10 +4390,10 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J105" t="str">
         <v>climatizacion</v>
@@ -4419,19 +4419,19 @@
         <v>200</v>
       </c>
       <c r="E106">
-        <v>20321</v>
+        <v>29633</v>
       </c>
       <c r="F106" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G106">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H106">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I106">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J106" t="str">
         <v>climatizacion</v>
@@ -4457,7 +4457,7 @@
         <v>200</v>
       </c>
       <c r="E107">
-        <v>25225</v>
+        <v>25810</v>
       </c>
       <c r="F107" t="str">
         <v>VACIO</v>
@@ -4495,19 +4495,19 @@
         <v>200</v>
       </c>
       <c r="E108">
-        <v>21398</v>
+        <v>19187</v>
       </c>
       <c r="F108" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G108">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H108">
         <v>2</v>
       </c>
       <c r="I108">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J108" t="str">
         <v>climatizacion</v>
@@ -4533,19 +4533,19 @@
         <v>200</v>
       </c>
       <c r="E109">
-        <v>21752</v>
+        <v>15198</v>
       </c>
       <c r="F109" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G109">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I109">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J109" t="str">
         <v>climatizacion</v>
@@ -4571,19 +4571,19 @@
         <v>200</v>
       </c>
       <c r="E110">
-        <v>13117</v>
+        <v>11777</v>
       </c>
       <c r="F110" t="str">
-        <v>PRECIO_INVALIDO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G110">
         <v>8</v>
       </c>
       <c r="H110">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="str">
         <v>climatizacion</v>
@@ -4592,7 +4592,7 @@
         <v>SI</v>
       </c>
       <c r="L110" t="str">
-        <v>Partida de catálogo con precio 0 o nulo</v>
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -4609,25 +4609,25 @@
         <v>200</v>
       </c>
       <c r="E111">
-        <v>22585</v>
+        <v>23854</v>
       </c>
       <c r="F111" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G111">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I111">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J111" t="str">
-        <v>climatizacion</v>
+        <v>electricidad</v>
       </c>
       <c r="K111" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -4647,7 +4647,7 @@
         <v>200</v>
       </c>
       <c r="E112">
-        <v>21459</v>
+        <v>25662</v>
       </c>
       <c r="F112" t="str">
         <v>OK_MIXTO</v>
@@ -4656,10 +4656,10 @@
         <v>12</v>
       </c>
       <c r="H112">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I112">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J112" t="str">
         <v>climatizacion</v>
@@ -4685,7 +4685,7 @@
         <v>200</v>
       </c>
       <c r="E113">
-        <v>12803</v>
+        <v>11776</v>
       </c>
       <c r="F113" t="str">
         <v>OK_MIXTO</v>
@@ -4694,10 +4694,10 @@
         <v>5</v>
       </c>
       <c r="H113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J113" t="str">
         <v>climatizacion</v>
@@ -4723,19 +4723,19 @@
         <v>200</v>
       </c>
       <c r="E114">
-        <v>21295</v>
+        <v>26105</v>
       </c>
       <c r="F114" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G114">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H114">
         <v>5</v>
       </c>
       <c r="I114">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J114" t="str">
         <v>climatizacion</v>
@@ -4761,19 +4761,19 @@
         <v>200</v>
       </c>
       <c r="E115">
-        <v>13967</v>
+        <v>17940</v>
       </c>
       <c r="F115" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G115">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H115">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J115" t="str">
         <v>climatizacion</v>
@@ -4799,16 +4799,16 @@
         <v>200</v>
       </c>
       <c r="E116">
-        <v>17751</v>
+        <v>15086</v>
       </c>
       <c r="F116" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G116">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I116">
         <v>5</v>
@@ -4837,19 +4837,19 @@
         <v>200</v>
       </c>
       <c r="E117">
-        <v>12521</v>
+        <v>17916</v>
       </c>
       <c r="F117" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I117">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J117" t="str">
         <v>mecanica_especializada</v>
@@ -4875,7 +4875,7 @@
         <v>200</v>
       </c>
       <c r="E118">
-        <v>14263</v>
+        <v>12611</v>
       </c>
       <c r="F118" t="str">
         <v>OK_MIXTO</v>
@@ -4884,10 +4884,10 @@
         <v>5</v>
       </c>
       <c r="H118">
+        <v>3</v>
+      </c>
+      <c r="I118">
         <v>2</v>
-      </c>
-      <c r="I118">
-        <v>3</v>
       </c>
       <c r="J118" t="str">
         <v>electricidad</v>
@@ -4913,16 +4913,16 @@
         <v>200</v>
       </c>
       <c r="E119">
-        <v>18052</v>
+        <v>20678</v>
       </c>
       <c r="F119" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G119">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I119">
         <v>4</v>
@@ -4951,19 +4951,19 @@
         <v>200</v>
       </c>
       <c r="E120">
-        <v>24477</v>
+        <v>30689</v>
       </c>
       <c r="F120" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G120">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H120">
+        <v>6</v>
+      </c>
+      <c r="I120">
         <v>7</v>
-      </c>
-      <c r="I120">
-        <v>5</v>
       </c>
       <c r="J120" t="str">
         <v>climatizacion</v>
@@ -4989,19 +4989,19 @@
         <v>200</v>
       </c>
       <c r="E121">
-        <v>30751</v>
+        <v>22657</v>
       </c>
       <c r="F121" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G121">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H121">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I121">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J121" t="str">
         <v>fontaneria</v>
@@ -5027,19 +5027,19 @@
         <v>200</v>
       </c>
       <c r="E122">
-        <v>16818</v>
+        <v>13222</v>
       </c>
       <c r="F122" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G122">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J122" t="str">
         <v>tejados_cubiertas</v>
@@ -5065,25 +5065,25 @@
         <v>200</v>
       </c>
       <c r="E123">
-        <v>24393</v>
+        <v>52862</v>
       </c>
       <c r="F123" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G123">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H123">
         <v>0</v>
       </c>
       <c r="I123">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J123" t="str">
-        <v>tejados_cubiertas</v>
+        <v>impermeabilizacion</v>
       </c>
       <c r="K123" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L123" t="str">
         <v/>
@@ -5103,19 +5103,19 @@
         <v>200</v>
       </c>
       <c r="E124">
-        <v>14678</v>
+        <v>11492</v>
       </c>
       <c r="F124" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G124">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
       <c r="I124">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J124" t="str">
         <v>fachadas</v>
@@ -5141,7 +5141,7 @@
         <v>200</v>
       </c>
       <c r="E125">
-        <v>15344</v>
+        <v>13845</v>
       </c>
       <c r="F125" t="str">
         <v>OK_MIXTO</v>
@@ -5179,19 +5179,19 @@
         <v>200</v>
       </c>
       <c r="E126">
-        <v>19364</v>
+        <v>15502</v>
       </c>
       <c r="F126" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G126">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H126">
+        <v>3</v>
+      </c>
+      <c r="I126">
         <v>4</v>
-      </c>
-      <c r="I126">
-        <v>6</v>
       </c>
       <c r="J126" t="str">
         <v>impermeabilizacion</v>
@@ -5217,16 +5217,16 @@
         <v>200</v>
       </c>
       <c r="E127">
-        <v>17392</v>
+        <v>24497</v>
       </c>
       <c r="F127" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G127">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H127">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I127">
         <v>4</v>
@@ -5255,19 +5255,19 @@
         <v>200</v>
       </c>
       <c r="E128">
-        <v>15629</v>
+        <v>17532</v>
       </c>
       <c r="F128" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G128">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H128">
         <v>2</v>
       </c>
       <c r="I128">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J128" t="str">
         <v>tejados_cubiertas</v>
@@ -5293,25 +5293,25 @@
         <v>200</v>
       </c>
       <c r="E129">
-        <v>17676</v>
+        <v>23371</v>
       </c>
       <c r="F129" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G129">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H129">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I129">
         <v>4</v>
       </c>
       <c r="J129" t="str">
-        <v>cristaleria</v>
+        <v>tejados_cubiertas</v>
       </c>
       <c r="K129" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L129" t="str">
         <v/>
@@ -5331,7 +5331,7 @@
         <v>200</v>
       </c>
       <c r="E130">
-        <v>16855</v>
+        <v>21115</v>
       </c>
       <c r="F130" t="str">
         <v>OK_MIXTO</v>
@@ -5369,19 +5369,19 @@
         <v>200</v>
       </c>
       <c r="E131">
-        <v>16854</v>
+        <v>17102</v>
       </c>
       <c r="F131" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G131">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H131">
         <v>3</v>
       </c>
       <c r="I131">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J131" t="str">
         <v>tejados_cubiertas</v>
@@ -5407,16 +5407,16 @@
         <v>200</v>
       </c>
       <c r="E132">
-        <v>18802</v>
+        <v>19737</v>
       </c>
       <c r="F132" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G132">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H132">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I132">
         <v>3</v>
@@ -5445,7 +5445,7 @@
         <v>200</v>
       </c>
       <c r="E133">
-        <v>23101</v>
+        <v>24366</v>
       </c>
       <c r="F133" t="str">
         <v>OK_MIXTO</v>
@@ -5483,19 +5483,19 @@
         <v>200</v>
       </c>
       <c r="E134">
-        <v>19750</v>
+        <v>12428</v>
       </c>
       <c r="F134" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G134">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H134">
         <v>2</v>
       </c>
       <c r="I134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J134" t="str">
         <v>impermeabilizacion</v>
@@ -5521,19 +5521,19 @@
         <v>200</v>
       </c>
       <c r="E135">
-        <v>13708</v>
+        <v>19653</v>
       </c>
       <c r="F135" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G135">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H135">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J135" t="str">
         <v>impermeabilizacion</v>
@@ -5559,7 +5559,7 @@
         <v>200</v>
       </c>
       <c r="E136">
-        <v>20175</v>
+        <v>20370</v>
       </c>
       <c r="F136" t="str">
         <v>OK_MIXTO</v>
@@ -5597,19 +5597,19 @@
         <v>200</v>
       </c>
       <c r="E137">
-        <v>34694</v>
+        <v>32690</v>
       </c>
       <c r="F137" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G137">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H137">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I137">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J137" t="str">
         <v>tejados_cubiertas</v>
@@ -5635,7 +5635,7 @@
         <v>200</v>
       </c>
       <c r="E138">
-        <v>16730</v>
+        <v>13754</v>
       </c>
       <c r="F138" t="str">
         <v>OK_MIXTO</v>
@@ -5673,19 +5673,19 @@
         <v>200</v>
       </c>
       <c r="E139">
-        <v>16159</v>
+        <v>17194</v>
       </c>
       <c r="F139" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G139">
         <v>4</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J139" t="str">
         <v>tejados_cubiertas</v>
@@ -5711,25 +5711,25 @@
         <v>200</v>
       </c>
       <c r="E140">
-        <v>23167</v>
+        <v>17278</v>
       </c>
       <c r="F140" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G140">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H140">
         <v>3</v>
       </c>
       <c r="I140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J140" t="str">
-        <v>cristaleria</v>
+        <v>tejados_cubiertas</v>
       </c>
       <c r="K140" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L140" t="str">
         <v/>
@@ -5749,7 +5749,7 @@
         <v>200</v>
       </c>
       <c r="E141">
-        <v>15859</v>
+        <v>15736</v>
       </c>
       <c r="F141" t="str">
         <v>OK_MIXTO</v>
@@ -5787,19 +5787,19 @@
         <v>200</v>
       </c>
       <c r="E142">
-        <v>20565</v>
+        <v>18818</v>
       </c>
       <c r="F142" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G142">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H142">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I142">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J142" t="str">
         <v>pladur_escayola</v>
@@ -5825,19 +5825,19 @@
         <v>200</v>
       </c>
       <c r="E143">
-        <v>18108</v>
+        <v>24037</v>
       </c>
       <c r="F143" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G143">
+        <v>11</v>
+      </c>
+      <c r="H143">
+        <v>3</v>
+      </c>
+      <c r="I143">
         <v>8</v>
-      </c>
-      <c r="H143">
-        <v>2</v>
-      </c>
-      <c r="I143">
-        <v>6</v>
       </c>
       <c r="J143" t="str">
         <v>pladur_escayola</v>
@@ -5863,16 +5863,16 @@
         <v>200</v>
       </c>
       <c r="E144">
-        <v>16325</v>
+        <v>23628</v>
       </c>
       <c r="F144" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G144">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I144">
         <v>6</v>
@@ -5901,19 +5901,19 @@
         <v>200</v>
       </c>
       <c r="E145">
-        <v>20347</v>
+        <v>22295</v>
       </c>
       <c r="F145" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G145">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H145">
         <v>4</v>
       </c>
       <c r="I145">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J145" t="str">
         <v>pladur_escayola</v>
@@ -5939,7 +5939,7 @@
         <v>200</v>
       </c>
       <c r="E146">
-        <v>11068</v>
+        <v>10741</v>
       </c>
       <c r="F146" t="str">
         <v>OK_MIXTO</v>
@@ -5977,19 +5977,19 @@
         <v>200</v>
       </c>
       <c r="E147">
-        <v>18053</v>
+        <v>17129</v>
       </c>
       <c r="F147" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G147">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H147">
         <v>5</v>
       </c>
       <c r="I147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J147" t="str">
         <v>pladur_escayola</v>
@@ -6015,19 +6015,19 @@
         <v>200</v>
       </c>
       <c r="E148">
-        <v>22171</v>
+        <v>23846</v>
       </c>
       <c r="F148" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G148">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H148">
         <v>3</v>
       </c>
       <c r="I148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J148" t="str">
         <v>pladur_escayola</v>
@@ -6053,7 +6053,7 @@
         <v>200</v>
       </c>
       <c r="E149">
-        <v>13164</v>
+        <v>19442</v>
       </c>
       <c r="F149" t="str">
         <v>OK_MIXTO</v>
@@ -6091,7 +6091,7 @@
         <v>200</v>
       </c>
       <c r="E150">
-        <v>19235</v>
+        <v>15790</v>
       </c>
       <c r="F150" t="str">
         <v>OK_MIXTO</v>
@@ -6129,19 +6129,19 @@
         <v>200</v>
       </c>
       <c r="E151">
-        <v>21551</v>
+        <v>18722</v>
       </c>
       <c r="F151" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G151">
         <v>7</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I151">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J151" t="str">
         <v>pladur_escayola</v>
@@ -6167,25 +6167,25 @@
         <v>200</v>
       </c>
       <c r="E152">
-        <v>19564</v>
+        <v>23578</v>
       </c>
       <c r="F152" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G152">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H152">
         <v>3</v>
       </c>
       <c r="I152">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J152" t="str">
-        <v>pladur_escayola</v>
+        <v>albanileria</v>
       </c>
       <c r="K152" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L152" t="str">
         <v/>
@@ -6205,16 +6205,16 @@
         <v>200</v>
       </c>
       <c r="E153">
-        <v>18026</v>
+        <v>21593</v>
       </c>
       <c r="F153" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G153">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H153">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I153">
         <v>5</v>
@@ -6243,7 +6243,7 @@
         <v>200</v>
       </c>
       <c r="E154">
-        <v>11473</v>
+        <v>19552</v>
       </c>
       <c r="F154" t="str">
         <v>OK_MIXTO</v>
@@ -6281,7 +6281,7 @@
         <v>200</v>
       </c>
       <c r="E155">
-        <v>18932</v>
+        <v>18928</v>
       </c>
       <c r="F155" t="str">
         <v>OK_MIXTO</v>
@@ -6319,7 +6319,7 @@
         <v>200</v>
       </c>
       <c r="E156">
-        <v>13210</v>
+        <v>13191</v>
       </c>
       <c r="F156" t="str">
         <v>OK_MIXTO</v>
@@ -6357,19 +6357,19 @@
         <v>200</v>
       </c>
       <c r="E157">
-        <v>18563</v>
+        <v>19931</v>
       </c>
       <c r="F157" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G157">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H157">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I157">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J157" t="str">
         <v>pladur_escayola</v>
@@ -6395,7 +6395,7 @@
         <v>200</v>
       </c>
       <c r="E158">
-        <v>16816</v>
+        <v>20818</v>
       </c>
       <c r="F158" t="str">
         <v>OK_MIXTO</v>
@@ -6404,10 +6404,10 @@
         <v>6</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J158" t="str">
         <v>pladur_escayola</v>
@@ -6433,7 +6433,7 @@
         <v>200</v>
       </c>
       <c r="E159">
-        <v>11069</v>
+        <v>20816</v>
       </c>
       <c r="F159" t="str">
         <v>OK_MIXTO</v>
@@ -6442,10 +6442,10 @@
         <v>5</v>
       </c>
       <c r="H159">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J159" t="str">
         <v>pladur_escayola</v>
@@ -6471,7 +6471,7 @@
         <v>200</v>
       </c>
       <c r="E160">
-        <v>16374</v>
+        <v>15752</v>
       </c>
       <c r="F160" t="str">
         <v>OK_MIXTO</v>
@@ -6509,19 +6509,19 @@
         <v>200</v>
       </c>
       <c r="E161">
-        <v>20609</v>
+        <v>19204</v>
       </c>
       <c r="F161" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G161">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H161">
         <v>1</v>
       </c>
       <c r="I161">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J161" t="str">
         <v>pladur_escayola</v>
@@ -6547,19 +6547,19 @@
         <v>200</v>
       </c>
       <c r="E162">
-        <v>16813</v>
+        <v>18081</v>
       </c>
       <c r="F162" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G162">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I162">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J162" t="str">
         <v>suelos_alicatados</v>
@@ -6585,7 +6585,7 @@
         <v>200</v>
       </c>
       <c r="E163">
-        <v>18416</v>
+        <v>15750</v>
       </c>
       <c r="F163" t="str">
         <v>OK_MIXTO</v>
@@ -6594,10 +6594,10 @@
         <v>6</v>
       </c>
       <c r="H163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I163">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J163" t="str">
         <v>suelos_tarimas</v>
@@ -6623,19 +6623,19 @@
         <v>200</v>
       </c>
       <c r="E164">
-        <v>13477</v>
+        <v>11594</v>
       </c>
       <c r="F164" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G164">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J164" t="str">
         <v>albanileria</v>
@@ -6661,16 +6661,16 @@
         <v>200</v>
       </c>
       <c r="E165">
-        <v>12048</v>
+        <v>12033</v>
       </c>
       <c r="F165" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G165">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I165">
         <v>1</v>
@@ -6699,19 +6699,19 @@
         <v>200</v>
       </c>
       <c r="E166">
-        <v>19022</v>
+        <v>20333</v>
       </c>
       <c r="F166" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G166">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H166">
         <v>2</v>
       </c>
       <c r="I166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J166" t="str">
         <v>suelos_tarimas</v>
@@ -6737,19 +6737,19 @@
         <v>200</v>
       </c>
       <c r="E167">
-        <v>17367</v>
+        <v>16046</v>
       </c>
       <c r="F167" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G167">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H167">
+        <v>2</v>
+      </c>
+      <c r="I167">
         <v>4</v>
-      </c>
-      <c r="I167">
-        <v>5</v>
       </c>
       <c r="J167" t="str">
         <v>suelos_alicatados</v>
@@ -6775,7 +6775,7 @@
         <v>200</v>
       </c>
       <c r="E168">
-        <v>21208</v>
+        <v>24088</v>
       </c>
       <c r="F168" t="str">
         <v>OK_MIXTO</v>
@@ -6813,7 +6813,7 @@
         <v>200</v>
       </c>
       <c r="E169">
-        <v>13818</v>
+        <v>13436</v>
       </c>
       <c r="F169" t="str">
         <v>OK_MIXTO</v>
@@ -6822,10 +6822,10 @@
         <v>7</v>
       </c>
       <c r="H169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J169" t="str">
         <v>suelos_alicatados</v>
@@ -6851,19 +6851,19 @@
         <v>200</v>
       </c>
       <c r="E170">
-        <v>14849</v>
+        <v>11919</v>
       </c>
       <c r="F170" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H170">
         <v>1</v>
       </c>
       <c r="I170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J170" t="str">
         <v>suelos_alicatados</v>
@@ -6889,7 +6889,7 @@
         <v>200</v>
       </c>
       <c r="E171">
-        <v>14849</v>
+        <v>22838</v>
       </c>
       <c r="F171" t="str">
         <v>OK_MIXTO</v>
@@ -6898,10 +6898,10 @@
         <v>8</v>
       </c>
       <c r="H171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I171">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J171" t="str">
         <v>electricidad</v>
@@ -6927,7 +6927,7 @@
         <v>200</v>
       </c>
       <c r="E172">
-        <v>15196</v>
+        <v>19269</v>
       </c>
       <c r="F172" t="str">
         <v>OK_MIXTO</v>
@@ -6965,19 +6965,19 @@
         <v>200</v>
       </c>
       <c r="E173">
-        <v>18859</v>
+        <v>23959</v>
       </c>
       <c r="F173" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G173">
+        <v>11</v>
+      </c>
+      <c r="H173">
+        <v>3</v>
+      </c>
+      <c r="I173">
         <v>8</v>
-      </c>
-      <c r="H173">
-        <v>1</v>
-      </c>
-      <c r="I173">
-        <v>7</v>
       </c>
       <c r="J173" t="str">
         <v>suelos_alicatados</v>
@@ -7003,22 +7003,22 @@
         <v>200</v>
       </c>
       <c r="E174">
-        <v>21240</v>
+        <v>22118</v>
       </c>
       <c r="F174" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G174">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H174">
         <v>4</v>
       </c>
       <c r="I174">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J174" t="str">
-        <v>impermeabilizacion</v>
+        <v>albanileria</v>
       </c>
       <c r="K174" t="str">
         <v>NO</v>
@@ -7041,7 +7041,7 @@
         <v>200</v>
       </c>
       <c r="E175">
-        <v>16225</v>
+        <v>14374</v>
       </c>
       <c r="F175" t="str">
         <v>OK_MIXTO</v>
@@ -7050,10 +7050,10 @@
         <v>6</v>
       </c>
       <c r="H175">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J175" t="str">
         <v>suelos_alicatados</v>
@@ -7079,7 +7079,7 @@
         <v>200</v>
       </c>
       <c r="E176">
-        <v>17816</v>
+        <v>20264</v>
       </c>
       <c r="F176" t="str">
         <v>OK_MIXTO</v>
@@ -7117,19 +7117,19 @@
         <v>200</v>
       </c>
       <c r="E177">
-        <v>22266</v>
+        <v>22560</v>
       </c>
       <c r="F177" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G177">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H177">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I177">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J177" t="str">
         <v>suelos_alicatados</v>
@@ -7155,19 +7155,19 @@
         <v>200</v>
       </c>
       <c r="E178">
-        <v>25188</v>
+        <v>25793</v>
       </c>
       <c r="F178" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G178">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H178">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I178">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J178" t="str">
         <v>suelos_alicatados</v>
@@ -7193,7 +7193,7 @@
         <v>200</v>
       </c>
       <c r="E179">
-        <v>14738</v>
+        <v>12523</v>
       </c>
       <c r="F179" t="str">
         <v>OK_MIXTO</v>
@@ -7202,10 +7202,10 @@
         <v>6</v>
       </c>
       <c r="H179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J179" t="str">
         <v>albanileria</v>
@@ -7231,16 +7231,16 @@
         <v>200</v>
       </c>
       <c r="E180">
-        <v>12548</v>
+        <v>15590</v>
       </c>
       <c r="F180" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G180">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I180">
         <v>4</v>
@@ -7269,19 +7269,19 @@
         <v>200</v>
       </c>
       <c r="E181">
-        <v>16994</v>
+        <v>23232</v>
       </c>
       <c r="F181" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G181">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H181">
         <v>4</v>
       </c>
       <c r="I181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J181" t="str">
         <v>suelos_alicatados</v>
@@ -7307,19 +7307,19 @@
         <v>200</v>
       </c>
       <c r="E182">
-        <v>9529</v>
+        <v>9936</v>
       </c>
       <c r="F182" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G182">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H182">
         <v>2</v>
       </c>
       <c r="I182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J182" t="str">
         <v>cerrajeria</v>
@@ -7345,16 +7345,16 @@
         <v>200</v>
       </c>
       <c r="E183">
-        <v>12894</v>
+        <v>14786</v>
       </c>
       <c r="F183" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H183">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I183">
         <v>2</v>
@@ -7383,19 +7383,19 @@
         <v>200</v>
       </c>
       <c r="E184">
-        <v>9522</v>
+        <v>10995</v>
       </c>
       <c r="F184" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G184">
         <v>3</v>
       </c>
       <c r="H184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I184">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J184" t="str">
         <v>cerrajeria</v>
@@ -7421,7 +7421,7 @@
         <v>200</v>
       </c>
       <c r="E185">
-        <v>13719</v>
+        <v>14169</v>
       </c>
       <c r="F185" t="str">
         <v>OK_MIXTO</v>
@@ -7430,10 +7430,10 @@
         <v>6</v>
       </c>
       <c r="H185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J185" t="str">
         <v>cerrajeria</v>
@@ -7459,19 +7459,19 @@
         <v>200</v>
       </c>
       <c r="E186">
-        <v>20674</v>
+        <v>17817</v>
       </c>
       <c r="F186" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G186">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I186">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J186" t="str">
         <v>cerrajeria</v>
@@ -7497,19 +7497,19 @@
         <v>200</v>
       </c>
       <c r="E187">
-        <v>12628</v>
+        <v>9715</v>
       </c>
       <c r="F187" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G187">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J187" t="str">
         <v>cerrajeria</v>
@@ -7535,16 +7535,16 @@
         <v>200</v>
       </c>
       <c r="E188">
-        <v>14579</v>
+        <v>10894</v>
       </c>
       <c r="F188" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G188">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I188">
         <v>4</v>
@@ -7573,19 +7573,19 @@
         <v>200</v>
       </c>
       <c r="E189">
-        <v>14577</v>
+        <v>14273</v>
       </c>
       <c r="F189" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G189">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H189">
         <v>2</v>
       </c>
       <c r="I189">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J189" t="str">
         <v>cerrajeria</v>
@@ -7611,19 +7611,19 @@
         <v>200</v>
       </c>
       <c r="E190">
-        <v>17509</v>
+        <v>17145</v>
       </c>
       <c r="F190" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G190">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H190">
         <v>5</v>
       </c>
       <c r="I190">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J190" t="str">
         <v>electricidad</v>
@@ -7649,7 +7649,7 @@
         <v>200</v>
       </c>
       <c r="E191">
-        <v>12590</v>
+        <v>11445</v>
       </c>
       <c r="F191" t="str">
         <v>OK_MIXTO</v>
@@ -7658,10 +7658,10 @@
         <v>5</v>
       </c>
       <c r="H191">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J191" t="str">
         <v>cerrajeria</v>
@@ -7687,19 +7687,19 @@
         <v>200</v>
       </c>
       <c r="E192">
-        <v>14572</v>
+        <v>16285</v>
       </c>
       <c r="F192" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G192">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H192">
         <v>2</v>
       </c>
       <c r="I192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J192" t="str">
         <v>cristaleria</v>
@@ -7725,19 +7725,19 @@
         <v>200</v>
       </c>
       <c r="E193">
-        <v>10645</v>
+        <v>8802</v>
       </c>
       <c r="F193" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G193">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J193" t="str">
         <v>cerrajeria</v>
@@ -7763,19 +7763,19 @@
         <v>200</v>
       </c>
       <c r="E194">
-        <v>10744</v>
+        <v>19671</v>
       </c>
       <c r="F194" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H194">
         <v>1</v>
       </c>
       <c r="I194">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J194" t="str">
         <v>cerrajeria</v>
@@ -7801,7 +7801,7 @@
         <v>200</v>
       </c>
       <c r="E195">
-        <v>16378</v>
+        <v>20460</v>
       </c>
       <c r="F195" t="str">
         <v>OK_MIXTO</v>
@@ -7810,10 +7810,10 @@
         <v>7</v>
       </c>
       <c r="H195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I195">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J195" t="str">
         <v>carpinteria</v>
@@ -7839,7 +7839,7 @@
         <v>200</v>
       </c>
       <c r="E196">
-        <v>21491</v>
+        <v>22997</v>
       </c>
       <c r="F196" t="str">
         <v>OK_MIXTO</v>
@@ -7877,19 +7877,19 @@
         <v>200</v>
       </c>
       <c r="E197">
-        <v>12118</v>
+        <v>12792</v>
       </c>
       <c r="F197" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G197">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H197">
         <v>1</v>
       </c>
       <c r="I197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J197" t="str">
         <v>cerrajeria</v>
@@ -7915,7 +7915,7 @@
         <v>200</v>
       </c>
       <c r="E198">
-        <v>16929</v>
+        <v>16443</v>
       </c>
       <c r="F198" t="str">
         <v>OK_MIXTO</v>
@@ -7953,7 +7953,7 @@
         <v>200</v>
       </c>
       <c r="E199">
-        <v>11565</v>
+        <v>16130</v>
       </c>
       <c r="F199" t="str">
         <v>OK_MIXTO</v>
@@ -7991,7 +7991,7 @@
         <v>200</v>
       </c>
       <c r="E200">
-        <v>29909</v>
+        <v>27132</v>
       </c>
       <c r="F200" t="str">
         <v>OK_MIXTO</v>
@@ -8029,19 +8029,19 @@
         <v>200</v>
       </c>
       <c r="E201">
-        <v>8106</v>
+        <v>8599</v>
       </c>
       <c r="F201" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G201">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H201">
         <v>2</v>
       </c>
       <c r="I201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J201" t="str">
         <v>cerrajeria</v>
@@ -8067,19 +8067,19 @@
         <v>200</v>
       </c>
       <c r="E202">
-        <v>9556</v>
+        <v>12181</v>
       </c>
       <c r="F202" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G202">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H202">
+        <v>3</v>
+      </c>
+      <c r="I202">
         <v>2</v>
-      </c>
-      <c r="I202">
-        <v>1</v>
       </c>
       <c r="J202" t="str">
         <v>jardineria</v>
@@ -8105,19 +8105,19 @@
         <v>200</v>
       </c>
       <c r="E203">
-        <v>15840</v>
+        <v>20576</v>
       </c>
       <c r="F203" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G203">
         <v>8</v>
       </c>
       <c r="H203">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I203">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J203" t="str">
         <v>jardineria</v>
@@ -8143,7 +8143,7 @@
         <v>200</v>
       </c>
       <c r="E204">
-        <v>13573</v>
+        <v>14841</v>
       </c>
       <c r="F204" t="str">
         <v>OK_MIXTO</v>
@@ -8181,19 +8181,19 @@
         <v>200</v>
       </c>
       <c r="E205">
-        <v>11474</v>
+        <v>11363</v>
       </c>
       <c r="F205" t="str">
-        <v>OK_MIXTO</v>
+        <v>OK_CATALOGO</v>
       </c>
       <c r="G205">
         <v>4</v>
       </c>
       <c r="H205">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J205" t="str">
         <v>mantenimiento_general</v>
@@ -8219,7 +8219,7 @@
         <v>200</v>
       </c>
       <c r="E206">
-        <v>13331</v>
+        <v>13321</v>
       </c>
       <c r="F206" t="str">
         <v>OK_MIXTO</v>
@@ -8228,10 +8228,10 @@
         <v>6</v>
       </c>
       <c r="H206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J206" t="str">
         <v>jardineria</v>
@@ -8257,7 +8257,7 @@
         <v>200</v>
       </c>
       <c r="E207">
-        <v>13820</v>
+        <v>14019</v>
       </c>
       <c r="F207" t="str">
         <v>OK_MIXTO</v>
@@ -8295,16 +8295,16 @@
         <v>200</v>
       </c>
       <c r="E208">
-        <v>15458</v>
+        <v>18566</v>
       </c>
       <c r="F208" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G208">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H208">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I208">
         <v>3</v>
@@ -8333,7 +8333,7 @@
         <v>200</v>
       </c>
       <c r="E209">
-        <v>13329</v>
+        <v>14544</v>
       </c>
       <c r="F209" t="str">
         <v>OK_MIXTO</v>
@@ -8371,19 +8371,19 @@
         <v>200</v>
       </c>
       <c r="E210">
-        <v>20674</v>
+        <v>24584</v>
       </c>
       <c r="F210" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G210">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H210">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I210">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J210" t="str">
         <v>jardineria</v>
@@ -8409,19 +8409,19 @@
         <v>200</v>
       </c>
       <c r="E211">
-        <v>17300</v>
+        <v>20114</v>
       </c>
       <c r="F211" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G211">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H211">
         <v>3</v>
       </c>
       <c r="I211">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J211" t="str">
         <v>jardineria</v>
@@ -8447,16 +8447,16 @@
         <v>200</v>
       </c>
       <c r="E212">
-        <v>20267</v>
+        <v>22621</v>
       </c>
       <c r="F212" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G212">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I212">
         <v>7</v>
@@ -8485,7 +8485,7 @@
         <v>200</v>
       </c>
       <c r="E213">
-        <v>17092</v>
+        <v>18214</v>
       </c>
       <c r="F213" t="str">
         <v>OK_MIXTO</v>
@@ -8494,10 +8494,10 @@
         <v>6</v>
       </c>
       <c r="H213">
+        <v>2</v>
+      </c>
+      <c r="I213">
         <v>4</v>
-      </c>
-      <c r="I213">
-        <v>2</v>
       </c>
       <c r="J213" t="str">
         <v>jardineria</v>
@@ -8523,7 +8523,7 @@
         <v>200</v>
       </c>
       <c r="E214">
-        <v>14933</v>
+        <v>15552</v>
       </c>
       <c r="F214" t="str">
         <v>OK_MIXTO</v>
@@ -8561,19 +8561,19 @@
         <v>200</v>
       </c>
       <c r="E215">
-        <v>12376</v>
+        <v>9820</v>
       </c>
       <c r="F215" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H215">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I215">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J215" t="str">
         <v>jardineria</v>
@@ -8599,7 +8599,7 @@
         <v>200</v>
       </c>
       <c r="E216">
-        <v>12377</v>
+        <v>13828</v>
       </c>
       <c r="F216" t="str">
         <v>OK_MIXTO</v>
@@ -8637,7 +8637,7 @@
         <v>200</v>
       </c>
       <c r="E217">
-        <v>16572</v>
+        <v>16982</v>
       </c>
       <c r="F217" t="str">
         <v>OK_MIXTO</v>
@@ -8675,7 +8675,7 @@
         <v>200</v>
       </c>
       <c r="E218">
-        <v>20271</v>
+        <v>20197</v>
       </c>
       <c r="F218" t="str">
         <v>OK_MIXTO</v>
@@ -8684,13 +8684,13 @@
         <v>8</v>
       </c>
       <c r="H218">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J218" t="str">
-        <v>energia_solar</v>
+        <v>electricidad</v>
       </c>
       <c r="K218" t="str">
         <v>NO</v>
@@ -8713,16 +8713,16 @@
         <v>200</v>
       </c>
       <c r="E219">
-        <v>25939</v>
+        <v>23543</v>
       </c>
       <c r="F219" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G219">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I219">
         <v>6</v>
@@ -8751,19 +8751,19 @@
         <v>200</v>
       </c>
       <c r="E220">
-        <v>16998</v>
+        <v>12383</v>
       </c>
       <c r="F220" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G220">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H220">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I220">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J220" t="str">
         <v>jardineria</v>
@@ -8789,7 +8789,7 @@
         <v>200</v>
       </c>
       <c r="E221">
-        <v>13705</v>
+        <v>13613</v>
       </c>
       <c r="F221" t="str">
         <v>OK_MIXTO</v>
@@ -8827,19 +8827,19 @@
         <v>200</v>
       </c>
       <c r="E222">
-        <v>27749</v>
+        <v>18876</v>
       </c>
       <c r="F222" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G222">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H222">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I222">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J222" t="str">
         <v>energia_solar</v>
@@ -8865,19 +8865,19 @@
         <v>200</v>
       </c>
       <c r="E223">
-        <v>28357</v>
+        <v>28865</v>
       </c>
       <c r="F223" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G223">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H223">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I223">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J223" t="str">
         <v>energia_solar</v>
@@ -8903,19 +8903,19 @@
         <v>200</v>
       </c>
       <c r="E224">
-        <v>16642</v>
+        <v>20376</v>
       </c>
       <c r="F224" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G224">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H224">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I224">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J224" t="str">
         <v>energia_solar</v>
@@ -8941,19 +8941,19 @@
         <v>200</v>
       </c>
       <c r="E225">
-        <v>24580</v>
+        <v>19098</v>
       </c>
       <c r="F225" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G225">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H225">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I225">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J225" t="str">
         <v>energia_solar</v>
@@ -8979,7 +8979,7 @@
         <v>200</v>
       </c>
       <c r="E226">
-        <v>18648</v>
+        <v>15073</v>
       </c>
       <c r="F226" t="str">
         <v>OK_MIXTO</v>
@@ -8988,10 +8988,10 @@
         <v>6</v>
       </c>
       <c r="H226">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J226" t="str">
         <v>energia_solar</v>
@@ -9017,16 +9017,16 @@
         <v>200</v>
       </c>
       <c r="E227">
-        <v>22407</v>
+        <v>29080</v>
       </c>
       <c r="F227" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G227">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H227">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I227">
         <v>8</v>
@@ -9055,16 +9055,16 @@
         <v>200</v>
       </c>
       <c r="E228">
-        <v>14033</v>
+        <v>13868</v>
       </c>
       <c r="F228" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G228">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H228">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I228">
         <v>2</v>
@@ -9093,16 +9093,16 @@
         <v>200</v>
       </c>
       <c r="E229">
-        <v>26016</v>
+        <v>28567</v>
       </c>
       <c r="F229" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G229">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H229">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I229">
         <v>9</v>
@@ -9131,25 +9131,25 @@
         <v>200</v>
       </c>
       <c r="E230">
-        <v>27232</v>
+        <v>29018</v>
       </c>
       <c r="F230" t="str">
-        <v>OK_MIXTO</v>
+        <v>VACIO</v>
       </c>
       <c r="G230">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H230">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I230">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J230" t="str">
-        <v>energia_solar</v>
+        <v/>
       </c>
       <c r="K230" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L230" t="str">
         <v/>
@@ -9169,19 +9169,19 @@
         <v>200</v>
       </c>
       <c r="E231">
-        <v>17136</v>
+        <v>27959</v>
       </c>
       <c r="F231" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G231">
         <v>8</v>
       </c>
       <c r="H231">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I231">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J231" t="str">
         <v>energia_solar</v>
@@ -9207,16 +9207,16 @@
         <v>200</v>
       </c>
       <c r="E232">
-        <v>13404</v>
+        <v>17809</v>
       </c>
       <c r="F232" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G232">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I232">
         <v>2</v>
@@ -9245,16 +9245,16 @@
         <v>200</v>
       </c>
       <c r="E233">
-        <v>15452</v>
+        <v>16887</v>
       </c>
       <c r="F233" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G233">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233">
         <v>4</v>
@@ -9283,19 +9283,19 @@
         <v>200</v>
       </c>
       <c r="E234">
-        <v>25486</v>
+        <v>25958</v>
       </c>
       <c r="F234" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G234">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H234">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I234">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J234" t="str">
         <v>energia_solar</v>
@@ -9321,19 +9321,19 @@
         <v>200</v>
       </c>
       <c r="E235">
-        <v>17133</v>
+        <v>15919</v>
       </c>
       <c r="F235" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G235">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H235">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J235" t="str">
         <v>energia_solar</v>
@@ -9359,7 +9359,7 @@
         <v>200</v>
       </c>
       <c r="E236">
-        <v>26454</v>
+        <v>27526</v>
       </c>
       <c r="F236" t="str">
         <v>VACIO</v>
@@ -9397,7 +9397,7 @@
         <v>200</v>
       </c>
       <c r="E237">
-        <v>15147</v>
+        <v>14838</v>
       </c>
       <c r="F237" t="str">
         <v>OK_MIXTO</v>
@@ -9406,10 +9406,10 @@
         <v>7</v>
       </c>
       <c r="H237">
+        <v>3</v>
+      </c>
+      <c r="I237">
         <v>4</v>
-      </c>
-      <c r="I237">
-        <v>3</v>
       </c>
       <c r="J237" t="str">
         <v>energia_solar</v>
@@ -9435,19 +9435,19 @@
         <v>200</v>
       </c>
       <c r="E238">
-        <v>20222</v>
+        <v>20791</v>
       </c>
       <c r="F238" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G238">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H238">
         <v>4</v>
       </c>
       <c r="I238">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J238" t="str">
         <v>energia_solar</v>
@@ -9473,19 +9473,19 @@
         <v>200</v>
       </c>
       <c r="E239">
-        <v>18539</v>
+        <v>16422</v>
       </c>
       <c r="F239" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G239">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H239">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I239">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J239" t="str">
         <v>energia_solar</v>
@@ -9511,19 +9511,19 @@
         <v>200</v>
       </c>
       <c r="E240">
-        <v>29179</v>
+        <v>27218</v>
       </c>
       <c r="F240" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G240">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H240">
         <v>4</v>
       </c>
       <c r="I240">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J240" t="str">
         <v>energia_solar</v>
@@ -9549,19 +9549,19 @@
         <v>200</v>
       </c>
       <c r="E241">
-        <v>19461</v>
+        <v>19808</v>
       </c>
       <c r="F241" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G241">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H241">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I241">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J241" t="str">
         <v>energia_solar</v>
@@ -9587,7 +9587,7 @@
         <v>200</v>
       </c>
       <c r="E242">
-        <v>16175</v>
+        <v>18928</v>
       </c>
       <c r="F242" t="str">
         <v>OK_MIXTO</v>
@@ -9596,10 +9596,10 @@
         <v>8</v>
       </c>
       <c r="H242">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I242">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J242" t="str">
         <v>telecomunicaciones</v>
@@ -9625,19 +9625,19 @@
         <v>200</v>
       </c>
       <c r="E243">
-        <v>16919</v>
+        <v>14914</v>
       </c>
       <c r="F243" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G243">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H243">
         <v>5</v>
       </c>
       <c r="I243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J243" t="str">
         <v>telecomunicaciones</v>
@@ -9663,16 +9663,16 @@
         <v>200</v>
       </c>
       <c r="E244">
-        <v>16916</v>
+        <v>16553</v>
       </c>
       <c r="F244" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G244">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I244">
         <v>4</v>
@@ -9701,19 +9701,19 @@
         <v>200</v>
       </c>
       <c r="E245">
-        <v>18796</v>
+        <v>16966</v>
       </c>
       <c r="F245" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G245">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H245">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I245">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J245" t="str">
         <v>telecomunicaciones</v>
@@ -9739,16 +9739,16 @@
         <v>200</v>
       </c>
       <c r="E246">
-        <v>15049</v>
+        <v>15633</v>
       </c>
       <c r="F246" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G246">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I246">
         <v>6</v>
@@ -9777,25 +9777,25 @@
         <v>200</v>
       </c>
       <c r="E247">
-        <v>12896</v>
+        <v>10963</v>
       </c>
       <c r="F247" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G247">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H247">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I247">
         <v>1</v>
       </c>
       <c r="J247" t="str">
-        <v>instalador_cctv</v>
+        <v>telecomunicaciones</v>
       </c>
       <c r="K247" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L247" t="str">
         <v/>
@@ -9815,19 +9815,19 @@
         <v>200</v>
       </c>
       <c r="E248">
-        <v>12949</v>
+        <v>18255</v>
       </c>
       <c r="F248" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G248">
+        <v>9</v>
+      </c>
+      <c r="H248">
+        <v>3</v>
+      </c>
+      <c r="I248">
         <v>6</v>
-      </c>
-      <c r="H248">
-        <v>1</v>
-      </c>
-      <c r="I248">
-        <v>5</v>
       </c>
       <c r="J248" t="str">
         <v>telecomunicaciones</v>
@@ -9853,25 +9853,25 @@
         <v>200</v>
       </c>
       <c r="E249">
-        <v>12370</v>
+        <v>12219</v>
       </c>
       <c r="F249" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G249">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H249">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I249">
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>electricidad</v>
+        <v>telecomunicaciones</v>
       </c>
       <c r="K249" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L249" t="str">
         <v/>
@@ -9891,7 +9891,7 @@
         <v>200</v>
       </c>
       <c r="E250">
-        <v>18107</v>
+        <v>14910</v>
       </c>
       <c r="F250" t="str">
         <v>OK_MIXTO</v>
@@ -9929,16 +9929,16 @@
         <v>200</v>
       </c>
       <c r="E251">
-        <v>10284</v>
+        <v>11774</v>
       </c>
       <c r="F251" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G251">
+        <v>5</v>
+      </c>
+      <c r="H251">
         <v>4</v>
-      </c>
-      <c r="H251">
-        <v>3</v>
       </c>
       <c r="I251">
         <v>1</v>
@@ -9967,7 +9967,7 @@
         <v>200</v>
       </c>
       <c r="E252">
-        <v>25237</v>
+        <v>26174</v>
       </c>
       <c r="F252" t="str">
         <v>OK_MIXTO</v>
@@ -10005,19 +10005,19 @@
         <v>200</v>
       </c>
       <c r="E253">
-        <v>16221</v>
+        <v>22686</v>
       </c>
       <c r="F253" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G253">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H253">
         <v>1</v>
       </c>
       <c r="I253">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J253" t="str">
         <v>telecomunicaciones</v>
@@ -10043,7 +10043,7 @@
         <v>200</v>
       </c>
       <c r="E254">
-        <v>22219</v>
+        <v>19855</v>
       </c>
       <c r="F254" t="str">
         <v>OK_MIXTO</v>
@@ -10081,16 +10081,16 @@
         <v>200</v>
       </c>
       <c r="E255">
-        <v>26103</v>
+        <v>25365</v>
       </c>
       <c r="F255" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G255">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H255">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I255">
         <v>5</v>
@@ -10119,7 +10119,7 @@
         <v>200</v>
       </c>
       <c r="E256">
-        <v>19143</v>
+        <v>16776</v>
       </c>
       <c r="F256" t="str">
         <v>OK_MIXTO</v>
@@ -10157,19 +10157,19 @@
         <v>200</v>
       </c>
       <c r="E257">
-        <v>25387</v>
+        <v>22713</v>
       </c>
       <c r="F257" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G257">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H257">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I257">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J257" t="str">
         <v>telecomunicaciones</v>
@@ -10195,7 +10195,7 @@
         <v>200</v>
       </c>
       <c r="E258">
-        <v>10640</v>
+        <v>11040</v>
       </c>
       <c r="F258" t="str">
         <v>OK_CATALOGO</v>
@@ -10233,7 +10233,7 @@
         <v>200</v>
       </c>
       <c r="E259">
-        <v>20578</v>
+        <v>26706</v>
       </c>
       <c r="F259" t="str">
         <v>OK_MIXTO</v>
@@ -10271,7 +10271,7 @@
         <v>200</v>
       </c>
       <c r="E260">
-        <v>17817</v>
+        <v>15174</v>
       </c>
       <c r="F260" t="str">
         <v>OK_MIXTO</v>
@@ -10309,19 +10309,19 @@
         <v>200</v>
       </c>
       <c r="E261">
-        <v>17729</v>
+        <v>23857</v>
       </c>
       <c r="F261" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G261">
         <v>10</v>
       </c>
       <c r="H261">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I261">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J261" t="str">
         <v>telecomunicaciones</v>
@@ -10347,7 +10347,7 @@
         <v>200</v>
       </c>
       <c r="E262">
-        <v>13003</v>
+        <v>11162</v>
       </c>
       <c r="F262" t="str">
         <v>OK_MIXTO</v>
@@ -10385,19 +10385,19 @@
         <v>200</v>
       </c>
       <c r="E263">
-        <v>14438</v>
+        <v>15894</v>
       </c>
       <c r="F263" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G263">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H263">
         <v>1</v>
       </c>
       <c r="I263">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J263" t="str">
         <v>cristaleria</v>
@@ -10423,7 +10423,7 @@
         <v>200</v>
       </c>
       <c r="E264">
-        <v>13518</v>
+        <v>12943</v>
       </c>
       <c r="F264" t="str">
         <v>OK_MIXTO</v>
@@ -10461,7 +10461,7 @@
         <v>200</v>
       </c>
       <c r="E265">
-        <v>17534</v>
+        <v>16944</v>
       </c>
       <c r="F265" t="str">
         <v>OK_MIXTO</v>
@@ -10470,10 +10470,10 @@
         <v>6</v>
       </c>
       <c r="H265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I265">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J265" t="str">
         <v>cristaleria</v>
@@ -10499,19 +10499,19 @@
         <v>200</v>
       </c>
       <c r="E266">
-        <v>16892</v>
+        <v>16108</v>
       </c>
       <c r="F266" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G266">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H266">
         <v>2</v>
       </c>
       <c r="I266">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J266" t="str">
         <v>cristaleria</v>
@@ -10537,19 +10537,19 @@
         <v>200</v>
       </c>
       <c r="E267">
-        <v>21801</v>
+        <v>18318</v>
       </c>
       <c r="F267" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G267">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H267">
         <v>2</v>
       </c>
       <c r="I267">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J267" t="str">
         <v>persianas</v>
@@ -10575,7 +10575,7 @@
         <v>200</v>
       </c>
       <c r="E268">
-        <v>18646</v>
+        <v>20460</v>
       </c>
       <c r="F268" t="str">
         <v>OK_MIXTO</v>
@@ -10613,19 +10613,19 @@
         <v>200</v>
       </c>
       <c r="E269">
-        <v>23163</v>
+        <v>18830</v>
       </c>
       <c r="F269" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G269">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H269">
         <v>1</v>
       </c>
       <c r="I269">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J269" t="str">
         <v>cristaleria</v>
@@ -10651,7 +10651,7 @@
         <v>200</v>
       </c>
       <c r="E270">
-        <v>11051</v>
+        <v>10572</v>
       </c>
       <c r="F270" t="str">
         <v>OK_MIXTO</v>
@@ -10689,16 +10689,16 @@
         <v>200</v>
       </c>
       <c r="E271">
-        <v>12178</v>
+        <v>15143</v>
       </c>
       <c r="F271" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I271">
         <v>3</v>
@@ -10727,7 +10727,7 @@
         <v>200</v>
       </c>
       <c r="E272">
-        <v>12571</v>
+        <v>12850</v>
       </c>
       <c r="F272" t="str">
         <v>OK_MIXTO</v>
@@ -10765,7 +10765,7 @@
         <v>200</v>
       </c>
       <c r="E273">
-        <v>21074</v>
+        <v>16127</v>
       </c>
       <c r="F273" t="str">
         <v>OK_MIXTO</v>
@@ -10774,10 +10774,10 @@
         <v>8</v>
       </c>
       <c r="H273">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I273">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J273" t="str">
         <v>cristaleria</v>
@@ -10803,16 +10803,16 @@
         <v>200</v>
       </c>
       <c r="E274">
-        <v>11752</v>
+        <v>12115</v>
       </c>
       <c r="F274" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I274">
         <v>2</v>
@@ -10841,19 +10841,19 @@
         <v>200</v>
       </c>
       <c r="E275">
-        <v>16592</v>
+        <v>15574</v>
       </c>
       <c r="F275" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G275">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H275">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I275">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J275" t="str">
         <v>cristaleria</v>
@@ -10879,19 +10879,19 @@
         <v>200</v>
       </c>
       <c r="E276">
-        <v>11440</v>
+        <v>13423</v>
       </c>
       <c r="F276" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G276">
         <v>4</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I276">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J276" t="str">
         <v>cristaleria</v>
@@ -10917,7 +10917,7 @@
         <v>200</v>
       </c>
       <c r="E277">
-        <v>14106</v>
+        <v>13424</v>
       </c>
       <c r="F277" t="str">
         <v>OK_MIXTO</v>
@@ -10955,16 +10955,16 @@
         <v>200</v>
       </c>
       <c r="E278">
-        <v>12712</v>
+        <v>18390</v>
       </c>
       <c r="F278" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G278">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I278">
         <v>3</v>
@@ -10993,19 +10993,19 @@
         <v>200</v>
       </c>
       <c r="E279">
-        <v>19026</v>
+        <v>17874</v>
       </c>
       <c r="F279" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G279">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H279">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I279">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J279" t="str">
         <v>cristaleria</v>
@@ -11031,19 +11031,19 @@
         <v>200</v>
       </c>
       <c r="E280">
-        <v>17587</v>
+        <v>17873</v>
       </c>
       <c r="F280" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G280">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H280">
         <v>3</v>
       </c>
       <c r="I280">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J280" t="str">
         <v>carpinteria</v>
@@ -11069,7 +11069,7 @@
         <v>200</v>
       </c>
       <c r="E281">
-        <v>12978</v>
+        <v>15166</v>
       </c>
       <c r="F281" t="str">
         <v>OK_MIXTO</v>
@@ -11084,7 +11084,7 @@
         <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>mecanica</v>
+        <v>mecanica_especializada</v>
       </c>
       <c r="K281" t="str">
         <v>NO</v>
@@ -11107,19 +11107,19 @@
         <v>200</v>
       </c>
       <c r="E282">
-        <v>21620</v>
+        <v>20942</v>
       </c>
       <c r="F282" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G282">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H282">
+        <v>2</v>
+      </c>
+      <c r="I282">
         <v>4</v>
-      </c>
-      <c r="I282">
-        <v>5</v>
       </c>
       <c r="J282" t="str">
         <v>impermeabilizacion</v>
@@ -11145,19 +11145,19 @@
         <v>200</v>
       </c>
       <c r="E283">
-        <v>18099</v>
+        <v>21869</v>
       </c>
       <c r="F283" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G283">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H283">
         <v>0</v>
       </c>
       <c r="I283">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J283" t="str">
         <v>impermeabilizacion</v>
@@ -11183,19 +11183,19 @@
         <v>200</v>
       </c>
       <c r="E284">
-        <v>19833</v>
+        <v>23555</v>
       </c>
       <c r="F284" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G284">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H284">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I284">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J284" t="str">
         <v>impermeabilizacion</v>
@@ -11221,7 +11221,7 @@
         <v>200</v>
       </c>
       <c r="E285">
-        <v>20345</v>
+        <v>21233</v>
       </c>
       <c r="F285" t="str">
         <v>OK_MIXTO</v>
@@ -11259,7 +11259,7 @@
         <v>200</v>
       </c>
       <c r="E286">
-        <v>16861</v>
+        <v>16177</v>
       </c>
       <c r="F286" t="str">
         <v>OK_MIXTO</v>
@@ -11297,19 +11297,19 @@
         <v>200</v>
       </c>
       <c r="E287">
-        <v>20750</v>
+        <v>25241</v>
       </c>
       <c r="F287" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G287">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J287" t="str">
         <v>impermeabilizacion</v>
@@ -11335,19 +11335,19 @@
         <v>200</v>
       </c>
       <c r="E288">
-        <v>23516</v>
+        <v>26213</v>
       </c>
       <c r="F288" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G288">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H288">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I288">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J288" t="str">
         <v>impermeabilizacion</v>
@@ -11373,19 +11373,19 @@
         <v>200</v>
       </c>
       <c r="E289">
-        <v>21466</v>
+        <v>16176</v>
       </c>
       <c r="F289" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G289">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H289">
         <v>0</v>
       </c>
       <c r="I289">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J289" t="str">
         <v>jardineria</v>
@@ -11411,19 +11411,19 @@
         <v>200</v>
       </c>
       <c r="E290">
-        <v>21196</v>
+        <v>21597</v>
       </c>
       <c r="F290" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G290">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H290">
         <v>5</v>
       </c>
       <c r="I290">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J290" t="str">
         <v>impermeabilizacion</v>
@@ -11449,7 +11449,7 @@
         <v>200</v>
       </c>
       <c r="E291">
-        <v>21537</v>
+        <v>21228</v>
       </c>
       <c r="F291" t="str">
         <v>OK_MIXTO</v>
@@ -11487,19 +11487,19 @@
         <v>200</v>
       </c>
       <c r="E292">
-        <v>25146</v>
+        <v>18770</v>
       </c>
       <c r="F292" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G292">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H292">
+        <v>3</v>
+      </c>
+      <c r="I292">
         <v>5</v>
-      </c>
-      <c r="I292">
-        <v>6</v>
       </c>
       <c r="J292" t="str">
         <v>impermeabilizacion</v>
@@ -11525,25 +11525,25 @@
         <v>200</v>
       </c>
       <c r="E293">
-        <v>19350</v>
+        <v>20114</v>
       </c>
       <c r="F293" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G293">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H293">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I293">
         <v>4</v>
       </c>
       <c r="J293" t="str">
-        <v>impermeabilizacion</v>
+        <v>tejados_cubiertas</v>
       </c>
       <c r="K293" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L293" t="str">
         <v/>
@@ -11563,7 +11563,7 @@
         <v>200</v>
       </c>
       <c r="E294">
-        <v>12077</v>
+        <v>14120</v>
       </c>
       <c r="F294" t="str">
         <v>OK_MIXTO</v>
@@ -11601,19 +11601,19 @@
         <v>200</v>
       </c>
       <c r="E295">
-        <v>22519</v>
+        <v>22786</v>
       </c>
       <c r="F295" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G295">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H295">
         <v>1</v>
       </c>
       <c r="I295">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J295" t="str">
         <v>impermeabilizacion</v>
@@ -11639,7 +11639,7 @@
         <v>200</v>
       </c>
       <c r="E296">
-        <v>16945</v>
+        <v>12048</v>
       </c>
       <c r="F296" t="str">
         <v>OK_MIXTO</v>
@@ -11654,10 +11654,10 @@
         <v>1</v>
       </c>
       <c r="J296" t="str">
-        <v>impermeabilizacion</v>
+        <v>suelos_alicatados</v>
       </c>
       <c r="K296" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L296" t="str">
         <v/>
@@ -11677,16 +11677,16 @@
         <v>200</v>
       </c>
       <c r="E297">
-        <v>23892</v>
+        <v>25927</v>
       </c>
       <c r="F297" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G297">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I297">
         <v>8</v>
@@ -11715,7 +11715,7 @@
         <v>200</v>
       </c>
       <c r="E298">
-        <v>19997</v>
+        <v>19685</v>
       </c>
       <c r="F298" t="str">
         <v>OK_MIXTO</v>
@@ -11724,10 +11724,10 @@
         <v>6</v>
       </c>
       <c r="H298">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I298">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J298" t="str">
         <v>impermeabilizacion</v>
@@ -11753,19 +11753,19 @@
         <v>200</v>
       </c>
       <c r="E299">
-        <v>29208</v>
+        <v>23694</v>
       </c>
       <c r="F299" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G299">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H299">
         <v>0</v>
       </c>
       <c r="I299">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J299" t="str">
         <v>impermeabilizacion</v>
@@ -11791,7 +11791,7 @@
         <v>200</v>
       </c>
       <c r="E300">
-        <v>19999</v>
+        <v>14271</v>
       </c>
       <c r="F300" t="str">
         <v>OK_MIXTO</v>
@@ -11800,10 +11800,10 @@
         <v>6</v>
       </c>
       <c r="H300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I300">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J300" t="str">
         <v>impermeabilizacion</v>
@@ -11829,19 +11829,19 @@
         <v>200</v>
       </c>
       <c r="E301">
-        <v>14058</v>
+        <v>19682</v>
       </c>
       <c r="F301" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G301">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H301">
         <v>3</v>
       </c>
       <c r="I301">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J301" t="str">
         <v>tejados_cubiertas</v>
@@ -11867,7 +11867,7 @@
         <v>200</v>
       </c>
       <c r="E302">
-        <v>17717</v>
+        <v>17343</v>
       </c>
       <c r="F302" t="str">
         <v>OK_MIXTO</v>
@@ -11905,19 +11905,19 @@
         <v>200</v>
       </c>
       <c r="E303">
-        <v>22157</v>
+        <v>18330</v>
       </c>
       <c r="F303" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G303">
         <v>6</v>
       </c>
       <c r="H303">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I303">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J303" t="str">
         <v>contra_incendios</v>
@@ -11943,19 +11943,19 @@
         <v>200</v>
       </c>
       <c r="E304">
-        <v>26525</v>
+        <v>23692</v>
       </c>
       <c r="F304" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G304">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H304">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I304">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J304" t="str">
         <v>contra_incendios</v>
@@ -11981,7 +11981,7 @@
         <v>200</v>
       </c>
       <c r="E305">
-        <v>14172</v>
+        <v>13005</v>
       </c>
       <c r="F305" t="str">
         <v>OK_MIXTO</v>
@@ -11990,10 +11990,10 @@
         <v>6</v>
       </c>
       <c r="H305">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I305">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J305" t="str">
         <v>contra_incendios</v>
@@ -12019,7 +12019,7 @@
         <v>200</v>
       </c>
       <c r="E306">
-        <v>28876</v>
+        <v>30103</v>
       </c>
       <c r="F306" t="str">
         <v>OK_MIXTO</v>
@@ -12057,16 +12057,16 @@
         <v>200</v>
       </c>
       <c r="E307">
-        <v>28057</v>
+        <v>27887</v>
       </c>
       <c r="F307" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G307">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H307">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I307">
         <v>7</v>
@@ -12095,16 +12095,16 @@
         <v>200</v>
       </c>
       <c r="E308">
-        <v>26307</v>
+        <v>27277</v>
       </c>
       <c r="F308" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G308">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I308">
         <v>6</v>
@@ -12133,16 +12133,16 @@
         <v>200</v>
       </c>
       <c r="E309">
-        <v>20880</v>
+        <v>16394</v>
       </c>
       <c r="F309" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G309">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H309">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I309">
         <v>7</v>
@@ -12171,19 +12171,19 @@
         <v>200</v>
       </c>
       <c r="E310">
-        <v>16207</v>
+        <v>16719</v>
       </c>
       <c r="F310" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G310">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H310">
         <v>6</v>
       </c>
       <c r="I310">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J310" t="str">
         <v>contra_incendios</v>
@@ -12209,7 +12209,7 @@
         <v>200</v>
       </c>
       <c r="E311">
-        <v>17398</v>
+        <v>21812</v>
       </c>
       <c r="F311" t="str">
         <v>OK_MIXTO</v>
@@ -12218,10 +12218,10 @@
         <v>6</v>
       </c>
       <c r="H311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I311">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J311" t="str">
         <v>cerrajeria</v>
@@ -12247,7 +12247,7 @@
         <v>200</v>
       </c>
       <c r="E312">
-        <v>12587</v>
+        <v>13207</v>
       </c>
       <c r="F312" t="str">
         <v>OK_MIXTO</v>
@@ -12285,7 +12285,7 @@
         <v>200</v>
       </c>
       <c r="E313">
-        <v>27469</v>
+        <v>28204</v>
       </c>
       <c r="F313" t="str">
         <v>OK_MIXTO</v>
@@ -12323,7 +12323,7 @@
         <v>200</v>
       </c>
       <c r="E314">
-        <v>11660</v>
+        <v>13826</v>
       </c>
       <c r="F314" t="str">
         <v>OK_MIXTO</v>
@@ -12361,19 +12361,19 @@
         <v>200</v>
       </c>
       <c r="E315">
-        <v>26270</v>
+        <v>22471</v>
       </c>
       <c r="F315" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G315">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H315">
         <v>0</v>
       </c>
       <c r="I315">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J315" t="str">
         <v>contra_incendios</v>
@@ -12399,16 +12399,16 @@
         <v>200</v>
       </c>
       <c r="E316">
-        <v>20940</v>
+        <v>18172</v>
       </c>
       <c r="F316" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G316">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H316">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I316">
         <v>4</v>
@@ -12437,16 +12437,16 @@
         <v>200</v>
       </c>
       <c r="E317">
-        <v>17768</v>
+        <v>15343</v>
       </c>
       <c r="F317" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G317">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H317">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I317">
         <v>2</v>
@@ -12475,16 +12475,16 @@
         <v>200</v>
       </c>
       <c r="E318">
-        <v>23127</v>
+        <v>29129</v>
       </c>
       <c r="F318" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G318">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H318">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I318">
         <v>5</v>
@@ -12513,19 +12513,19 @@
         <v>200</v>
       </c>
       <c r="E319">
-        <v>28106</v>
+        <v>25492</v>
       </c>
       <c r="F319" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G319">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H319">
         <v>0</v>
       </c>
       <c r="I319">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J319" t="str">
         <v>contra_incendios</v>
@@ -12551,16 +12551,16 @@
         <v>200</v>
       </c>
       <c r="E320">
-        <v>17918</v>
+        <v>18325</v>
       </c>
       <c r="F320" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G320">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H320">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I320">
         <v>5</v>
@@ -12589,7 +12589,7 @@
         <v>200</v>
       </c>
       <c r="E321">
-        <v>28453</v>
+        <v>30714</v>
       </c>
       <c r="F321" t="str">
         <v>VACIO</v>
@@ -12627,7 +12627,7 @@
         <v>200</v>
       </c>
       <c r="E322">
-        <v>20655</v>
+        <v>34707</v>
       </c>
       <c r="F322" t="str">
         <v>OK_MIXTO</v>
@@ -12636,10 +12636,10 @@
         <v>11</v>
       </c>
       <c r="H322">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I322">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J322" t="str">
         <v>fachadas</v>
@@ -12665,19 +12665,19 @@
         <v>200</v>
       </c>
       <c r="E323">
-        <v>29073</v>
+        <v>30711</v>
       </c>
       <c r="F323" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G323">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H323">
         <v>4</v>
       </c>
       <c r="I323">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J323" t="str">
         <v>fachadas</v>
@@ -12703,7 +12703,7 @@
         <v>200</v>
       </c>
       <c r="E324">
-        <v>15763</v>
+        <v>15790</v>
       </c>
       <c r="F324" t="str">
         <v>OK_MIXTO</v>
@@ -12741,7 +12741,7 @@
         <v>200</v>
       </c>
       <c r="E325">
-        <v>17919</v>
+        <v>20470</v>
       </c>
       <c r="F325" t="str">
         <v>OK_MIXTO</v>
@@ -12779,19 +12779,19 @@
         <v>200</v>
       </c>
       <c r="E326">
-        <v>25501</v>
+        <v>26205</v>
       </c>
       <c r="F326" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G326">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H326">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I326">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J326" t="str">
         <v>fachadas</v>
@@ -12817,7 +12817,7 @@
         <v>200</v>
       </c>
       <c r="E327">
-        <v>19895</v>
+        <v>22007</v>
       </c>
       <c r="F327" t="str">
         <v>OK_MIXTO</v>
@@ -12826,10 +12826,10 @@
         <v>6</v>
       </c>
       <c r="H327">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I327">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J327" t="str">
         <v>fachadas</v>
@@ -12855,19 +12855,19 @@
         <v>200</v>
       </c>
       <c r="E328">
-        <v>15874</v>
+        <v>19754</v>
       </c>
       <c r="F328" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G328">
         <v>7</v>
       </c>
       <c r="H328">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I328">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J328" t="str">
         <v>fachadas</v>
@@ -12893,7 +12893,7 @@
         <v>200</v>
       </c>
       <c r="E329">
-        <v>12186</v>
+        <v>12889</v>
       </c>
       <c r="F329" t="str">
         <v>OK_MIXTO</v>
@@ -12931,16 +12931,16 @@
         <v>200</v>
       </c>
       <c r="E330">
-        <v>19763</v>
+        <v>27540</v>
       </c>
       <c r="F330" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G330">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H330">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I330">
         <v>8</v>
@@ -12969,7 +12969,7 @@
         <v>200</v>
       </c>
       <c r="E331">
-        <v>19892</v>
+        <v>20263</v>
       </c>
       <c r="F331" t="str">
         <v>OK_MIXTO</v>
@@ -12978,10 +12978,10 @@
         <v>6</v>
       </c>
       <c r="H331">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I331">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J331" t="str">
         <v>fachadas</v>
@@ -13007,19 +13007,19 @@
         <v>200</v>
       </c>
       <c r="E332">
-        <v>23276</v>
+        <v>22979</v>
       </c>
       <c r="F332" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G332">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H332">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I332">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J332" t="str">
         <v>fachadas</v>
@@ -13045,7 +13045,7 @@
         <v>200</v>
       </c>
       <c r="E333">
-        <v>16164</v>
+        <v>14338</v>
       </c>
       <c r="F333" t="str">
         <v>OK_MIXTO</v>
@@ -13083,7 +13083,7 @@
         <v>200</v>
       </c>
       <c r="E334">
-        <v>12989</v>
+        <v>14165</v>
       </c>
       <c r="F334" t="str">
         <v>OK_MIXTO</v>
@@ -13092,10 +13092,10 @@
         <v>6</v>
       </c>
       <c r="H334">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I334">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J334" t="str">
         <v>fachadas</v>
@@ -13121,19 +13121,19 @@
         <v>200</v>
       </c>
       <c r="E335">
-        <v>17000</v>
+        <v>16688</v>
       </c>
       <c r="F335" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G335">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H335">
         <v>1</v>
       </c>
       <c r="I335">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J335" t="str">
         <v>fachadas</v>
@@ -13159,7 +13159,7 @@
         <v>200</v>
       </c>
       <c r="E336">
-        <v>17193</v>
+        <v>17442</v>
       </c>
       <c r="F336" t="str">
         <v>OK_MIXTO</v>
@@ -13168,13 +13168,13 @@
         <v>8</v>
       </c>
       <c r="H336">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I336">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J336" t="str">
-        <v>carpinteria</v>
+        <v>cristaleria</v>
       </c>
       <c r="K336" t="str">
         <v>NO</v>
@@ -13197,7 +13197,7 @@
         <v>200</v>
       </c>
       <c r="E337">
-        <v>17702</v>
+        <v>19758</v>
       </c>
       <c r="F337" t="str">
         <v>OK_MIXTO</v>
@@ -13206,10 +13206,10 @@
         <v>9</v>
       </c>
       <c r="H337">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I337">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J337" t="str">
         <v>fachadas</v>
@@ -13235,7 +13235,7 @@
         <v>200</v>
       </c>
       <c r="E338">
-        <v>12242</v>
+        <v>15903</v>
       </c>
       <c r="F338" t="str">
         <v>OK_MIXTO</v>
@@ -13273,22 +13273,22 @@
         <v>200</v>
       </c>
       <c r="E339">
-        <v>16541</v>
+        <v>16416</v>
       </c>
       <c r="F339" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G339">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H339">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I339">
         <v>4</v>
       </c>
       <c r="J339" t="str">
-        <v>electricidad</v>
+        <v>cristaleria</v>
       </c>
       <c r="K339" t="str">
         <v>NO</v>
@@ -13311,25 +13311,25 @@
         <v>200</v>
       </c>
       <c r="E340">
-        <v>16843</v>
+        <v>19917</v>
       </c>
       <c r="F340" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G340">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H340">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I340">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J340" t="str">
-        <v>fachadas</v>
+        <v>suelos_alicatados</v>
       </c>
       <c r="K340" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L340" t="str">
         <v/>
@@ -13349,19 +13349,19 @@
         <v>200</v>
       </c>
       <c r="E341">
-        <v>15312</v>
+        <v>14572</v>
       </c>
       <c r="F341" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G341">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H341">
         <v>1</v>
       </c>
       <c r="I341">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J341" t="str">
         <v>energia_solar</v>
@@ -13387,7 +13387,7 @@
         <v>403</v>
       </c>
       <c r="E342">
-        <v>973</v>
+        <v>788</v>
       </c>
       <c r="F342" t="str">
         <v>ERROR_TECNICO</v>
@@ -13425,19 +13425,19 @@
         <v>200</v>
       </c>
       <c r="E343">
-        <v>18894</v>
+        <v>13751</v>
       </c>
       <c r="F343" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G343">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H343">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I343">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J343" t="str">
         <v>mantenimiento_general</v>
@@ -13463,7 +13463,7 @@
         <v>200</v>
       </c>
       <c r="E344">
-        <v>10722</v>
+        <v>9602</v>
       </c>
       <c r="F344" t="str">
         <v>OK_MIXTO</v>
@@ -13501,7 +13501,7 @@
         <v>200</v>
       </c>
       <c r="E345">
-        <v>13724</v>
+        <v>17951</v>
       </c>
       <c r="F345" t="str">
         <v>OK_MIXTO</v>
@@ -13539,19 +13539,19 @@
         <v>200</v>
       </c>
       <c r="E346">
-        <v>17931</v>
+        <v>11753</v>
       </c>
       <c r="F346" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G346">
         <v>6</v>
       </c>
       <c r="H346">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I346">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J346" t="str">
         <v>mantenimiento_general</v>
@@ -13577,7 +13577,7 @@
         <v>403</v>
       </c>
       <c r="E347">
-        <v>1122</v>
+        <v>732</v>
       </c>
       <c r="F347" t="str">
         <v>ERROR_TECNICO</v>
@@ -13615,19 +13615,19 @@
         <v>200</v>
       </c>
       <c r="E348">
-        <v>17509</v>
+        <v>15779</v>
       </c>
       <c r="F348" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G348">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H348">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I348">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J348" t="str">
         <v>tejados_cubiertas</v>
@@ -13653,25 +13653,25 @@
         <v>200</v>
       </c>
       <c r="E349">
-        <v>23654</v>
+        <v>24277</v>
       </c>
       <c r="F349" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G349">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H349">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I349">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J349" t="str">
-        <v>fontaneria</v>
+        <v>mantenimiento_general</v>
       </c>
       <c r="K349" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L349" t="str">
         <v/>
@@ -13691,16 +13691,16 @@
         <v>200</v>
       </c>
       <c r="E350">
-        <v>11665</v>
+        <v>11670</v>
       </c>
       <c r="F350" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G350">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H350">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I350">
         <v>2</v>
@@ -13729,16 +13729,16 @@
         <v>200</v>
       </c>
       <c r="E351">
-        <v>13918</v>
+        <v>15347</v>
       </c>
       <c r="F351" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G351">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I351">
         <v>4</v>
@@ -13767,19 +13767,19 @@
         <v>200</v>
       </c>
       <c r="E352">
-        <v>17191</v>
+        <v>24153</v>
       </c>
       <c r="F352" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G352">
+        <v>9</v>
+      </c>
+      <c r="H352">
         <v>4</v>
       </c>
-      <c r="H352">
-        <v>2</v>
-      </c>
       <c r="I352">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J352" t="str">
         <v>albanileria</v>
@@ -13805,25 +13805,25 @@
         <v>200</v>
       </c>
       <c r="E353">
-        <v>13914</v>
+        <v>12905</v>
       </c>
       <c r="F353" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G353">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H353">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I353">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J353" t="str">
-        <v>mantenimiento_general</v>
+        <v>multiservicio</v>
       </c>
       <c r="K353" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L353" t="str">
         <v/>
@@ -13843,16 +13843,16 @@
         <v>200</v>
       </c>
       <c r="E354">
-        <v>13919</v>
+        <v>13813</v>
       </c>
       <c r="F354" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G354">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H354">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I354">
         <v>2</v>
@@ -13881,7 +13881,7 @@
         <v>200</v>
       </c>
       <c r="E355">
-        <v>14349</v>
+        <v>17459</v>
       </c>
       <c r="F355" t="str">
         <v>OK_MIXTO</v>
@@ -13896,10 +13896,10 @@
         <v>3</v>
       </c>
       <c r="J355" t="str">
-        <v>mecanica_especializada</v>
+        <v>mantenimiento_general</v>
       </c>
       <c r="K355" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L355" t="str">
         <v/>
@@ -13919,7 +13919,7 @@
         <v>200</v>
       </c>
       <c r="E356">
-        <v>17709</v>
+        <v>11105</v>
       </c>
       <c r="F356" t="str">
         <v>OK_MIXTO</v>
@@ -13928,10 +13928,10 @@
         <v>6</v>
       </c>
       <c r="H356">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I356">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J356" t="str">
         <v>pintura</v>
@@ -13957,19 +13957,19 @@
         <v>200</v>
       </c>
       <c r="E357">
-        <v>14741</v>
+        <v>15610</v>
       </c>
       <c r="F357" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G357">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H357">
         <v>3</v>
       </c>
       <c r="I357">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J357" t="str">
         <v>albanileria</v>
@@ -13995,7 +13995,7 @@
         <v>200</v>
       </c>
       <c r="E358">
-        <v>13411</v>
+        <v>11858</v>
       </c>
       <c r="F358" t="str">
         <v>OK_MIXTO</v>
@@ -14004,10 +14004,10 @@
         <v>4</v>
       </c>
       <c r="H358">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I358">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J358" t="str">
         <v>cerrajeria</v>
@@ -14033,16 +14033,16 @@
         <v>200</v>
       </c>
       <c r="E359">
-        <v>15456</v>
+        <v>14902</v>
       </c>
       <c r="F359" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G359">
+        <v>7</v>
+      </c>
+      <c r="H359">
         <v>6</v>
-      </c>
-      <c r="H359">
-        <v>5</v>
       </c>
       <c r="I359">
         <v>1</v>
@@ -14071,7 +14071,7 @@
         <v>200</v>
       </c>
       <c r="E360">
-        <v>13711</v>
+        <v>13665</v>
       </c>
       <c r="F360" t="str">
         <v>OK_MIXTO</v>
@@ -14080,10 +14080,10 @@
         <v>5</v>
       </c>
       <c r="H360">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J360" t="str">
         <v>electricidad</v>
@@ -14109,16 +14109,16 @@
         <v>200</v>
       </c>
       <c r="E361">
-        <v>14121</v>
+        <v>16121</v>
       </c>
       <c r="F361" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G361">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H361">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I361">
         <v>3</v>
@@ -14147,7 +14147,7 @@
         <v>200</v>
       </c>
       <c r="E362">
-        <v>35023</v>
+        <v>30307</v>
       </c>
       <c r="F362" t="str">
         <v>OK_MIXTO</v>
@@ -14156,10 +14156,10 @@
         <v>12</v>
       </c>
       <c r="H362">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I362">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J362" t="str">
         <v>reforma_integral</v>
@@ -14185,19 +14185,19 @@
         <v>200</v>
       </c>
       <c r="E363">
-        <v>28030</v>
+        <v>24569</v>
       </c>
       <c r="F363" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G363">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H363">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I363">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J363" t="str">
         <v>reforma_integral</v>
@@ -14223,19 +14223,19 @@
         <v>200</v>
       </c>
       <c r="E364">
-        <v>37885</v>
+        <v>47710</v>
       </c>
       <c r="F364" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G364">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H364">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I364">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J364" t="str">
         <v>reforma_integral</v>
@@ -14261,22 +14261,22 @@
         <v>200</v>
       </c>
       <c r="E365">
-        <v>39316</v>
+        <v>48627</v>
       </c>
       <c r="F365" t="str">
-        <v>OK_MIXTO</v>
+        <v>VACIO</v>
       </c>
       <c r="G365">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H365">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I365">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J365" t="str">
-        <v>reforma_integral</v>
+        <v/>
       </c>
       <c r="K365" t="str">
         <v>NO</v>
@@ -14299,19 +14299,19 @@
         <v>200</v>
       </c>
       <c r="E366">
-        <v>41903</v>
+        <v>30302</v>
       </c>
       <c r="F366" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G366">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H366">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I366">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J366" t="str">
         <v>reforma_integral</v>
@@ -14337,7 +14337,7 @@
         <v>200</v>
       </c>
       <c r="E367">
-        <v>31941</v>
+        <v>30761</v>
       </c>
       <c r="F367" t="str">
         <v>OK_MIXTO</v>
@@ -14375,19 +14375,19 @@
         <v>200</v>
       </c>
       <c r="E368">
-        <v>32142</v>
+        <v>37067</v>
       </c>
       <c r="F368" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G368">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H368">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I368">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J368" t="str">
         <v>reforma_integral</v>
@@ -14413,19 +14413,19 @@
         <v>200</v>
       </c>
       <c r="E369">
-        <v>34584</v>
+        <v>42798</v>
       </c>
       <c r="F369" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G369">
+        <v>23</v>
+      </c>
+      <c r="H369">
         <v>16</v>
       </c>
-      <c r="H369">
-        <v>12</v>
-      </c>
       <c r="I369">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J369" t="str">
         <v>reforma_integral</v>
@@ -14451,19 +14451,19 @@
         <v>200</v>
       </c>
       <c r="E370">
-        <v>29690</v>
+        <v>28362</v>
       </c>
       <c r="F370" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G370">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H370">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I370">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J370" t="str">
         <v>reforma_integral</v>
@@ -14489,7 +14489,7 @@
         <v>200</v>
       </c>
       <c r="E371">
-        <v>27045</v>
+        <v>29279</v>
       </c>
       <c r="F371" t="str">
         <v>OK_MIXTO</v>
@@ -14498,10 +14498,10 @@
         <v>12</v>
       </c>
       <c r="H371">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I371">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J371" t="str">
         <v>reforma_integral</v>
@@ -14527,7 +14527,7 @@
         <v>200</v>
       </c>
       <c r="E372">
-        <v>25676</v>
+        <v>28010</v>
       </c>
       <c r="F372" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14565,7 +14565,7 @@
         <v>200</v>
       </c>
       <c r="E373">
-        <v>31364</v>
+        <v>28359</v>
       </c>
       <c r="F373" t="str">
         <v>OK_MIXTO</v>
@@ -14603,7 +14603,7 @@
         <v>200</v>
       </c>
       <c r="E374">
-        <v>32159</v>
+        <v>27844</v>
       </c>
       <c r="F374" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14641,19 +14641,19 @@
         <v>200</v>
       </c>
       <c r="E375">
-        <v>37213</v>
+        <v>31361</v>
       </c>
       <c r="F375" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G375">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H375">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I375">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J375" t="str">
         <v>reforma_integral</v>
@@ -14679,16 +14679,16 @@
         <v>200</v>
       </c>
       <c r="E376">
-        <v>34702</v>
+        <v>32597</v>
       </c>
       <c r="F376" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G376">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H376">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I376">
         <v>10</v>
@@ -14717,7 +14717,7 @@
         <v>200</v>
       </c>
       <c r="E377">
-        <v>26817</v>
+        <v>24467</v>
       </c>
       <c r="F377" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14755,7 +14755,7 @@
         <v>200</v>
       </c>
       <c r="E378">
-        <v>27835</v>
+        <v>29891</v>
       </c>
       <c r="F378" t="str">
         <v>OK_MIXTO</v>
@@ -14764,10 +14764,10 @@
         <v>13</v>
       </c>
       <c r="H378">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I378">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J378" t="str">
         <v>reforma_integral</v>
@@ -14793,19 +14793,19 @@
         <v>200</v>
       </c>
       <c r="E379">
-        <v>33198</v>
+        <v>24177</v>
       </c>
       <c r="F379" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G379">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H379">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I379">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J379" t="str">
         <v>reforma_integral</v>
@@ -14831,19 +14831,19 @@
         <v>200</v>
       </c>
       <c r="E380">
-        <v>26196</v>
+        <v>31937</v>
       </c>
       <c r="F380" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G380">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H380">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I380">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J380" t="str">
         <v>reforma_integral</v>
@@ -14869,19 +14869,19 @@
         <v>200</v>
       </c>
       <c r="E381">
-        <v>43254</v>
+        <v>14835</v>
       </c>
       <c r="F381" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G381">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H381">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I381">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J381" t="str">
         <v>reforma_integral</v>
@@ -14907,19 +14907,19 @@
         <v>200</v>
       </c>
       <c r="E382">
-        <v>10486</v>
+        <v>11792</v>
       </c>
       <c r="F382" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G382">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H382">
         <v>1</v>
       </c>
       <c r="I382">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J382" t="str">
         <v>persianas</v>
@@ -14945,19 +14945,19 @@
         <v>200</v>
       </c>
       <c r="E383">
-        <v>13495</v>
+        <v>17970</v>
       </c>
       <c r="F383" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G383">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H383">
         <v>2</v>
       </c>
       <c r="I383">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J383" t="str">
         <v>persianas</v>
@@ -14983,7 +14983,7 @@
         <v>200</v>
       </c>
       <c r="E384">
-        <v>11240</v>
+        <v>12223</v>
       </c>
       <c r="F384" t="str">
         <v>OK_MIXTO</v>
@@ -15021,19 +15021,19 @@
         <v>200</v>
       </c>
       <c r="E385">
-        <v>13495</v>
+        <v>12590</v>
       </c>
       <c r="F385" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G385">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H385">
         <v>2</v>
       </c>
       <c r="I385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J385" t="str">
         <v>persianas</v>
@@ -15059,19 +15059,19 @@
         <v>200</v>
       </c>
       <c r="E386">
-        <v>18343</v>
+        <v>15578</v>
       </c>
       <c r="F386" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G386">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H386">
         <v>1</v>
       </c>
       <c r="I386">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J386" t="str">
         <v>persianas</v>
@@ -15097,7 +15097,7 @@
         <v>200</v>
       </c>
       <c r="E387">
-        <v>11709</v>
+        <v>11830</v>
       </c>
       <c r="F387" t="str">
         <v>OK_MIXTO</v>
@@ -15135,7 +15135,7 @@
         <v>200</v>
       </c>
       <c r="E388">
-        <v>21639</v>
+        <v>18118</v>
       </c>
       <c r="F388" t="str">
         <v>OK_MIXTO</v>
@@ -15173,7 +15173,7 @@
         <v>200</v>
       </c>
       <c r="E389">
-        <v>19657</v>
+        <v>17940</v>
       </c>
       <c r="F389" t="str">
         <v>OK_MIXTO</v>
@@ -15182,10 +15182,10 @@
         <v>8</v>
       </c>
       <c r="H389">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I389">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J389" t="str">
         <v>carpinteria</v>
@@ -15211,19 +15211,19 @@
         <v>200</v>
       </c>
       <c r="E390">
-        <v>21635</v>
+        <v>17937</v>
       </c>
       <c r="F390" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G390">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H390">
         <v>1</v>
       </c>
       <c r="I390">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J390" t="str">
         <v>persianas</v>
@@ -15249,19 +15249,19 @@
         <v>200</v>
       </c>
       <c r="E391">
-        <v>13200</v>
+        <v>10812</v>
       </c>
       <c r="F391" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G391">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H391">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I391">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J391" t="str">
         <v>persianas</v>
@@ -15287,7 +15287,7 @@
         <v>200</v>
       </c>
       <c r="E392">
-        <v>18397</v>
+        <v>19667</v>
       </c>
       <c r="F392" t="str">
         <v>OK_MIXTO</v>
@@ -15325,7 +15325,7 @@
         <v>200</v>
       </c>
       <c r="E393">
-        <v>13176</v>
+        <v>13063</v>
       </c>
       <c r="F393" t="str">
         <v>OK_MIXTO</v>
@@ -15363,19 +15363,19 @@
         <v>200</v>
       </c>
       <c r="E394">
-        <v>18803</v>
+        <v>18078</v>
       </c>
       <c r="F394" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G394">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H394">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I394">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J394" t="str">
         <v>persianas</v>
@@ -15401,19 +15401,19 @@
         <v>200</v>
       </c>
       <c r="E395">
-        <v>18396</v>
+        <v>23647</v>
       </c>
       <c r="F395" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G395">
+        <v>6</v>
+      </c>
+      <c r="H395">
+        <v>1</v>
+      </c>
+      <c r="I395">
         <v>5</v>
-      </c>
-      <c r="H395">
-        <v>2</v>
-      </c>
-      <c r="I395">
-        <v>3</v>
       </c>
       <c r="J395" t="str">
         <v>persianas</v>
@@ -15439,7 +15439,7 @@
         <v>200</v>
       </c>
       <c r="E396">
-        <v>11229</v>
+        <v>11217</v>
       </c>
       <c r="F396" t="str">
         <v>OK_MIXTO</v>
@@ -15477,7 +15477,7 @@
         <v>200</v>
       </c>
       <c r="E397">
-        <v>17783</v>
+        <v>13878</v>
       </c>
       <c r="F397" t="str">
         <v>OK_MIXTO</v>
@@ -15486,13 +15486,13 @@
         <v>5</v>
       </c>
       <c r="H397">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I397">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J397" t="str">
-        <v>fachadas</v>
+        <v>carpinteria</v>
       </c>
       <c r="K397" t="str">
         <v>NO</v>
@@ -15515,7 +15515,7 @@
         <v>200</v>
       </c>
       <c r="E398">
-        <v>10631</v>
+        <v>11940</v>
       </c>
       <c r="F398" t="str">
         <v>OK_MIXTO</v>
@@ -15524,10 +15524,10 @@
         <v>5</v>
       </c>
       <c r="H398">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I398">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J398" t="str">
         <v>persianas</v>
@@ -15553,7 +15553,7 @@
         <v>200</v>
       </c>
       <c r="E399">
-        <v>11179</v>
+        <v>11237</v>
       </c>
       <c r="F399" t="str">
         <v>OK_MIXTO</v>
@@ -15591,19 +15591,19 @@
         <v>200</v>
       </c>
       <c r="E400">
-        <v>21587</v>
+        <v>13776</v>
       </c>
       <c r="F400" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G400">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H400">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I400">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J400" t="str">
         <v>cerrajeria</v>
@@ -15629,19 +15629,19 @@
         <v>200</v>
       </c>
       <c r="E401">
-        <v>22435</v>
+        <v>22582</v>
       </c>
       <c r="F401" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G401">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H401">
         <v>3</v>
       </c>
       <c r="I401">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J401" t="str">
         <v>cerrajeria</v>
@@ -15744,7 +15744,7 @@
         <v>60%</v>
       </c>
       <c r="K2">
-        <v>19450</v>
+        <v>19363</v>
       </c>
     </row>
     <row r="3">
@@ -15758,10 +15758,10 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -15773,13 +15773,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>95%</v>
+        <v>90%</v>
       </c>
       <c r="J3" t="str">
         <v>80%</v>
       </c>
       <c r="K3">
-        <v>16318</v>
+        <v>16648</v>
       </c>
     </row>
     <row r="4">
@@ -15793,10 +15793,10 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -15808,13 +15808,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>100%</v>
+        <v>95%</v>
       </c>
       <c r="J4" t="str">
         <v>80%</v>
       </c>
       <c r="K4">
-        <v>14534</v>
+        <v>15024</v>
       </c>
     </row>
     <row r="5">
@@ -15828,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -15840,16 +15840,16 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>90%</v>
+        <v>95%</v>
       </c>
       <c r="J5" t="str">
         <v>75%</v>
       </c>
       <c r="K5">
-        <v>20205</v>
+        <v>21546</v>
       </c>
     </row>
     <row r="6">
@@ -15863,10 +15863,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -15878,13 +15878,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>85%</v>
+        <v>75%</v>
       </c>
       <c r="J6" t="str">
         <v>80%</v>
       </c>
       <c r="K6">
-        <v>21630</v>
+        <v>21372</v>
       </c>
     </row>
     <row r="7">
@@ -15898,10 +15898,10 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -15913,13 +15913,13 @@
         <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>95%</v>
+        <v>100%</v>
       </c>
       <c r="J7" t="str">
         <v>85%</v>
       </c>
       <c r="K7">
-        <v>15603</v>
+        <v>15460</v>
       </c>
     </row>
     <row r="8">
@@ -15933,10 +15933,10 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -15948,13 +15948,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v>100%</v>
+        <v>95%</v>
       </c>
       <c r="J8" t="str">
-        <v>75%</v>
+        <v>80%</v>
       </c>
       <c r="K8">
-        <v>17294</v>
+        <v>16378</v>
       </c>
     </row>
     <row r="9">
@@ -15968,13 +15968,13 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -15983,13 +15983,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v>95%</v>
+        <v>80%</v>
       </c>
       <c r="J9" t="str">
-        <v>90%</v>
+        <v>85%</v>
       </c>
       <c r="K9">
-        <v>21164</v>
+        <v>21698</v>
       </c>
     </row>
     <row r="10">
@@ -16003,10 +16003,10 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -16018,13 +16018,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>100%</v>
+        <v>95%</v>
       </c>
       <c r="J10" t="str">
-        <v>75%</v>
+        <v>70%</v>
       </c>
       <c r="K10">
-        <v>18089</v>
+        <v>20126</v>
       </c>
     </row>
     <row r="11">
@@ -16038,13 +16038,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -16053,13 +16053,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>95%</v>
+        <v>85%</v>
       </c>
       <c r="J11" t="str">
-        <v>75%</v>
+        <v>70%</v>
       </c>
       <c r="K11">
-        <v>17248</v>
+        <v>16837</v>
       </c>
     </row>
     <row r="12">
@@ -16073,10 +16073,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -16088,13 +16088,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>75%</v>
+        <v>85%</v>
       </c>
       <c r="J12" t="str">
-        <v>90%</v>
+        <v>80%</v>
       </c>
       <c r="K12">
-        <v>20421</v>
+        <v>20266</v>
       </c>
     </row>
     <row r="13">
@@ -16105,13 +16105,13 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -16123,13 +16123,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>100%</v>
+        <v>90%</v>
       </c>
       <c r="J13" t="str">
         <v>85%</v>
       </c>
       <c r="K13">
-        <v>15744</v>
+        <v>16543</v>
       </c>
     </row>
     <row r="14">
@@ -16143,10 +16143,10 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -16158,13 +16158,13 @@
         <v>0</v>
       </c>
       <c r="I14" t="str">
-        <v>80%</v>
+        <v>90%</v>
       </c>
       <c r="J14" t="str">
-        <v>25%</v>
+        <v>30%</v>
       </c>
       <c r="K14">
-        <v>13932</v>
+        <v>13662</v>
       </c>
     </row>
     <row r="15">
@@ -16199,7 +16199,7 @@
         <v>75%</v>
       </c>
       <c r="K15">
-        <v>15926</v>
+        <v>15294</v>
       </c>
     </row>
     <row r="16">
@@ -16213,10 +16213,10 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -16228,13 +16228,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="str">
-        <v>95%</v>
+        <v>85%</v>
       </c>
       <c r="J16" t="str">
         <v>75%</v>
       </c>
       <c r="K16">
-        <v>14799</v>
+        <v>14832</v>
       </c>
     </row>
     <row r="17">
@@ -16248,10 +16248,10 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -16263,13 +16263,13 @@
         <v>0</v>
       </c>
       <c r="I17" t="str">
+        <v>100%</v>
+      </c>
+      <c r="J17" t="str">
         <v>95%</v>
       </c>
-      <c r="J17" t="str">
-        <v>100%</v>
-      </c>
       <c r="K17">
-        <v>17261</v>
+        <v>19391</v>
       </c>
     </row>
     <row r="18">
@@ -16283,13 +16283,13 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -16298,13 +16298,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>75%</v>
+        <v>60%</v>
       </c>
       <c r="J18" t="str">
         <v>0%</v>
       </c>
       <c r="K18">
-        <v>32799</v>
+        <v>31163</v>
       </c>
     </row>
     <row r="19">
@@ -16318,10 +16318,10 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -16333,13 +16333,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>100%</v>
+        <v>95%</v>
       </c>
       <c r="J19" t="str">
         <v>75%</v>
       </c>
       <c r="K19">
-        <v>17147</v>
+        <v>18290</v>
       </c>
     </row>
     <row r="20">
@@ -16353,10 +16353,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -16368,13 +16368,13 @@
         <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>95%</v>
+        <v>90%</v>
       </c>
       <c r="J20" t="str">
-        <v>65%</v>
+        <v>70%</v>
       </c>
       <c r="K20">
-        <v>18857</v>
+        <v>20187</v>
       </c>
     </row>
     <row r="21">
@@ -16388,10 +16388,10 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -16403,13 +16403,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="str">
+        <v>95%</v>
+      </c>
+      <c r="J21" t="str">
         <v>100%</v>
       </c>
-      <c r="J21" t="str">
-        <v>90%</v>
-      </c>
       <c r="K21">
-        <v>17577</v>
+        <v>18073</v>
       </c>
     </row>
     <row r="22">
@@ -16420,31 +16420,31 @@
         <v>400</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="str">
-        <v>93%</v>
+        <v>90%</v>
       </c>
       <c r="J22" t="str">
         <v>73%</v>
       </c>
       <c r="K22">
-        <v>18300</v>
+        <v>18608</v>
       </c>
     </row>
   </sheetData>
@@ -16456,7 +16456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -16496,19 +16496,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B2" t="str">
         <v>Fontanería</v>
       </c>
       <c r="C2" t="str">
-        <v>Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad</v>
+        <v>Cambio de bañera por plato de ducha en baño principal de 90x90 con mamparas</v>
       </c>
       <c r="D2">
         <v>200</v>
       </c>
       <c r="E2">
-        <v>23658</v>
+        <v>28714</v>
       </c>
       <c r="F2" t="str">
         <v>VACIO</v>
@@ -16517,24 +16517,24 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>{"transcript":"Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados</v>
+        <v>{"transcript":"Cambio de bañera por plato de ducha en baño principal de 90x90 con mamparas","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":{"subtotal":0,"</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="B3" t="str">
-        <v>Climatización</v>
+        <v>Fontanería</v>
       </c>
       <c r="C3" t="str">
-        <v>Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados</v>
+        <v>Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad</v>
       </c>
       <c r="D3">
         <v>200</v>
       </c>
       <c r="E3">
-        <v>25225</v>
+        <v>25516</v>
       </c>
       <c r="F3" t="str">
         <v>VACIO</v>
@@ -16543,50 +16543,50 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>{"transcript":"Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":{"su</v>
+        <v>{"transcript":"Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B4" t="str">
         <v>Climatización</v>
       </c>
       <c r="C4" t="str">
-        <v>Mantenimiento anual de caldera de gas, limpieza quemador, revisión electrodos y gases de combustión</v>
+        <v>Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados</v>
       </c>
       <c r="D4">
         <v>200</v>
       </c>
       <c r="E4">
-        <v>13117</v>
+        <v>25810</v>
       </c>
       <c r="F4" t="str">
-        <v>PRECIO_INVALIDO</v>
+        <v>VACIO</v>
       </c>
       <c r="G4" t="str">
-        <v>Partida de catálogo con precio 0 o nulo</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>{"transcript":"Mantenimiento anual de caldera de gas, limpieza quemador, revisión electrodos y gases de combustión","quote":{"resumen":{"texto_original":"Mantenimiento anual de caldera de gas, limpieza quemador, revisión electrodos y gases de combustión","tipo_presupuesto":"mantenimiento_recurrente"</v>
+        <v>{"transcript":"Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":{"su</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B5" t="str">
         <v>Energía Solar</v>
       </c>
       <c r="C5" t="str">
-        <v>Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético</v>
+        <v>Instalar cargador de coche eléctrico alimentado por energía solar con gestión inteligente de carga</v>
       </c>
       <c r="D5">
         <v>200</v>
       </c>
       <c r="E5">
-        <v>26454</v>
+        <v>29018</v>
       </c>
       <c r="F5" t="str">
         <v>VACIO</v>
@@ -16595,24 +16595,24 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>{"transcript":"Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
+        <v>{"transcript":"Instalar cargador de coche eléctrico alimentado por energía solar con gestión inteligente de carga","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"ca</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>320</v>
+        <v>235</v>
       </c>
       <c r="B6" t="str">
-        <v>Contra Incendios</v>
+        <v>Energía Solar</v>
       </c>
       <c r="C6" t="str">
-        <v>Instalar detección temprana de incendios en archivo de documentación, sistema de aspiración VESDA</v>
+        <v>Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético</v>
       </c>
       <c r="D6">
         <v>200</v>
       </c>
       <c r="E6">
-        <v>28453</v>
+        <v>27526</v>
       </c>
       <c r="F6" t="str">
         <v>VACIO</v>
@@ -16621,50 +16621,50 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>{"transcript":"Instalar detección temprana de incendios en archivo de documentación, sistema de aspiración VESDA","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
+        <v>{"transcript":"Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="B7" t="str">
-        <v>Mantenimiento General</v>
+        <v>Contra Incendios</v>
       </c>
       <c r="C7" t="str">
-        <v>Contrato de mantenimiento mensual de edificio de oficinas, electricidad, fontanería y carpintería</v>
+        <v>Instalar detección temprana de incendios en archivo de documentación, sistema de aspiración VESDA</v>
       </c>
       <c r="D7">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="E7">
-        <v>973</v>
+        <v>30714</v>
       </c>
       <c r="F7" t="str">
-        <v>ERROR_TECNICO</v>
+        <v>VACIO</v>
       </c>
       <c r="G7" t="str">
-        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
+        <v>{"transcript":"Instalar detección temprana de incendios en archivo de documentación, sistema de aspiración VESDA","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B8" t="str">
         <v>Mantenimiento General</v>
       </c>
       <c r="C8" t="str">
-        <v>Contrato anual de mantenimiento de comunidad de vecinos, incluye piscina, jardines y zonas comunes</v>
+        <v>Contrato de mantenimiento mensual de edificio de oficinas, electricidad, fontanería y carpintería</v>
       </c>
       <c r="D8">
         <v>403</v>
       </c>
       <c r="E8">
-        <v>1122</v>
+        <v>788</v>
       </c>
       <c r="F8" t="str">
         <v>ERROR_TECNICO</v>
@@ -16676,9 +16676,61 @@
         <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9">
+        <v>346</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Mantenimiento General</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Contrato anual de mantenimiento de comunidad de vecinos, incluye piscina, jardines y zonas comunes</v>
+      </c>
+      <c r="D9">
+        <v>403</v>
+      </c>
+      <c r="E9">
+        <v>732</v>
+      </c>
+      <c r="F9" t="str">
+        <v>ERROR_TECNICO</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
+      </c>
+      <c r="H9" t="str">
+        <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>364</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Reformas Integrales</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Convertir local comercial en vivienda de 60 metros cuadrados con licencia de cambio de uso</v>
+      </c>
+      <c r="D10">
+        <v>200</v>
+      </c>
+      <c r="E10">
+        <v>48627</v>
+      </c>
+      <c r="F10" t="str">
+        <v>VACIO</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>{"transcript":"Convertir local comercial en vivienda de 60 metros cuadrados con licencia de cambio de uso","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/test-motor-ia/output/test_results.xlsx
+++ b/scripts/test-motor-ia/output/test_results.xlsx
@@ -467,7 +467,7 @@
         <v>200</v>
       </c>
       <c r="E2">
-        <v>11659</v>
+        <v>10736</v>
       </c>
       <c r="F2" t="str">
         <v>OK_MIXTO</v>
@@ -505,25 +505,25 @@
         <v>200</v>
       </c>
       <c r="E3">
-        <v>28714</v>
+        <v>19738</v>
       </c>
       <c r="F3" t="str">
-        <v>VACIO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>fontaneria</v>
       </c>
       <c r="K3" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -543,7 +543,7 @@
         <v>200</v>
       </c>
       <c r="E4">
-        <v>11661</v>
+        <v>11222</v>
       </c>
       <c r="F4" t="str">
         <v>OK_MIXTO</v>
@@ -581,16 +581,16 @@
         <v>200</v>
       </c>
       <c r="E5">
-        <v>12023</v>
+        <v>12437</v>
       </c>
       <c r="F5" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -619,7 +619,7 @@
         <v>200</v>
       </c>
       <c r="E6">
-        <v>17141</v>
+        <v>16294</v>
       </c>
       <c r="F6" t="str">
         <v>OK_MIXTO</v>
@@ -657,19 +657,19 @@
         <v>200</v>
       </c>
       <c r="E7">
-        <v>23799</v>
+        <v>17511</v>
       </c>
       <c r="F7" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>5</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J7" t="str">
         <v>fontaneria</v>
@@ -695,22 +695,22 @@
         <v>200</v>
       </c>
       <c r="E8">
-        <v>25516</v>
+        <v>23451</v>
       </c>
       <c r="F8" t="str">
-        <v>VACIO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>reforma_integral</v>
       </c>
       <c r="K8" t="str">
         <v>NO</v>
@@ -733,19 +733,19 @@
         <v>200</v>
       </c>
       <c r="E9">
-        <v>14066</v>
+        <v>17907</v>
       </c>
       <c r="F9" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <v>7</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="str">
         <v>climatizacion</v>
@@ -771,19 +771,19 @@
         <v>200</v>
       </c>
       <c r="E10">
-        <v>19354</v>
+        <v>18601</v>
       </c>
       <c r="F10" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" t="str">
         <v>fontaneria</v>
@@ -809,19 +809,19 @@
         <v>200</v>
       </c>
       <c r="E11">
-        <v>15011</v>
+        <v>13736</v>
       </c>
       <c r="F11" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" t="str">
         <v>fontaneria</v>
@@ -847,7 +847,7 @@
         <v>200</v>
       </c>
       <c r="E12">
-        <v>13147</v>
+        <v>12937</v>
       </c>
       <c r="F12" t="str">
         <v>OK_MIXTO</v>
@@ -856,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="str">
         <v>fontaneria</v>
@@ -885,19 +885,19 @@
         <v>200</v>
       </c>
       <c r="E13">
-        <v>16867</v>
+        <v>18383</v>
       </c>
       <c r="F13" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" t="str">
         <v>fontaneria</v>
@@ -923,7 +923,7 @@
         <v>200</v>
       </c>
       <c r="E14">
-        <v>14924</v>
+        <v>16971</v>
       </c>
       <c r="F14" t="str">
         <v>OK_MIXTO</v>
@@ -932,10 +932,10 @@
         <v>7</v>
       </c>
       <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
         <v>3</v>
-      </c>
-      <c r="I14">
-        <v>4</v>
       </c>
       <c r="J14" t="str">
         <v>fontaneria</v>
@@ -961,19 +961,19 @@
         <v>200</v>
       </c>
       <c r="E15">
-        <v>11529</v>
+        <v>12442</v>
       </c>
       <c r="F15" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="str">
         <v>mantenimiento_general</v>
@@ -999,19 +999,19 @@
         <v>200</v>
       </c>
       <c r="E16">
-        <v>15276</v>
+        <v>19812</v>
       </c>
       <c r="F16" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G16">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" t="str">
         <v>fontaneria</v>
@@ -1037,7 +1037,7 @@
         <v>200</v>
       </c>
       <c r="E17">
-        <v>24893</v>
+        <v>27310</v>
       </c>
       <c r="F17" t="str">
         <v>OK_MIXTO</v>
@@ -1046,10 +1046,10 @@
         <v>12</v>
       </c>
       <c r="H17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J17" t="str">
         <v>climatizacion</v>
@@ -1075,7 +1075,7 @@
         <v>200</v>
       </c>
       <c r="E18">
-        <v>21598</v>
+        <v>22851</v>
       </c>
       <c r="F18" t="str">
         <v>OK_MIXTO</v>
@@ -1084,10 +1084,10 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J18" t="str">
         <v>fontaneria</v>
@@ -1113,19 +1113,19 @@
         <v>200</v>
       </c>
       <c r="E19">
-        <v>13569</v>
+        <v>20529</v>
       </c>
       <c r="F19" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H19">
         <v>5</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J19" t="str">
         <v>fontaneria</v>
@@ -1151,16 +1151,16 @@
         <v>200</v>
       </c>
       <c r="E20">
-        <v>14070</v>
+        <v>14196</v>
       </c>
       <c r="F20" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>3</v>
@@ -1189,7 +1189,7 @@
         <v>200</v>
       </c>
       <c r="E21">
-        <v>11927</v>
+        <v>10797</v>
       </c>
       <c r="F21" t="str">
         <v>OK_MIXTO</v>
@@ -1227,7 +1227,7 @@
         <v>200</v>
       </c>
       <c r="E22">
-        <v>15336</v>
+        <v>15634</v>
       </c>
       <c r="F22" t="str">
         <v>OK_MIXTO</v>
@@ -1265,7 +1265,7 @@
         <v>200</v>
       </c>
       <c r="E23">
-        <v>15333</v>
+        <v>22540</v>
       </c>
       <c r="F23" t="str">
         <v>OK_MIXTO</v>
@@ -1303,19 +1303,19 @@
         <v>200</v>
       </c>
       <c r="E24">
-        <v>21568</v>
+        <v>23008</v>
       </c>
       <c r="F24" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" t="str">
         <v>electricidad</v>
@@ -1341,16 +1341,16 @@
         <v>200</v>
       </c>
       <c r="E25">
-        <v>17156</v>
+        <v>23650</v>
       </c>
       <c r="F25" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25">
         <v>6</v>
@@ -1379,19 +1379,19 @@
         <v>200</v>
       </c>
       <c r="E26">
-        <v>11756</v>
+        <v>8730</v>
       </c>
       <c r="F26" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" t="str">
         <v>electricidad</v>
@@ -1417,19 +1417,19 @@
         <v>200</v>
       </c>
       <c r="E27">
-        <v>14016</v>
+        <v>13599</v>
       </c>
       <c r="F27" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27">
+        <v>4</v>
+      </c>
+      <c r="I27">
         <v>2</v>
-      </c>
-      <c r="I27">
-        <v>3</v>
       </c>
       <c r="J27" t="str">
         <v>electricidad</v>
@@ -1455,19 +1455,19 @@
         <v>200</v>
       </c>
       <c r="E28">
-        <v>15074</v>
+        <v>14629</v>
       </c>
       <c r="F28" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28">
         <v>2</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" t="str">
         <v>electricidad</v>
@@ -1493,19 +1493,19 @@
         <v>200</v>
       </c>
       <c r="E29">
-        <v>25369</v>
+        <v>19489</v>
       </c>
       <c r="F29" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H29">
         <v>4</v>
       </c>
       <c r="I29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J29" t="str">
         <v>electricidad</v>
@@ -1531,7 +1531,7 @@
         <v>200</v>
       </c>
       <c r="E30">
-        <v>11055</v>
+        <v>10691</v>
       </c>
       <c r="F30" t="str">
         <v>OK_MIXTO</v>
@@ -1569,7 +1569,7 @@
         <v>200</v>
       </c>
       <c r="E31">
-        <v>20140</v>
+        <v>20583</v>
       </c>
       <c r="F31" t="str">
         <v>OK_MIXTO</v>
@@ -1607,16 +1607,16 @@
         <v>200</v>
       </c>
       <c r="E32">
-        <v>18884</v>
+        <v>21782</v>
       </c>
       <c r="F32" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I32">
         <v>3</v>
@@ -1645,7 +1645,7 @@
         <v>200</v>
       </c>
       <c r="E33">
-        <v>14288</v>
+        <v>13230</v>
       </c>
       <c r="F33" t="str">
         <v>OK_MIXTO</v>
@@ -1683,25 +1683,25 @@
         <v>200</v>
       </c>
       <c r="E34">
-        <v>16142</v>
+        <v>14135</v>
       </c>
       <c r="F34" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="str">
-        <v>electricidad</v>
+        <v>pladur_escayola</v>
       </c>
       <c r="K34" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>200</v>
       </c>
       <c r="E35">
-        <v>22223</v>
+        <v>20881</v>
       </c>
       <c r="F35" t="str">
         <v>OK_MIXTO</v>
@@ -1759,19 +1759,19 @@
         <v>200</v>
       </c>
       <c r="E36">
-        <v>18978</v>
+        <v>17604</v>
       </c>
       <c r="F36" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G36">
         <v>7</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J36" t="str">
         <v>electricidad</v>
@@ -1797,7 +1797,7 @@
         <v>200</v>
       </c>
       <c r="E37">
-        <v>12122</v>
+        <v>12649</v>
       </c>
       <c r="F37" t="str">
         <v>OK_MIXTO</v>
@@ -1835,7 +1835,7 @@
         <v>200</v>
       </c>
       <c r="E38">
-        <v>18953</v>
+        <v>18061</v>
       </c>
       <c r="F38" t="str">
         <v>OK_MIXTO</v>
@@ -1844,10 +1844,10 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J38" t="str">
         <v>electricidad</v>
@@ -1873,19 +1873,19 @@
         <v>200</v>
       </c>
       <c r="E39">
-        <v>15463</v>
+        <v>22144</v>
       </c>
       <c r="F39" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J39" t="str">
         <v>electricidad</v>
@@ -1911,19 +1911,19 @@
         <v>200</v>
       </c>
       <c r="E40">
-        <v>13826</v>
+        <v>15651</v>
       </c>
       <c r="F40" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
         <v>3</v>
-      </c>
-      <c r="I40">
-        <v>2</v>
       </c>
       <c r="J40" t="str">
         <v>telecomunicaciones</v>
@@ -1949,16 +1949,16 @@
         <v>200</v>
       </c>
       <c r="E41">
-        <v>9872</v>
+        <v>9192</v>
       </c>
       <c r="F41" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -1987,7 +1987,7 @@
         <v>200</v>
       </c>
       <c r="E42">
-        <v>19563</v>
+        <v>17459</v>
       </c>
       <c r="F42" t="str">
         <v>OK_MIXTO</v>
@@ -2025,19 +2025,19 @@
         <v>200</v>
       </c>
       <c r="E43">
-        <v>13030</v>
+        <v>10398</v>
       </c>
       <c r="F43" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" t="str">
         <v>carpinteria</v>
@@ -2063,16 +2063,16 @@
         <v>200</v>
       </c>
       <c r="E44">
-        <v>16569</v>
+        <v>16206</v>
       </c>
       <c r="F44" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -2101,19 +2101,19 @@
         <v>200</v>
       </c>
       <c r="E45">
-        <v>12555</v>
+        <v>11881</v>
       </c>
       <c r="F45" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H45">
         <v>4</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" t="str">
         <v>carpinteria</v>
@@ -2139,7 +2139,7 @@
         <v>200</v>
       </c>
       <c r="E46">
-        <v>18311</v>
+        <v>13362</v>
       </c>
       <c r="F46" t="str">
         <v>OK_MIXTO</v>
@@ -2154,10 +2154,10 @@
         <v>5</v>
       </c>
       <c r="J46" t="str">
-        <v>suelos_tarimas</v>
+        <v>carpinteria</v>
       </c>
       <c r="K46" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2177,16 +2177,16 @@
         <v>200</v>
       </c>
       <c r="E47">
-        <v>19027</v>
+        <v>14960</v>
       </c>
       <c r="F47" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G47">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I47">
         <v>4</v>
@@ -2215,7 +2215,7 @@
         <v>200</v>
       </c>
       <c r="E48">
-        <v>15847</v>
+        <v>14160</v>
       </c>
       <c r="F48" t="str">
         <v>OK_MIXTO</v>
@@ -2253,19 +2253,19 @@
         <v>200</v>
       </c>
       <c r="E49">
-        <v>13858</v>
+        <v>11738</v>
       </c>
       <c r="F49" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J49" t="str">
         <v>carpinteria</v>
@@ -2291,16 +2291,16 @@
         <v>200</v>
       </c>
       <c r="E50">
-        <v>17821</v>
+        <v>19229</v>
       </c>
       <c r="F50" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50">
         <v>5</v>
@@ -2329,19 +2329,19 @@
         <v>200</v>
       </c>
       <c r="E51">
-        <v>19239</v>
+        <v>22985</v>
       </c>
       <c r="F51" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I51">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J51" t="str">
         <v>carpinteria</v>
@@ -2367,7 +2367,7 @@
         <v>200</v>
       </c>
       <c r="E52">
-        <v>16422</v>
+        <v>14588</v>
       </c>
       <c r="F52" t="str">
         <v>OK_MIXTO</v>
@@ -2376,10 +2376,10 @@
         <v>7</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52" t="str">
         <v>carpinteria</v>
@@ -2405,7 +2405,7 @@
         <v>200</v>
       </c>
       <c r="E53">
-        <v>20386</v>
+        <v>18252</v>
       </c>
       <c r="F53" t="str">
         <v>OK_MIXTO</v>
@@ -2443,19 +2443,19 @@
         <v>200</v>
       </c>
       <c r="E54">
-        <v>17062</v>
+        <v>12746</v>
       </c>
       <c r="F54" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J54" t="str">
         <v>carpinteria</v>
@@ -2481,16 +2481,16 @@
         <v>200</v>
       </c>
       <c r="E55">
-        <v>22926</v>
+        <v>21514</v>
       </c>
       <c r="F55" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I55">
         <v>7</v>
@@ -2519,7 +2519,7 @@
         <v>200</v>
       </c>
       <c r="E56">
-        <v>15162</v>
+        <v>14579</v>
       </c>
       <c r="F56" t="str">
         <v>OK_MIXTO</v>
@@ -2557,16 +2557,16 @@
         <v>200</v>
       </c>
       <c r="E57">
-        <v>12397</v>
+        <v>13659</v>
       </c>
       <c r="F57" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I57">
         <v>3</v>
@@ -2595,19 +2595,19 @@
         <v>200</v>
       </c>
       <c r="E58">
-        <v>13244</v>
+        <v>15684</v>
       </c>
       <c r="F58" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H58">
         <v>4</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58" t="str">
         <v>carpinteria</v>
@@ -2633,19 +2633,19 @@
         <v>200</v>
       </c>
       <c r="E59">
-        <v>19177</v>
+        <v>23976</v>
       </c>
       <c r="F59" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G59">
+        <v>10</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
         <v>6</v>
-      </c>
-      <c r="H59">
-        <v>3</v>
-      </c>
-      <c r="I59">
-        <v>3</v>
       </c>
       <c r="J59" t="str">
         <v>carpinteria</v>
@@ -2671,7 +2671,7 @@
         <v>200</v>
       </c>
       <c r="E60">
-        <v>13551</v>
+        <v>12656</v>
       </c>
       <c r="F60" t="str">
         <v>OK_MIXTO</v>
@@ -2709,19 +2709,19 @@
         <v>200</v>
       </c>
       <c r="E61">
-        <v>16813</v>
+        <v>17554</v>
       </c>
       <c r="F61" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G61">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61" t="str">
         <v>carpinteria</v>
@@ -2747,16 +2747,16 @@
         <v>200</v>
       </c>
       <c r="E62">
-        <v>10926</v>
+        <v>11485</v>
       </c>
       <c r="F62" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>4</v>
@@ -2785,19 +2785,19 @@
         <v>200</v>
       </c>
       <c r="E63">
-        <v>13317</v>
+        <v>13451</v>
       </c>
       <c r="F63" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H63">
         <v>4</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J63" t="str">
         <v>pintura</v>
@@ -2823,25 +2823,25 @@
         <v>200</v>
       </c>
       <c r="E64">
-        <v>18852</v>
+        <v>21606</v>
       </c>
       <c r="F64" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J64" t="str">
-        <v>pintura</v>
+        <v>pladur_escayola</v>
       </c>
       <c r="K64" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -2861,19 +2861,19 @@
         <v>200</v>
       </c>
       <c r="E65">
-        <v>21880</v>
+        <v>24951</v>
       </c>
       <c r="F65" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
       <c r="I65">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J65" t="str">
         <v>impermeabilizacion</v>
@@ -2899,19 +2899,19 @@
         <v>200</v>
       </c>
       <c r="E66">
-        <v>15344</v>
+        <v>10188</v>
       </c>
       <c r="F66" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G66">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H66">
         <v>2</v>
       </c>
       <c r="I66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J66" t="str">
         <v>pintura</v>
@@ -2937,19 +2937,19 @@
         <v>200</v>
       </c>
       <c r="E67">
-        <v>11082</v>
+        <v>12482</v>
       </c>
       <c r="F67" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H67">
         <v>3</v>
       </c>
       <c r="I67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67" t="str">
         <v>pintura</v>
@@ -2975,19 +2975,19 @@
         <v>200</v>
       </c>
       <c r="E68">
-        <v>20687</v>
+        <v>10628</v>
       </c>
       <c r="F68" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H68">
         <v>2</v>
       </c>
       <c r="I68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J68" t="str">
         <v>pintura</v>
@@ -3013,7 +3013,7 @@
         <v>200</v>
       </c>
       <c r="E69">
-        <v>12518</v>
+        <v>11541</v>
       </c>
       <c r="F69" t="str">
         <v>OK_MIXTO</v>
@@ -3022,10 +3022,10 @@
         <v>6</v>
       </c>
       <c r="H69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" t="str">
         <v>pintura</v>
@@ -3051,7 +3051,7 @@
         <v>200</v>
       </c>
       <c r="E70">
-        <v>13826</v>
+        <v>16129</v>
       </c>
       <c r="F70" t="str">
         <v>OK_MIXTO</v>
@@ -3060,10 +3060,10 @@
         <v>6</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70" t="str">
         <v>pintura</v>
@@ -3089,19 +3089,19 @@
         <v>200</v>
       </c>
       <c r="E71">
-        <v>15462</v>
+        <v>16917</v>
       </c>
       <c r="F71" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G71">
         <v>6</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J71" t="str">
         <v>pintura</v>
@@ -3127,7 +3127,7 @@
         <v>200</v>
       </c>
       <c r="E72">
-        <v>13048</v>
+        <v>12815</v>
       </c>
       <c r="F72" t="str">
         <v>OK_MIXTO</v>
@@ -3136,10 +3136,10 @@
         <v>5</v>
       </c>
       <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
         <v>3</v>
-      </c>
-      <c r="I72">
-        <v>2</v>
       </c>
       <c r="J72" t="str">
         <v>fachadas</v>
@@ -3165,7 +3165,7 @@
         <v>200</v>
       </c>
       <c r="E73">
-        <v>16325</v>
+        <v>15627</v>
       </c>
       <c r="F73" t="str">
         <v>OK_MIXTO</v>
@@ -3174,10 +3174,10 @@
         <v>6</v>
       </c>
       <c r="H73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J73" t="str">
         <v>pintura</v>
@@ -3203,7 +3203,7 @@
         <v>200</v>
       </c>
       <c r="E74">
-        <v>16531</v>
+        <v>16298</v>
       </c>
       <c r="F74" t="str">
         <v>OK_MIXTO</v>
@@ -3212,10 +3212,10 @@
         <v>6</v>
       </c>
       <c r="H74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J74" t="str">
         <v>pintura</v>
@@ -3241,19 +3241,19 @@
         <v>200</v>
       </c>
       <c r="E75">
-        <v>16528</v>
+        <v>20117</v>
       </c>
       <c r="F75" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G75">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I75">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J75" t="str">
         <v>albanileria</v>
@@ -3279,7 +3279,7 @@
         <v>200</v>
       </c>
       <c r="E76">
-        <v>14751</v>
+        <v>12903</v>
       </c>
       <c r="F76" t="str">
         <v>OK_MIXTO</v>
@@ -3317,19 +3317,19 @@
         <v>200</v>
       </c>
       <c r="E77">
-        <v>13785</v>
+        <v>8188</v>
       </c>
       <c r="F77" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="str">
         <v>pintura</v>
@@ -3355,7 +3355,7 @@
         <v>200</v>
       </c>
       <c r="E78">
-        <v>13447</v>
+        <v>11875</v>
       </c>
       <c r="F78" t="str">
         <v>OK_MIXTO</v>
@@ -3393,7 +3393,7 @@
         <v>200</v>
       </c>
       <c r="E79">
-        <v>14957</v>
+        <v>12661</v>
       </c>
       <c r="F79" t="str">
         <v>OK_MIXTO</v>
@@ -3431,16 +3431,16 @@
         <v>200</v>
       </c>
       <c r="E80">
-        <v>12762</v>
+        <v>10854</v>
       </c>
       <c r="F80" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G80">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I80">
         <v>4</v>
@@ -3469,19 +3469,19 @@
         <v>200</v>
       </c>
       <c r="E81">
-        <v>10609</v>
+        <v>11615</v>
       </c>
       <c r="F81" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J81" t="str">
         <v>pintura</v>
@@ -3507,7 +3507,7 @@
         <v>200</v>
       </c>
       <c r="E82">
-        <v>16137</v>
+        <v>16698</v>
       </c>
       <c r="F82" t="str">
         <v>OK_MIXTO</v>
@@ -3516,10 +3516,10 @@
         <v>3</v>
       </c>
       <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
         <v>2</v>
-      </c>
-      <c r="I82">
-        <v>1</v>
       </c>
       <c r="J82" t="str">
         <v>albanileria</v>
@@ -3545,19 +3545,19 @@
         <v>200</v>
       </c>
       <c r="E83">
-        <v>14192</v>
+        <v>17040</v>
       </c>
       <c r="F83" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H83">
         <v>3</v>
       </c>
       <c r="I83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J83" t="str">
         <v>albanileria</v>
@@ -3583,7 +3583,7 @@
         <v>200</v>
       </c>
       <c r="E84">
-        <v>13576</v>
+        <v>17332</v>
       </c>
       <c r="F84" t="str">
         <v>OK_MIXTO</v>
@@ -3621,19 +3621,19 @@
         <v>200</v>
       </c>
       <c r="E85">
-        <v>19315</v>
+        <v>18956</v>
       </c>
       <c r="F85" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G85">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H85">
         <v>4</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J85" t="str">
         <v>albanileria</v>
@@ -3659,16 +3659,16 @@
         <v>200</v>
       </c>
       <c r="E86">
-        <v>24057</v>
+        <v>23089</v>
       </c>
       <c r="F86" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G86">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>8</v>
@@ -3697,19 +3697,19 @@
         <v>200</v>
       </c>
       <c r="E87">
-        <v>20472</v>
+        <v>12167</v>
       </c>
       <c r="F87" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G87">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J87" t="str">
         <v>pladur_escayola</v>
@@ -3735,7 +3735,7 @@
         <v>200</v>
       </c>
       <c r="E88">
-        <v>14940</v>
+        <v>13789</v>
       </c>
       <c r="F88" t="str">
         <v>OK_MIXTO</v>
@@ -3773,7 +3773,7 @@
         <v>200</v>
       </c>
       <c r="E89">
-        <v>13204</v>
+        <v>14155</v>
       </c>
       <c r="F89" t="str">
         <v>OK_MIXTO</v>
@@ -3782,10 +3782,10 @@
         <v>6</v>
       </c>
       <c r="H89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J89" t="str">
         <v>albanileria</v>
@@ -3811,7 +3811,7 @@
         <v>200</v>
       </c>
       <c r="E90">
-        <v>21714</v>
+        <v>18637</v>
       </c>
       <c r="F90" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -3849,7 +3849,7 @@
         <v>200</v>
       </c>
       <c r="E91">
-        <v>14943</v>
+        <v>14032</v>
       </c>
       <c r="F91" t="str">
         <v>OK_MIXTO</v>
@@ -3864,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="J91" t="str">
-        <v>albanileria</v>
+        <v>fachadas</v>
       </c>
       <c r="K91" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -3887,19 +3887,19 @@
         <v>200</v>
       </c>
       <c r="E92">
-        <v>19869</v>
+        <v>14178</v>
       </c>
       <c r="F92" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G92">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I92">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J92" t="str">
         <v>albanileria</v>
@@ -3925,7 +3925,7 @@
         <v>200</v>
       </c>
       <c r="E93">
-        <v>17927</v>
+        <v>17512</v>
       </c>
       <c r="F93" t="str">
         <v>OK_MIXTO</v>
@@ -3934,10 +3934,10 @@
         <v>6</v>
       </c>
       <c r="H93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J93" t="str">
         <v>albanileria</v>
@@ -3963,7 +3963,7 @@
         <v>200</v>
       </c>
       <c r="E94">
-        <v>38859</v>
+        <v>41007</v>
       </c>
       <c r="F94" t="str">
         <v>OK_MIXTO</v>
@@ -3972,10 +3972,10 @@
         <v>21</v>
       </c>
       <c r="H94">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I94">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J94" t="str">
         <v>albanileria</v>
@@ -4001,7 +4001,7 @@
         <v>200</v>
       </c>
       <c r="E95">
-        <v>17283</v>
+        <v>17451</v>
       </c>
       <c r="F95" t="str">
         <v>OK_MIXTO</v>
@@ -4010,10 +4010,10 @@
         <v>6</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J95" t="str">
         <v>impermeabilizacion</v>
@@ -4039,19 +4039,19 @@
         <v>200</v>
       </c>
       <c r="E96">
-        <v>18639</v>
+        <v>24457</v>
       </c>
       <c r="F96" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G96">
+        <v>13</v>
+      </c>
+      <c r="H96">
+        <v>5</v>
+      </c>
+      <c r="I96">
         <v>8</v>
-      </c>
-      <c r="H96">
-        <v>3</v>
-      </c>
-      <c r="I96">
-        <v>5</v>
       </c>
       <c r="J96" t="str">
         <v>suelos_alicatados</v>
@@ -4077,16 +4077,16 @@
         <v>200</v>
       </c>
       <c r="E97">
-        <v>22668</v>
+        <v>21273</v>
       </c>
       <c r="F97" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I97">
         <v>4</v>
@@ -4115,7 +4115,7 @@
         <v>200</v>
       </c>
       <c r="E98">
-        <v>13097</v>
+        <v>16906</v>
       </c>
       <c r="F98" t="str">
         <v>OK_MIXTO</v>
@@ -4153,19 +4153,19 @@
         <v>200</v>
       </c>
       <c r="E99">
-        <v>29537</v>
+        <v>28181</v>
       </c>
       <c r="F99" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G99">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I99">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J99" t="str">
         <v>reforma_integral</v>
@@ -4191,19 +4191,19 @@
         <v>200</v>
       </c>
       <c r="E100">
-        <v>16770</v>
+        <v>19754</v>
       </c>
       <c r="F100" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G100">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H100">
         <v>4</v>
       </c>
       <c r="I100">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J100" t="str">
         <v>suelos_alicatados</v>
@@ -4229,16 +4229,16 @@
         <v>200</v>
       </c>
       <c r="E101">
-        <v>20054</v>
+        <v>19061</v>
       </c>
       <c r="F101" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G101">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H101">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I101">
         <v>5</v>
@@ -4267,19 +4267,19 @@
         <v>200</v>
       </c>
       <c r="E102">
-        <v>18479</v>
+        <v>17048</v>
       </c>
       <c r="F102" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G102">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H102">
         <v>1</v>
       </c>
       <c r="I102">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J102" t="str">
         <v>climatizacion</v>
@@ -4305,25 +4305,25 @@
         <v>200</v>
       </c>
       <c r="E103">
-        <v>36496</v>
+        <v>32445</v>
       </c>
       <c r="F103" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G103">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I103">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J103" t="str">
-        <v>climatizacion</v>
+        <v>reforma_integral</v>
       </c>
       <c r="K103" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -4343,7 +4343,7 @@
         <v>200</v>
       </c>
       <c r="E104">
-        <v>32055</v>
+        <v>23865</v>
       </c>
       <c r="F104" t="str">
         <v>OK_MIXTO</v>
@@ -4381,7 +4381,7 @@
         <v>200</v>
       </c>
       <c r="E105">
-        <v>17314</v>
+        <v>12496</v>
       </c>
       <c r="F105" t="str">
         <v>OK_MIXTO</v>
@@ -4390,10 +4390,10 @@
         <v>6</v>
       </c>
       <c r="H105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J105" t="str">
         <v>climatizacion</v>
@@ -4419,19 +4419,19 @@
         <v>200</v>
       </c>
       <c r="E106">
-        <v>29633</v>
+        <v>21025</v>
       </c>
       <c r="F106" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G106">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H106">
         <v>2</v>
       </c>
       <c r="I106">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J106" t="str">
         <v>climatizacion</v>
@@ -4457,25 +4457,25 @@
         <v>200</v>
       </c>
       <c r="E107">
-        <v>25810</v>
+        <v>28030</v>
       </c>
       <c r="F107" t="str">
-        <v>VACIO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>climatizacion</v>
       </c>
       <c r="K107" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -4495,19 +4495,19 @@
         <v>200</v>
       </c>
       <c r="E108">
-        <v>19187</v>
+        <v>21526</v>
       </c>
       <c r="F108" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G108">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H108">
         <v>2</v>
       </c>
       <c r="I108">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J108" t="str">
         <v>climatizacion</v>
@@ -4533,19 +4533,19 @@
         <v>200</v>
       </c>
       <c r="E109">
-        <v>15198</v>
+        <v>17571</v>
       </c>
       <c r="F109" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G109">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J109" t="str">
         <v>climatizacion</v>
@@ -4571,19 +4571,19 @@
         <v>200</v>
       </c>
       <c r="E110">
-        <v>11777</v>
+        <v>11566</v>
       </c>
       <c r="F110" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G110">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H110">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" t="str">
         <v>climatizacion</v>
@@ -4609,25 +4609,25 @@
         <v>200</v>
       </c>
       <c r="E111">
-        <v>23854</v>
+        <v>21593</v>
       </c>
       <c r="F111" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G111">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H111">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I111">
         <v>5</v>
       </c>
       <c r="J111" t="str">
-        <v>electricidad</v>
+        <v>climatizacion</v>
       </c>
       <c r="K111" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -4647,19 +4647,19 @@
         <v>200</v>
       </c>
       <c r="E112">
-        <v>25662</v>
+        <v>26717</v>
       </c>
       <c r="F112" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G112">
         <v>12</v>
       </c>
       <c r="H112">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I112">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J112" t="str">
         <v>climatizacion</v>
@@ -4685,7 +4685,7 @@
         <v>200</v>
       </c>
       <c r="E113">
-        <v>11776</v>
+        <v>12291</v>
       </c>
       <c r="F113" t="str">
         <v>OK_MIXTO</v>
@@ -4723,19 +4723,19 @@
         <v>200</v>
       </c>
       <c r="E114">
-        <v>26105</v>
+        <v>20835</v>
       </c>
       <c r="F114" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G114">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H114">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I114">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J114" t="str">
         <v>climatizacion</v>
@@ -4761,16 +4761,16 @@
         <v>200</v>
       </c>
       <c r="E115">
-        <v>17940</v>
+        <v>11734</v>
       </c>
       <c r="F115" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G115">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H115">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I115">
         <v>3</v>
@@ -4799,19 +4799,19 @@
         <v>200</v>
       </c>
       <c r="E116">
-        <v>15086</v>
+        <v>21832</v>
       </c>
       <c r="F116" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G116">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H116">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J116" t="str">
         <v>climatizacion</v>
@@ -4837,19 +4837,19 @@
         <v>200</v>
       </c>
       <c r="E117">
-        <v>17916</v>
+        <v>10949</v>
       </c>
       <c r="F117" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G117">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H117">
         <v>2</v>
       </c>
       <c r="I117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J117" t="str">
         <v>mecanica_especializada</v>
@@ -4875,19 +4875,19 @@
         <v>200</v>
       </c>
       <c r="E118">
-        <v>12611</v>
+        <v>16571</v>
       </c>
       <c r="F118" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J118" t="str">
         <v>electricidad</v>
@@ -4913,7 +4913,7 @@
         <v>200</v>
       </c>
       <c r="E119">
-        <v>20678</v>
+        <v>20546</v>
       </c>
       <c r="F119" t="str">
         <v>OK_MIXTO</v>
@@ -4922,10 +4922,10 @@
         <v>7</v>
       </c>
       <c r="H119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I119">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J119" t="str">
         <v>climatizacion</v>
@@ -4951,19 +4951,19 @@
         <v>200</v>
       </c>
       <c r="E120">
-        <v>30689</v>
+        <v>24791</v>
       </c>
       <c r="F120" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G120">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H120">
         <v>6</v>
       </c>
       <c r="I120">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J120" t="str">
         <v>climatizacion</v>
@@ -4989,19 +4989,19 @@
         <v>200</v>
       </c>
       <c r="E121">
-        <v>22657</v>
+        <v>29417</v>
       </c>
       <c r="F121" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G121">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H121">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I121">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J121" t="str">
         <v>fontaneria</v>
@@ -5027,19 +5027,19 @@
         <v>200</v>
       </c>
       <c r="E122">
-        <v>13222</v>
+        <v>15172</v>
       </c>
       <c r="F122" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G122">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J122" t="str">
         <v>tejados_cubiertas</v>
@@ -5065,19 +5065,19 @@
         <v>200</v>
       </c>
       <c r="E123">
-        <v>52862</v>
+        <v>21507</v>
       </c>
       <c r="F123" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G123">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H123">
         <v>0</v>
       </c>
       <c r="I123">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J123" t="str">
         <v>impermeabilizacion</v>
@@ -5103,19 +5103,19 @@
         <v>200</v>
       </c>
       <c r="E124">
-        <v>11492</v>
+        <v>10752</v>
       </c>
       <c r="F124" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G124">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
       <c r="I124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J124" t="str">
         <v>fachadas</v>
@@ -5141,7 +5141,7 @@
         <v>200</v>
       </c>
       <c r="E125">
-        <v>13845</v>
+        <v>12444</v>
       </c>
       <c r="F125" t="str">
         <v>OK_MIXTO</v>
@@ -5179,7 +5179,7 @@
         <v>200</v>
       </c>
       <c r="E126">
-        <v>15502</v>
+        <v>12826</v>
       </c>
       <c r="F126" t="str">
         <v>OK_MIXTO</v>
@@ -5217,7 +5217,7 @@
         <v>200</v>
       </c>
       <c r="E127">
-        <v>24497</v>
+        <v>17230</v>
       </c>
       <c r="F127" t="str">
         <v>OK_MIXTO</v>
@@ -5226,10 +5226,10 @@
         <v>8</v>
       </c>
       <c r="H127">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I127">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J127" t="str">
         <v>tejados_cubiertas</v>
@@ -5255,19 +5255,19 @@
         <v>200</v>
       </c>
       <c r="E128">
-        <v>17532</v>
+        <v>14873</v>
       </c>
       <c r="F128" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G128">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H128">
         <v>2</v>
       </c>
       <c r="I128">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J128" t="str">
         <v>tejados_cubiertas</v>
@@ -5293,16 +5293,16 @@
         <v>200</v>
       </c>
       <c r="E129">
-        <v>23371</v>
+        <v>17854</v>
       </c>
       <c r="F129" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G129">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I129">
         <v>4</v>
@@ -5331,19 +5331,19 @@
         <v>200</v>
       </c>
       <c r="E130">
-        <v>21115</v>
+        <v>18609</v>
       </c>
       <c r="F130" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G130">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H130">
         <v>5</v>
       </c>
       <c r="I130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J130" t="str">
         <v>tejados_cubiertas</v>
@@ -5369,16 +5369,16 @@
         <v>200</v>
       </c>
       <c r="E131">
-        <v>17102</v>
+        <v>15127</v>
       </c>
       <c r="F131" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G131">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H131">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I131">
         <v>4</v>
@@ -5407,16 +5407,16 @@
         <v>200</v>
       </c>
       <c r="E132">
-        <v>19737</v>
+        <v>18983</v>
       </c>
       <c r="F132" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G132">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H132">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I132">
         <v>3</v>
@@ -5445,19 +5445,19 @@
         <v>200</v>
       </c>
       <c r="E133">
-        <v>24366</v>
+        <v>25448</v>
       </c>
       <c r="F133" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H133">
         <v>3</v>
       </c>
       <c r="I133">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J133" t="str">
         <v>energia_solar</v>
@@ -5483,19 +5483,19 @@
         <v>200</v>
       </c>
       <c r="E134">
-        <v>12428</v>
+        <v>14043</v>
       </c>
       <c r="F134" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G134">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H134">
         <v>2</v>
       </c>
       <c r="I134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J134" t="str">
         <v>impermeabilizacion</v>
@@ -5521,19 +5521,19 @@
         <v>200</v>
       </c>
       <c r="E135">
-        <v>19653</v>
+        <v>19546</v>
       </c>
       <c r="F135" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G135">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I135">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J135" t="str">
         <v>impermeabilizacion</v>
@@ -5559,19 +5559,19 @@
         <v>200</v>
       </c>
       <c r="E136">
-        <v>20370</v>
+        <v>22786</v>
       </c>
       <c r="F136" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G136">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H136">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I136">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J136" t="str">
         <v>tejados_cubiertas</v>
@@ -5597,19 +5597,19 @@
         <v>200</v>
       </c>
       <c r="E137">
-        <v>32690</v>
+        <v>35937</v>
       </c>
       <c r="F137" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G137">
+        <v>21</v>
+      </c>
+      <c r="H137">
+        <v>9</v>
+      </c>
+      <c r="I137">
         <v>12</v>
-      </c>
-      <c r="H137">
-        <v>6</v>
-      </c>
-      <c r="I137">
-        <v>6</v>
       </c>
       <c r="J137" t="str">
         <v>tejados_cubiertas</v>
@@ -5635,19 +5635,19 @@
         <v>200</v>
       </c>
       <c r="E138">
-        <v>13754</v>
+        <v>13877</v>
       </c>
       <c r="F138" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H138">
         <v>2</v>
       </c>
       <c r="I138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J138" t="str">
         <v>tejados_cubiertas</v>
@@ -5673,19 +5673,19 @@
         <v>200</v>
       </c>
       <c r="E139">
-        <v>17194</v>
+        <v>12948</v>
       </c>
       <c r="F139" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G139">
         <v>4</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J139" t="str">
         <v>tejados_cubiertas</v>
@@ -5711,7 +5711,7 @@
         <v>200</v>
       </c>
       <c r="E140">
-        <v>17278</v>
+        <v>17354</v>
       </c>
       <c r="F140" t="str">
         <v>OK_MIXTO</v>
@@ -5749,19 +5749,19 @@
         <v>200</v>
       </c>
       <c r="E141">
-        <v>15736</v>
+        <v>13235</v>
       </c>
       <c r="F141" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G141">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H141">
         <v>3</v>
       </c>
       <c r="I141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J141" t="str">
         <v>tejados_cubiertas</v>
@@ -5787,19 +5787,19 @@
         <v>200</v>
       </c>
       <c r="E142">
-        <v>18818</v>
+        <v>22877</v>
       </c>
       <c r="F142" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G142">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H142">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I142">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J142" t="str">
         <v>pladur_escayola</v>
@@ -5825,19 +5825,19 @@
         <v>200</v>
       </c>
       <c r="E143">
-        <v>24037</v>
+        <v>21060</v>
       </c>
       <c r="F143" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G143">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H143">
         <v>3</v>
       </c>
       <c r="I143">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J143" t="str">
         <v>pladur_escayola</v>
@@ -5863,19 +5863,19 @@
         <v>200</v>
       </c>
       <c r="E144">
-        <v>23628</v>
+        <v>19121</v>
       </c>
       <c r="F144" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G144">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I144">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J144" t="str">
         <v>pladur_escayola</v>
@@ -5901,16 +5901,16 @@
         <v>200</v>
       </c>
       <c r="E145">
-        <v>22295</v>
+        <v>19800</v>
       </c>
       <c r="F145" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G145">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H145">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I145">
         <v>7</v>
@@ -5939,7 +5939,7 @@
         <v>200</v>
       </c>
       <c r="E146">
-        <v>10741</v>
+        <v>9585</v>
       </c>
       <c r="F146" t="str">
         <v>OK_MIXTO</v>
@@ -5977,19 +5977,19 @@
         <v>200</v>
       </c>
       <c r="E147">
-        <v>17129</v>
+        <v>24509</v>
       </c>
       <c r="F147" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G147">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H147">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J147" t="str">
         <v>pladur_escayola</v>
@@ -6015,7 +6015,7 @@
         <v>200</v>
       </c>
       <c r="E148">
-        <v>23846</v>
+        <v>20197</v>
       </c>
       <c r="F148" t="str">
         <v>OK_MIXTO</v>
@@ -6024,16 +6024,16 @@
         <v>10</v>
       </c>
       <c r="H148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I148">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J148" t="str">
-        <v>pladur_escayola</v>
+        <v>contra_incendios</v>
       </c>
       <c r="K148" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L148" t="str">
         <v/>
@@ -6053,7 +6053,7 @@
         <v>200</v>
       </c>
       <c r="E149">
-        <v>19442</v>
+        <v>13785</v>
       </c>
       <c r="F149" t="str">
         <v>OK_MIXTO</v>
@@ -6091,19 +6091,19 @@
         <v>200</v>
       </c>
       <c r="E150">
-        <v>15790</v>
+        <v>19436</v>
       </c>
       <c r="F150" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G150">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H150">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I150">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J150" t="str">
         <v>pladur_escayola</v>
@@ -6129,19 +6129,19 @@
         <v>200</v>
       </c>
       <c r="E151">
-        <v>18722</v>
+        <v>16253</v>
       </c>
       <c r="F151" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G151">
         <v>7</v>
       </c>
       <c r="H151">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I151">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J151" t="str">
         <v>pladur_escayola</v>
@@ -6167,25 +6167,25 @@
         <v>200</v>
       </c>
       <c r="E152">
-        <v>23578</v>
+        <v>20305</v>
       </c>
       <c r="F152" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G152">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H152">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I152">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J152" t="str">
-        <v>albanileria</v>
+        <v>pladur_escayola</v>
       </c>
       <c r="K152" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L152" t="str">
         <v/>
@@ -6205,19 +6205,19 @@
         <v>200</v>
       </c>
       <c r="E153">
-        <v>21593</v>
+        <v>24370</v>
       </c>
       <c r="F153" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G153">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H153">
         <v>3</v>
       </c>
       <c r="I153">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J153" t="str">
         <v>pladur_escayola</v>
@@ -6243,7 +6243,7 @@
         <v>200</v>
       </c>
       <c r="E154">
-        <v>19552</v>
+        <v>11185</v>
       </c>
       <c r="F154" t="str">
         <v>OK_MIXTO</v>
@@ -6281,7 +6281,7 @@
         <v>200</v>
       </c>
       <c r="E155">
-        <v>18928</v>
+        <v>18049</v>
       </c>
       <c r="F155" t="str">
         <v>OK_MIXTO</v>
@@ -6319,7 +6319,7 @@
         <v>200</v>
       </c>
       <c r="E156">
-        <v>13191</v>
+        <v>15151</v>
       </c>
       <c r="F156" t="str">
         <v>OK_MIXTO</v>
@@ -6357,19 +6357,19 @@
         <v>200</v>
       </c>
       <c r="E157">
-        <v>19931</v>
+        <v>20832</v>
       </c>
       <c r="F157" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G157">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H157">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I157">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J157" t="str">
         <v>pladur_escayola</v>
@@ -6395,7 +6395,7 @@
         <v>200</v>
       </c>
       <c r="E158">
-        <v>20818</v>
+        <v>16207</v>
       </c>
       <c r="F158" t="str">
         <v>OK_MIXTO</v>
@@ -6433,16 +6433,16 @@
         <v>200</v>
       </c>
       <c r="E159">
-        <v>20816</v>
+        <v>13384</v>
       </c>
       <c r="F159" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G159">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I159">
         <v>4</v>
@@ -6471,7 +6471,7 @@
         <v>200</v>
       </c>
       <c r="E160">
-        <v>15752</v>
+        <v>13607</v>
       </c>
       <c r="F160" t="str">
         <v>OK_MIXTO</v>
@@ -6509,19 +6509,19 @@
         <v>200</v>
       </c>
       <c r="E161">
-        <v>19204</v>
+        <v>20119</v>
       </c>
       <c r="F161" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G161">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H161">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I161">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J161" t="str">
         <v>pladur_escayola</v>
@@ -6547,7 +6547,7 @@
         <v>200</v>
       </c>
       <c r="E162">
-        <v>18081</v>
+        <v>19250</v>
       </c>
       <c r="F162" t="str">
         <v>OK_MIXTO</v>
@@ -6585,7 +6585,7 @@
         <v>200</v>
       </c>
       <c r="E163">
-        <v>15750</v>
+        <v>14218</v>
       </c>
       <c r="F163" t="str">
         <v>OK_MIXTO</v>
@@ -6594,10 +6594,10 @@
         <v>6</v>
       </c>
       <c r="H163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I163">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J163" t="str">
         <v>suelos_tarimas</v>
@@ -6623,19 +6623,19 @@
         <v>200</v>
       </c>
       <c r="E164">
-        <v>11594</v>
+        <v>12589</v>
       </c>
       <c r="F164" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G164">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H164">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I164">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J164" t="str">
         <v>albanileria</v>
@@ -6661,19 +6661,19 @@
         <v>200</v>
       </c>
       <c r="E165">
-        <v>12033</v>
+        <v>15205</v>
       </c>
       <c r="F165" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G165">
+        <v>8</v>
+      </c>
+      <c r="H165">
         <v>5</v>
       </c>
-      <c r="H165">
-        <v>4</v>
-      </c>
       <c r="I165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J165" t="str">
         <v>suelos_alicatados</v>
@@ -6699,19 +6699,19 @@
         <v>200</v>
       </c>
       <c r="E166">
-        <v>20333</v>
+        <v>18421</v>
       </c>
       <c r="F166" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G166">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H166">
         <v>2</v>
       </c>
       <c r="I166">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J166" t="str">
         <v>suelos_tarimas</v>
@@ -6737,16 +6737,16 @@
         <v>200</v>
       </c>
       <c r="E167">
-        <v>16046</v>
+        <v>16479</v>
       </c>
       <c r="F167" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G167">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H167">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I167">
         <v>4</v>
@@ -6775,19 +6775,19 @@
         <v>200</v>
       </c>
       <c r="E168">
-        <v>24088</v>
+        <v>20522</v>
       </c>
       <c r="F168" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G168">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H168">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I168">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J168" t="str">
         <v>impermeabilizacion</v>
@@ -6813,16 +6813,16 @@
         <v>200</v>
       </c>
       <c r="E169">
-        <v>13436</v>
+        <v>13472</v>
       </c>
       <c r="F169" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G169">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I169">
         <v>4</v>
@@ -6851,7 +6851,7 @@
         <v>200</v>
       </c>
       <c r="E170">
-        <v>11919</v>
+        <v>13327</v>
       </c>
       <c r="F170" t="str">
         <v>OK_MIXTO</v>
@@ -6889,7 +6889,7 @@
         <v>200</v>
       </c>
       <c r="E171">
-        <v>22838</v>
+        <v>16208</v>
       </c>
       <c r="F171" t="str">
         <v>OK_MIXTO</v>
@@ -6898,10 +6898,10 @@
         <v>8</v>
       </c>
       <c r="H171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J171" t="str">
         <v>electricidad</v>
@@ -6927,7 +6927,7 @@
         <v>200</v>
       </c>
       <c r="E172">
-        <v>19269</v>
+        <v>14396</v>
       </c>
       <c r="F172" t="str">
         <v>OK_MIXTO</v>
@@ -6936,10 +6936,10 @@
         <v>7</v>
       </c>
       <c r="H172">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I172">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J172" t="str">
         <v>suelos_alicatados</v>
@@ -6965,19 +6965,19 @@
         <v>200</v>
       </c>
       <c r="E173">
-        <v>23959</v>
+        <v>19473</v>
       </c>
       <c r="F173" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G173">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H173">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I173">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J173" t="str">
         <v>suelos_alicatados</v>
@@ -7003,25 +7003,25 @@
         <v>200</v>
       </c>
       <c r="E174">
-        <v>22118</v>
+        <v>25540</v>
       </c>
       <c r="F174" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G174">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H174">
         <v>4</v>
       </c>
       <c r="I174">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J174" t="str">
-        <v>albanileria</v>
+        <v>suelos_alicatados</v>
       </c>
       <c r="K174" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L174" t="str">
         <v/>
@@ -7041,19 +7041,19 @@
         <v>200</v>
       </c>
       <c r="E175">
-        <v>14374</v>
+        <v>21480</v>
       </c>
       <c r="F175" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G175">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H175">
         <v>4</v>
       </c>
       <c r="I175">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J175" t="str">
         <v>suelos_alicatados</v>
@@ -7079,7 +7079,7 @@
         <v>200</v>
       </c>
       <c r="E176">
-        <v>20264</v>
+        <v>18229</v>
       </c>
       <c r="F176" t="str">
         <v>OK_MIXTO</v>
@@ -7088,16 +7088,16 @@
         <v>6</v>
       </c>
       <c r="H176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I176">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J176" t="str">
-        <v>suelos_alicatados</v>
+        <v>carpinteria</v>
       </c>
       <c r="K176" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L176" t="str">
         <v/>
@@ -7117,19 +7117,19 @@
         <v>200</v>
       </c>
       <c r="E177">
-        <v>22560</v>
+        <v>19885</v>
       </c>
       <c r="F177" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G177">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H177">
         <v>0</v>
       </c>
       <c r="I177">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J177" t="str">
         <v>suelos_alicatados</v>
@@ -7155,19 +7155,19 @@
         <v>200</v>
       </c>
       <c r="E178">
-        <v>25793</v>
+        <v>27083</v>
       </c>
       <c r="F178" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G178">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J178" t="str">
         <v>suelos_alicatados</v>
@@ -7193,7 +7193,7 @@
         <v>200</v>
       </c>
       <c r="E179">
-        <v>12523</v>
+        <v>13209</v>
       </c>
       <c r="F179" t="str">
         <v>OK_MIXTO</v>
@@ -7231,16 +7231,16 @@
         <v>200</v>
       </c>
       <c r="E180">
-        <v>15590</v>
+        <v>13291</v>
       </c>
       <c r="F180" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G180">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I180">
         <v>4</v>
@@ -7269,16 +7269,16 @@
         <v>200</v>
       </c>
       <c r="E181">
-        <v>23232</v>
+        <v>17694</v>
       </c>
       <c r="F181" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G181">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H181">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I181">
         <v>5</v>
@@ -7307,19 +7307,19 @@
         <v>200</v>
       </c>
       <c r="E182">
-        <v>9936</v>
+        <v>9645</v>
       </c>
       <c r="F182" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H182">
         <v>2</v>
       </c>
       <c r="I182">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J182" t="str">
         <v>cerrajeria</v>
@@ -7345,7 +7345,7 @@
         <v>200</v>
       </c>
       <c r="E183">
-        <v>14786</v>
+        <v>14876</v>
       </c>
       <c r="F183" t="str">
         <v>OK_MIXTO</v>
@@ -7383,19 +7383,19 @@
         <v>200</v>
       </c>
       <c r="E184">
-        <v>10995</v>
+        <v>10591</v>
       </c>
       <c r="F184" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G184">
         <v>3</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J184" t="str">
         <v>cerrajeria</v>
@@ -7421,16 +7421,16 @@
         <v>200</v>
       </c>
       <c r="E185">
-        <v>14169</v>
+        <v>11897</v>
       </c>
       <c r="F185" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G185">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H185">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I185">
         <v>2</v>
@@ -7459,7 +7459,7 @@
         <v>200</v>
       </c>
       <c r="E186">
-        <v>17817</v>
+        <v>13553</v>
       </c>
       <c r="F186" t="str">
         <v>OK_MIXTO</v>
@@ -7497,19 +7497,19 @@
         <v>200</v>
       </c>
       <c r="E187">
-        <v>9715</v>
+        <v>11595</v>
       </c>
       <c r="F187" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G187">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J187" t="str">
         <v>cerrajeria</v>
@@ -7535,19 +7535,19 @@
         <v>200</v>
       </c>
       <c r="E188">
-        <v>10894</v>
+        <v>12098</v>
       </c>
       <c r="F188" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G188">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J188" t="str">
         <v>cerrajeria</v>
@@ -7573,19 +7573,19 @@
         <v>200</v>
       </c>
       <c r="E189">
-        <v>14273</v>
+        <v>10614</v>
       </c>
       <c r="F189" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G189">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H189">
         <v>2</v>
       </c>
       <c r="I189">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J189" t="str">
         <v>cerrajeria</v>
@@ -7611,19 +7611,19 @@
         <v>200</v>
       </c>
       <c r="E190">
-        <v>17145</v>
+        <v>16044</v>
       </c>
       <c r="F190" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G190">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H190">
         <v>5</v>
       </c>
       <c r="I190">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J190" t="str">
         <v>electricidad</v>
@@ -7649,7 +7649,7 @@
         <v>200</v>
       </c>
       <c r="E191">
-        <v>11445</v>
+        <v>10036</v>
       </c>
       <c r="F191" t="str">
         <v>OK_MIXTO</v>
@@ -7658,10 +7658,10 @@
         <v>5</v>
       </c>
       <c r="H191">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J191" t="str">
         <v>cerrajeria</v>
@@ -7687,19 +7687,19 @@
         <v>200</v>
       </c>
       <c r="E192">
-        <v>16285</v>
+        <v>14277</v>
       </c>
       <c r="F192" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G192">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H192">
         <v>2</v>
       </c>
       <c r="I192">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J192" t="str">
         <v>cristaleria</v>
@@ -7725,19 +7725,19 @@
         <v>200</v>
       </c>
       <c r="E193">
-        <v>8802</v>
+        <v>8680</v>
       </c>
       <c r="F193" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G193">
+        <v>4</v>
+      </c>
+      <c r="H193">
         <v>2</v>
       </c>
-      <c r="H193">
-        <v>1</v>
-      </c>
       <c r="I193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J193" t="str">
         <v>cerrajeria</v>
@@ -7763,7 +7763,7 @@
         <v>200</v>
       </c>
       <c r="E194">
-        <v>19671</v>
+        <v>13909</v>
       </c>
       <c r="F194" t="str">
         <v>OK_MIXTO</v>
@@ -7801,7 +7801,7 @@
         <v>200</v>
       </c>
       <c r="E195">
-        <v>20460</v>
+        <v>18996</v>
       </c>
       <c r="F195" t="str">
         <v>OK_MIXTO</v>
@@ -7810,10 +7810,10 @@
         <v>7</v>
       </c>
       <c r="H195">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J195" t="str">
         <v>carpinteria</v>
@@ -7839,16 +7839,16 @@
         <v>200</v>
       </c>
       <c r="E196">
-        <v>22997</v>
+        <v>24953</v>
       </c>
       <c r="F196" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G196">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H196">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I196">
         <v>6</v>
@@ -7877,19 +7877,19 @@
         <v>200</v>
       </c>
       <c r="E197">
-        <v>12792</v>
+        <v>13829</v>
       </c>
       <c r="F197" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J197" t="str">
         <v>cerrajeria</v>
@@ -7915,7 +7915,7 @@
         <v>200</v>
       </c>
       <c r="E198">
-        <v>16443</v>
+        <v>13360</v>
       </c>
       <c r="F198" t="str">
         <v>OK_MIXTO</v>
@@ -7953,7 +7953,7 @@
         <v>200</v>
       </c>
       <c r="E199">
-        <v>16130</v>
+        <v>9245</v>
       </c>
       <c r="F199" t="str">
         <v>OK_MIXTO</v>
@@ -7991,19 +7991,19 @@
         <v>200</v>
       </c>
       <c r="E200">
-        <v>27132</v>
+        <v>27994</v>
       </c>
       <c r="F200" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G200">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H200">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J200" t="str">
         <v>cerrajeria</v>
@@ -8029,19 +8029,19 @@
         <v>200</v>
       </c>
       <c r="E201">
-        <v>8599</v>
+        <v>7900</v>
       </c>
       <c r="F201" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G201">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H201">
         <v>2</v>
       </c>
       <c r="I201">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J201" t="str">
         <v>cerrajeria</v>
@@ -8067,19 +8067,19 @@
         <v>200</v>
       </c>
       <c r="E202">
-        <v>12181</v>
+        <v>9374</v>
       </c>
       <c r="F202" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G202">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H202">
         <v>3</v>
       </c>
       <c r="I202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J202" t="str">
         <v>jardineria</v>
@@ -8105,19 +8105,19 @@
         <v>200</v>
       </c>
       <c r="E203">
-        <v>20576</v>
+        <v>18025</v>
       </c>
       <c r="F203" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G203">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I203">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J203" t="str">
         <v>jardineria</v>
@@ -8143,7 +8143,7 @@
         <v>200</v>
       </c>
       <c r="E204">
-        <v>14841</v>
+        <v>13893</v>
       </c>
       <c r="F204" t="str">
         <v>OK_MIXTO</v>
@@ -8181,19 +8181,19 @@
         <v>200</v>
       </c>
       <c r="E205">
-        <v>11363</v>
+        <v>11379</v>
       </c>
       <c r="F205" t="str">
-        <v>OK_CATALOGO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G205">
         <v>4</v>
       </c>
       <c r="H205">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" t="str">
         <v>mantenimiento_general</v>
@@ -8219,7 +8219,7 @@
         <v>200</v>
       </c>
       <c r="E206">
-        <v>13321</v>
+        <v>16224</v>
       </c>
       <c r="F206" t="str">
         <v>OK_MIXTO</v>
@@ -8257,7 +8257,7 @@
         <v>200</v>
       </c>
       <c r="E207">
-        <v>14019</v>
+        <v>11903</v>
       </c>
       <c r="F207" t="str">
         <v>OK_MIXTO</v>
@@ -8295,16 +8295,16 @@
         <v>200</v>
       </c>
       <c r="E208">
-        <v>18566</v>
+        <v>13463</v>
       </c>
       <c r="F208" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G208">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H208">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I208">
         <v>3</v>
@@ -8333,16 +8333,16 @@
         <v>200</v>
       </c>
       <c r="E209">
-        <v>14544</v>
+        <v>11995</v>
       </c>
       <c r="F209" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G209">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I209">
         <v>4</v>
@@ -8371,7 +8371,7 @@
         <v>200</v>
       </c>
       <c r="E210">
-        <v>24584</v>
+        <v>19612</v>
       </c>
       <c r="F210" t="str">
         <v>OK_MIXTO</v>
@@ -8409,7 +8409,7 @@
         <v>200</v>
       </c>
       <c r="E211">
-        <v>20114</v>
+        <v>19320</v>
       </c>
       <c r="F211" t="str">
         <v>OK_MIXTO</v>
@@ -8418,10 +8418,10 @@
         <v>8</v>
       </c>
       <c r="H211">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J211" t="str">
         <v>jardineria</v>
@@ -8447,7 +8447,7 @@
         <v>200</v>
       </c>
       <c r="E212">
-        <v>22621</v>
+        <v>19653</v>
       </c>
       <c r="F212" t="str">
         <v>OK_MIXTO</v>
@@ -8485,7 +8485,7 @@
         <v>200</v>
       </c>
       <c r="E213">
-        <v>18214</v>
+        <v>15894</v>
       </c>
       <c r="F213" t="str">
         <v>OK_MIXTO</v>
@@ -8494,10 +8494,10 @@
         <v>6</v>
       </c>
       <c r="H213">
+        <v>4</v>
+      </c>
+      <c r="I213">
         <v>2</v>
-      </c>
-      <c r="I213">
-        <v>4</v>
       </c>
       <c r="J213" t="str">
         <v>jardineria</v>
@@ -8523,19 +8523,19 @@
         <v>200</v>
       </c>
       <c r="E214">
-        <v>15552</v>
+        <v>12229</v>
       </c>
       <c r="F214" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G214">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H214">
         <v>4</v>
       </c>
       <c r="I214">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J214" t="str">
         <v>carpinteria</v>
@@ -8561,7 +8561,7 @@
         <v>200</v>
       </c>
       <c r="E215">
-        <v>9820</v>
+        <v>11301</v>
       </c>
       <c r="F215" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -8599,16 +8599,16 @@
         <v>200</v>
       </c>
       <c r="E216">
-        <v>13828</v>
+        <v>11799</v>
       </c>
       <c r="F216" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G216">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I216">
         <v>2</v>
@@ -8637,7 +8637,7 @@
         <v>200</v>
       </c>
       <c r="E217">
-        <v>16982</v>
+        <v>17963</v>
       </c>
       <c r="F217" t="str">
         <v>OK_MIXTO</v>
@@ -8675,22 +8675,22 @@
         <v>200</v>
       </c>
       <c r="E218">
-        <v>20197</v>
+        <v>22283</v>
       </c>
       <c r="F218" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G218">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H218">
         <v>5</v>
       </c>
       <c r="I218">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J218" t="str">
-        <v>electricidad</v>
+        <v>energia_solar</v>
       </c>
       <c r="K218" t="str">
         <v>NO</v>
@@ -8713,16 +8713,16 @@
         <v>200</v>
       </c>
       <c r="E219">
-        <v>23543</v>
+        <v>27072</v>
       </c>
       <c r="F219" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G219">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H219">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I219">
         <v>6</v>
@@ -8751,7 +8751,7 @@
         <v>200</v>
       </c>
       <c r="E220">
-        <v>12383</v>
+        <v>14526</v>
       </c>
       <c r="F220" t="str">
         <v>OK_MIXTO</v>
@@ -8760,10 +8760,10 @@
         <v>6</v>
       </c>
       <c r="H220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J220" t="str">
         <v>jardineria</v>
@@ -8789,19 +8789,19 @@
         <v>200</v>
       </c>
       <c r="E221">
-        <v>13613</v>
+        <v>11940</v>
       </c>
       <c r="F221" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G221">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H221">
         <v>3</v>
       </c>
       <c r="I221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J221" t="str">
         <v>jardineria</v>
@@ -8827,7 +8827,7 @@
         <v>200</v>
       </c>
       <c r="E222">
-        <v>18876</v>
+        <v>19161</v>
       </c>
       <c r="F222" t="str">
         <v>OK_MIXTO</v>
@@ -8865,19 +8865,19 @@
         <v>200</v>
       </c>
       <c r="E223">
-        <v>28865</v>
+        <v>24926</v>
       </c>
       <c r="F223" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G223">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H223">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I223">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J223" t="str">
         <v>energia_solar</v>
@@ -8903,7 +8903,7 @@
         <v>200</v>
       </c>
       <c r="E224">
-        <v>20376</v>
+        <v>21299</v>
       </c>
       <c r="F224" t="str">
         <v>OK_MIXTO</v>
@@ -8912,10 +8912,10 @@
         <v>8</v>
       </c>
       <c r="H224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I224">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J224" t="str">
         <v>energia_solar</v>
@@ -8941,19 +8941,19 @@
         <v>200</v>
       </c>
       <c r="E225">
-        <v>19098</v>
+        <v>18309</v>
       </c>
       <c r="F225" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G225">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H225">
         <v>1</v>
       </c>
       <c r="I225">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J225" t="str">
         <v>energia_solar</v>
@@ -8979,7 +8979,7 @@
         <v>200</v>
       </c>
       <c r="E226">
-        <v>15073</v>
+        <v>15262</v>
       </c>
       <c r="F226" t="str">
         <v>OK_MIXTO</v>
@@ -8988,10 +8988,10 @@
         <v>6</v>
       </c>
       <c r="H226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I226">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J226" t="str">
         <v>energia_solar</v>
@@ -9017,16 +9017,16 @@
         <v>200</v>
       </c>
       <c r="E227">
-        <v>29080</v>
+        <v>26574</v>
       </c>
       <c r="F227" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G227">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H227">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I227">
         <v>8</v>
@@ -9055,7 +9055,7 @@
         <v>200</v>
       </c>
       <c r="E228">
-        <v>13868</v>
+        <v>12920</v>
       </c>
       <c r="F228" t="str">
         <v>OK_MIXTO</v>
@@ -9093,7 +9093,7 @@
         <v>200</v>
       </c>
       <c r="E229">
-        <v>28567</v>
+        <v>27662</v>
       </c>
       <c r="F229" t="str">
         <v>OK_MIXTO</v>
@@ -9102,10 +9102,10 @@
         <v>13</v>
       </c>
       <c r="H229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I229">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J229" t="str">
         <v>energia_solar</v>
@@ -9131,25 +9131,25 @@
         <v>200</v>
       </c>
       <c r="E230">
-        <v>29018</v>
+        <v>28543</v>
       </c>
       <c r="F230" t="str">
-        <v>VACIO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G230">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I230">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J230" t="str">
-        <v/>
+        <v>energia_solar</v>
       </c>
       <c r="K230" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L230" t="str">
         <v/>
@@ -9169,19 +9169,19 @@
         <v>200</v>
       </c>
       <c r="E231">
-        <v>27959</v>
+        <v>16423</v>
       </c>
       <c r="F231" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_CATALOGO</v>
       </c>
       <c r="G231">
         <v>8</v>
       </c>
       <c r="H231">
+        <v>8</v>
+      </c>
+      <c r="I231">
         <v>0</v>
-      </c>
-      <c r="I231">
-        <v>8</v>
       </c>
       <c r="J231" t="str">
         <v>energia_solar</v>
@@ -9207,19 +9207,19 @@
         <v>200</v>
       </c>
       <c r="E232">
-        <v>17809</v>
+        <v>15479</v>
       </c>
       <c r="F232" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G232">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H232">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I232">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J232" t="str">
         <v>energia_solar</v>
@@ -9245,19 +9245,19 @@
         <v>200</v>
       </c>
       <c r="E233">
-        <v>16887</v>
+        <v>19104</v>
       </c>
       <c r="F233" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G233">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H233">
         <v>0</v>
       </c>
       <c r="I233">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J233" t="str">
         <v>gestoria_tramites</v>
@@ -9283,7 +9283,7 @@
         <v>200</v>
       </c>
       <c r="E234">
-        <v>25958</v>
+        <v>28545</v>
       </c>
       <c r="F234" t="str">
         <v>OK_MIXTO</v>
@@ -9292,10 +9292,10 @@
         <v>10</v>
       </c>
       <c r="H234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I234">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J234" t="str">
         <v>energia_solar</v>
@@ -9321,19 +9321,19 @@
         <v>200</v>
       </c>
       <c r="E235">
-        <v>15919</v>
+        <v>16965</v>
       </c>
       <c r="F235" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G235">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H235">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J235" t="str">
         <v>energia_solar</v>
@@ -9359,7 +9359,7 @@
         <v>200</v>
       </c>
       <c r="E236">
-        <v>27526</v>
+        <v>27042</v>
       </c>
       <c r="F236" t="str">
         <v>VACIO</v>
@@ -9397,7 +9397,7 @@
         <v>200</v>
       </c>
       <c r="E237">
-        <v>14838</v>
+        <v>15549</v>
       </c>
       <c r="F237" t="str">
         <v>OK_MIXTO</v>
@@ -9406,10 +9406,10 @@
         <v>7</v>
       </c>
       <c r="H237">
+        <v>4</v>
+      </c>
+      <c r="I237">
         <v>3</v>
-      </c>
-      <c r="I237">
-        <v>4</v>
       </c>
       <c r="J237" t="str">
         <v>energia_solar</v>
@@ -9435,19 +9435,19 @@
         <v>200</v>
       </c>
       <c r="E238">
-        <v>20791</v>
+        <v>19379</v>
       </c>
       <c r="F238" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G238">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H238">
         <v>4</v>
       </c>
       <c r="I238">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J238" t="str">
         <v>energia_solar</v>
@@ -9473,7 +9473,7 @@
         <v>200</v>
       </c>
       <c r="E239">
-        <v>16422</v>
+        <v>16657</v>
       </c>
       <c r="F239" t="str">
         <v>OK_MIXTO</v>
@@ -9511,25 +9511,25 @@
         <v>200</v>
       </c>
       <c r="E240">
-        <v>27218</v>
+        <v>26750</v>
       </c>
       <c r="F240" t="str">
-        <v>OK_MIXTO</v>
+        <v>VACIO</v>
       </c>
       <c r="G240">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I240">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J240" t="str">
-        <v>energia_solar</v>
+        <v/>
       </c>
       <c r="K240" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L240" t="str">
         <v/>
@@ -9549,7 +9549,7 @@
         <v>200</v>
       </c>
       <c r="E241">
-        <v>19808</v>
+        <v>24774</v>
       </c>
       <c r="F241" t="str">
         <v>OK_MIXTO</v>
@@ -9587,19 +9587,19 @@
         <v>200</v>
       </c>
       <c r="E242">
-        <v>18928</v>
+        <v>14422</v>
       </c>
       <c r="F242" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G242">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H242">
         <v>1</v>
       </c>
       <c r="I242">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J242" t="str">
         <v>telecomunicaciones</v>
@@ -9625,7 +9625,7 @@
         <v>200</v>
       </c>
       <c r="E243">
-        <v>14914</v>
+        <v>13341</v>
       </c>
       <c r="F243" t="str">
         <v>OK_MIXTO</v>
@@ -9634,10 +9634,10 @@
         <v>6</v>
       </c>
       <c r="H243">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J243" t="str">
         <v>telecomunicaciones</v>
@@ -9663,7 +9663,7 @@
         <v>200</v>
       </c>
       <c r="E244">
-        <v>16553</v>
+        <v>14481</v>
       </c>
       <c r="F244" t="str">
         <v>OK_MIXTO</v>
@@ -9701,7 +9701,7 @@
         <v>200</v>
       </c>
       <c r="E245">
-        <v>16966</v>
+        <v>14907</v>
       </c>
       <c r="F245" t="str">
         <v>OK_MIXTO</v>
@@ -9710,10 +9710,10 @@
         <v>7</v>
       </c>
       <c r="H245">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J245" t="str">
         <v>telecomunicaciones</v>
@@ -9739,16 +9739,16 @@
         <v>200</v>
       </c>
       <c r="E246">
-        <v>15633</v>
+        <v>20566</v>
       </c>
       <c r="F246" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G246">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H246">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I246">
         <v>6</v>
@@ -9777,7 +9777,7 @@
         <v>200</v>
       </c>
       <c r="E247">
-        <v>10963</v>
+        <v>11838</v>
       </c>
       <c r="F247" t="str">
         <v>OK_MIXTO</v>
@@ -9815,19 +9815,19 @@
         <v>200</v>
       </c>
       <c r="E248">
-        <v>18255</v>
+        <v>17335</v>
       </c>
       <c r="F248" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G248">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H248">
         <v>3</v>
       </c>
       <c r="I248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J248" t="str">
         <v>telecomunicaciones</v>
@@ -9853,19 +9853,19 @@
         <v>200</v>
       </c>
       <c r="E249">
-        <v>12219</v>
+        <v>11249</v>
       </c>
       <c r="F249" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G249">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H249">
         <v>3</v>
       </c>
       <c r="I249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J249" t="str">
         <v>telecomunicaciones</v>
@@ -9891,7 +9891,7 @@
         <v>200</v>
       </c>
       <c r="E250">
-        <v>14910</v>
+        <v>13412</v>
       </c>
       <c r="F250" t="str">
         <v>OK_MIXTO</v>
@@ -9929,16 +9929,16 @@
         <v>200</v>
       </c>
       <c r="E251">
-        <v>11774</v>
+        <v>9063</v>
       </c>
       <c r="F251" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G251">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H251">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I251">
         <v>1</v>
@@ -9967,19 +9967,19 @@
         <v>200</v>
       </c>
       <c r="E252">
-        <v>26174</v>
+        <v>28323</v>
       </c>
       <c r="F252" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G252">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H252">
         <v>4</v>
       </c>
       <c r="I252">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J252" t="str">
         <v>telecomunicaciones</v>
@@ -10005,19 +10005,19 @@
         <v>200</v>
       </c>
       <c r="E253">
-        <v>22686</v>
+        <v>17616</v>
       </c>
       <c r="F253" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G253">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H253">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I253">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J253" t="str">
         <v>telecomunicaciones</v>
@@ -10043,16 +10043,16 @@
         <v>200</v>
       </c>
       <c r="E254">
-        <v>19855</v>
+        <v>22499</v>
       </c>
       <c r="F254" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G254">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H254">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I254">
         <v>5</v>
@@ -10081,16 +10081,16 @@
         <v>200</v>
       </c>
       <c r="E255">
-        <v>25365</v>
+        <v>19615</v>
       </c>
       <c r="F255" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G255">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H255">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I255">
         <v>5</v>
@@ -10119,16 +10119,16 @@
         <v>200</v>
       </c>
       <c r="E256">
-        <v>16776</v>
+        <v>14204</v>
       </c>
       <c r="F256" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G256">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H256">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I256">
         <v>4</v>
@@ -10157,19 +10157,19 @@
         <v>200</v>
       </c>
       <c r="E257">
-        <v>22713</v>
+        <v>20360</v>
       </c>
       <c r="F257" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G257">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H257">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I257">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J257" t="str">
         <v>telecomunicaciones</v>
@@ -10195,7 +10195,7 @@
         <v>200</v>
       </c>
       <c r="E258">
-        <v>11040</v>
+        <v>9752</v>
       </c>
       <c r="F258" t="str">
         <v>OK_CATALOGO</v>
@@ -10233,7 +10233,7 @@
         <v>200</v>
       </c>
       <c r="E259">
-        <v>26706</v>
+        <v>18137</v>
       </c>
       <c r="F259" t="str">
         <v>OK_MIXTO</v>
@@ -10271,7 +10271,7 @@
         <v>200</v>
       </c>
       <c r="E260">
-        <v>15174</v>
+        <v>18738</v>
       </c>
       <c r="F260" t="str">
         <v>OK_MIXTO</v>
@@ -10309,19 +10309,19 @@
         <v>200</v>
       </c>
       <c r="E261">
-        <v>23857</v>
+        <v>19992</v>
       </c>
       <c r="F261" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G261">
         <v>10</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I261">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J261" t="str">
         <v>telecomunicaciones</v>
@@ -10347,19 +10347,19 @@
         <v>200</v>
       </c>
       <c r="E262">
-        <v>11162</v>
+        <v>16127</v>
       </c>
       <c r="F262" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G262">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H262">
         <v>2</v>
       </c>
       <c r="I262">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J262" t="str">
         <v>cristaleria</v>
@@ -10385,19 +10385,19 @@
         <v>200</v>
       </c>
       <c r="E263">
-        <v>15894</v>
+        <v>14743</v>
       </c>
       <c r="F263" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G263">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H263">
         <v>1</v>
       </c>
       <c r="I263">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J263" t="str">
         <v>cristaleria</v>
@@ -10423,7 +10423,7 @@
         <v>200</v>
       </c>
       <c r="E264">
-        <v>12943</v>
+        <v>14252</v>
       </c>
       <c r="F264" t="str">
         <v>OK_MIXTO</v>
@@ -10461,7 +10461,7 @@
         <v>200</v>
       </c>
       <c r="E265">
-        <v>16944</v>
+        <v>16826</v>
       </c>
       <c r="F265" t="str">
         <v>OK_MIXTO</v>
@@ -10470,10 +10470,10 @@
         <v>6</v>
       </c>
       <c r="H265">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J265" t="str">
         <v>cristaleria</v>
@@ -10499,19 +10499,19 @@
         <v>200</v>
       </c>
       <c r="E266">
-        <v>16108</v>
+        <v>13500</v>
       </c>
       <c r="F266" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G266">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H266">
         <v>2</v>
       </c>
       <c r="I266">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J266" t="str">
         <v>cristaleria</v>
@@ -10537,19 +10537,19 @@
         <v>200</v>
       </c>
       <c r="E267">
-        <v>18318</v>
+        <v>24287</v>
       </c>
       <c r="F267" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G267">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H267">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I267">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J267" t="str">
         <v>persianas</v>
@@ -10575,19 +10575,19 @@
         <v>200</v>
       </c>
       <c r="E268">
-        <v>20460</v>
+        <v>16017</v>
       </c>
       <c r="F268" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G268">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H268">
+        <v>3</v>
+      </c>
+      <c r="I268">
         <v>2</v>
-      </c>
-      <c r="I268">
-        <v>4</v>
       </c>
       <c r="J268" t="str">
         <v>cristaleria</v>
@@ -10613,7 +10613,7 @@
         <v>200</v>
       </c>
       <c r="E269">
-        <v>18830</v>
+        <v>18952</v>
       </c>
       <c r="F269" t="str">
         <v>OK_MIXTO</v>
@@ -10651,7 +10651,7 @@
         <v>200</v>
       </c>
       <c r="E270">
-        <v>10572</v>
+        <v>9770</v>
       </c>
       <c r="F270" t="str">
         <v>OK_MIXTO</v>
@@ -10689,7 +10689,7 @@
         <v>200</v>
       </c>
       <c r="E271">
-        <v>15143</v>
+        <v>10620</v>
       </c>
       <c r="F271" t="str">
         <v>OK_MIXTO</v>
@@ -10727,7 +10727,7 @@
         <v>200</v>
       </c>
       <c r="E272">
-        <v>12850</v>
+        <v>11705</v>
       </c>
       <c r="F272" t="str">
         <v>OK_MIXTO</v>
@@ -10765,16 +10765,16 @@
         <v>200</v>
       </c>
       <c r="E273">
-        <v>16127</v>
+        <v>16776</v>
       </c>
       <c r="F273" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G273">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I273">
         <v>6</v>
@@ -10803,7 +10803,7 @@
         <v>200</v>
       </c>
       <c r="E274">
-        <v>12115</v>
+        <v>11506</v>
       </c>
       <c r="F274" t="str">
         <v>OK_MIXTO</v>
@@ -10841,7 +10841,7 @@
         <v>200</v>
       </c>
       <c r="E275">
-        <v>15574</v>
+        <v>16845</v>
       </c>
       <c r="F275" t="str">
         <v>OK_MIXTO</v>
@@ -10879,7 +10879,7 @@
         <v>200</v>
       </c>
       <c r="E276">
-        <v>13423</v>
+        <v>13259</v>
       </c>
       <c r="F276" t="str">
         <v>OK_MIXTO</v>
@@ -10917,7 +10917,7 @@
         <v>200</v>
       </c>
       <c r="E277">
-        <v>13424</v>
+        <v>14632</v>
       </c>
       <c r="F277" t="str">
         <v>OK_MIXTO</v>
@@ -10926,10 +10926,10 @@
         <v>6</v>
       </c>
       <c r="H277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J277" t="str">
         <v>cristaleria</v>
@@ -10955,16 +10955,16 @@
         <v>200</v>
       </c>
       <c r="E278">
-        <v>18390</v>
+        <v>14603</v>
       </c>
       <c r="F278" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G278">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H278">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I278">
         <v>3</v>
@@ -10993,19 +10993,19 @@
         <v>200</v>
       </c>
       <c r="E279">
-        <v>17874</v>
+        <v>18634</v>
       </c>
       <c r="F279" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G279">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I279">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J279" t="str">
         <v>cristaleria</v>
@@ -11031,7 +11031,7 @@
         <v>200</v>
       </c>
       <c r="E280">
-        <v>17873</v>
+        <v>19479</v>
       </c>
       <c r="F280" t="str">
         <v>OK_MIXTO</v>
@@ -11069,16 +11069,16 @@
         <v>200</v>
       </c>
       <c r="E281">
-        <v>15166</v>
+        <v>12780</v>
       </c>
       <c r="F281" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G281">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H281">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I281">
         <v>3</v>
@@ -11107,19 +11107,19 @@
         <v>200</v>
       </c>
       <c r="E282">
-        <v>20942</v>
+        <v>20856</v>
       </c>
       <c r="F282" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G282">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I282">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J282" t="str">
         <v>impermeabilizacion</v>
@@ -11145,19 +11145,19 @@
         <v>200</v>
       </c>
       <c r="E283">
-        <v>21869</v>
+        <v>21072</v>
       </c>
       <c r="F283" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G283">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I283">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J283" t="str">
         <v>impermeabilizacion</v>
@@ -11183,19 +11183,19 @@
         <v>200</v>
       </c>
       <c r="E284">
-        <v>23555</v>
+        <v>19773</v>
       </c>
       <c r="F284" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G284">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H284">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I284">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J284" t="str">
         <v>impermeabilizacion</v>
@@ -11221,19 +11221,19 @@
         <v>200</v>
       </c>
       <c r="E285">
-        <v>21233</v>
+        <v>22310</v>
       </c>
       <c r="F285" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G285">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H285">
         <v>3</v>
       </c>
       <c r="I285">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J285" t="str">
         <v>impermeabilizacion</v>
@@ -11259,16 +11259,16 @@
         <v>200</v>
       </c>
       <c r="E286">
-        <v>16177</v>
+        <v>14910</v>
       </c>
       <c r="F286" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G286">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H286">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I286">
         <v>5</v>
@@ -11297,19 +11297,19 @@
         <v>200</v>
       </c>
       <c r="E287">
-        <v>25241</v>
+        <v>24995</v>
       </c>
       <c r="F287" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G287">
         <v>8</v>
       </c>
       <c r="H287">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I287">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J287" t="str">
         <v>impermeabilizacion</v>
@@ -11335,19 +11335,19 @@
         <v>200</v>
       </c>
       <c r="E288">
-        <v>26213</v>
+        <v>24891</v>
       </c>
       <c r="F288" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G288">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H288">
         <v>5</v>
       </c>
       <c r="I288">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J288" t="str">
         <v>impermeabilizacion</v>
@@ -11373,7 +11373,7 @@
         <v>200</v>
       </c>
       <c r="E289">
-        <v>16176</v>
+        <v>16826</v>
       </c>
       <c r="F289" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -11388,10 +11388,10 @@
         <v>6</v>
       </c>
       <c r="J289" t="str">
-        <v>jardineria</v>
+        <v>impermeabilizacion</v>
       </c>
       <c r="K289" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L289" t="str">
         <v/>
@@ -11411,19 +11411,19 @@
         <v>200</v>
       </c>
       <c r="E290">
-        <v>21597</v>
+        <v>22462</v>
       </c>
       <c r="F290" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G290">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H290">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I290">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J290" t="str">
         <v>impermeabilizacion</v>
@@ -11449,16 +11449,16 @@
         <v>200</v>
       </c>
       <c r="E291">
-        <v>21228</v>
+        <v>24574</v>
       </c>
       <c r="F291" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G291">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H291">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I291">
         <v>6</v>
@@ -11487,7 +11487,7 @@
         <v>200</v>
       </c>
       <c r="E292">
-        <v>18770</v>
+        <v>20037</v>
       </c>
       <c r="F292" t="str">
         <v>OK_MIXTO</v>
@@ -11496,10 +11496,10 @@
         <v>8</v>
       </c>
       <c r="H292">
+        <v>5</v>
+      </c>
+      <c r="I292">
         <v>3</v>
-      </c>
-      <c r="I292">
-        <v>5</v>
       </c>
       <c r="J292" t="str">
         <v>impermeabilizacion</v>
@@ -11525,25 +11525,25 @@
         <v>200</v>
       </c>
       <c r="E293">
-        <v>20114</v>
+        <v>18275</v>
       </c>
       <c r="F293" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G293">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H293">
         <v>3</v>
       </c>
       <c r="I293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J293" t="str">
-        <v>tejados_cubiertas</v>
+        <v>impermeabilizacion</v>
       </c>
       <c r="K293" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L293" t="str">
         <v/>
@@ -11563,16 +11563,16 @@
         <v>200</v>
       </c>
       <c r="E294">
-        <v>14120</v>
+        <v>14186</v>
       </c>
       <c r="F294" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G294">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H294">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I294">
         <v>3</v>
@@ -11601,19 +11601,19 @@
         <v>200</v>
       </c>
       <c r="E295">
-        <v>22786</v>
+        <v>19574</v>
       </c>
       <c r="F295" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G295">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H295">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I295">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J295" t="str">
         <v>impermeabilizacion</v>
@@ -11639,25 +11639,25 @@
         <v>200</v>
       </c>
       <c r="E296">
-        <v>12048</v>
+        <v>18406</v>
       </c>
       <c r="F296" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G296">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H296">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I296">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J296" t="str">
-        <v>suelos_alicatados</v>
+        <v>impermeabilizacion</v>
       </c>
       <c r="K296" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L296" t="str">
         <v/>
@@ -11677,19 +11677,19 @@
         <v>200</v>
       </c>
       <c r="E297">
-        <v>25927</v>
+        <v>23931</v>
       </c>
       <c r="F297" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G297">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H297">
         <v>1</v>
       </c>
       <c r="I297">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J297" t="str">
         <v>impermeabilizacion</v>
@@ -11715,7 +11715,7 @@
         <v>200</v>
       </c>
       <c r="E298">
-        <v>19685</v>
+        <v>18099</v>
       </c>
       <c r="F298" t="str">
         <v>OK_MIXTO</v>
@@ -11724,10 +11724,10 @@
         <v>6</v>
       </c>
       <c r="H298">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I298">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J298" t="str">
         <v>impermeabilizacion</v>
@@ -11753,19 +11753,19 @@
         <v>200</v>
       </c>
       <c r="E299">
-        <v>23694</v>
+        <v>25358</v>
       </c>
       <c r="F299" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G299">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I299">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J299" t="str">
         <v>impermeabilizacion</v>
@@ -11791,7 +11791,7 @@
         <v>200</v>
       </c>
       <c r="E300">
-        <v>14271</v>
+        <v>20838</v>
       </c>
       <c r="F300" t="str">
         <v>OK_MIXTO</v>
@@ -11829,19 +11829,19 @@
         <v>200</v>
       </c>
       <c r="E301">
-        <v>19682</v>
+        <v>13112</v>
       </c>
       <c r="F301" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G301">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H301">
         <v>3</v>
       </c>
       <c r="I301">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J301" t="str">
         <v>tejados_cubiertas</v>
@@ -11867,19 +11867,19 @@
         <v>200</v>
       </c>
       <c r="E302">
-        <v>17343</v>
+        <v>14193</v>
       </c>
       <c r="F302" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G302">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H302">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I302">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J302" t="str">
         <v>contra_incendios</v>
@@ -11905,7 +11905,7 @@
         <v>200</v>
       </c>
       <c r="E303">
-        <v>18330</v>
+        <v>18704</v>
       </c>
       <c r="F303" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -11943,19 +11943,19 @@
         <v>200</v>
       </c>
       <c r="E304">
-        <v>23692</v>
+        <v>22345</v>
       </c>
       <c r="F304" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G304">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H304">
         <v>2</v>
       </c>
       <c r="I304">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J304" t="str">
         <v>contra_incendios</v>
@@ -11981,7 +11981,7 @@
         <v>200</v>
       </c>
       <c r="E305">
-        <v>13005</v>
+        <v>20328</v>
       </c>
       <c r="F305" t="str">
         <v>OK_MIXTO</v>
@@ -12019,7 +12019,7 @@
         <v>200</v>
       </c>
       <c r="E306">
-        <v>30103</v>
+        <v>22382</v>
       </c>
       <c r="F306" t="str">
         <v>OK_MIXTO</v>
@@ -12057,16 +12057,16 @@
         <v>200</v>
       </c>
       <c r="E307">
-        <v>27887</v>
+        <v>25614</v>
       </c>
       <c r="F307" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G307">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H307">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I307">
         <v>7</v>
@@ -12095,19 +12095,19 @@
         <v>200</v>
       </c>
       <c r="E308">
-        <v>27277</v>
+        <v>23611</v>
       </c>
       <c r="F308" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G308">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H308">
         <v>2</v>
       </c>
       <c r="I308">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J308" t="str">
         <v>contra_incendios</v>
@@ -12133,19 +12133,19 @@
         <v>200</v>
       </c>
       <c r="E309">
-        <v>16394</v>
+        <v>23447</v>
       </c>
       <c r="F309" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G309">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I309">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J309" t="str">
         <v>contra_incendios</v>
@@ -12171,19 +12171,19 @@
         <v>200</v>
       </c>
       <c r="E310">
-        <v>16719</v>
+        <v>17453</v>
       </c>
       <c r="F310" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G310">
+        <v>10</v>
+      </c>
+      <c r="H310">
         <v>9</v>
       </c>
-      <c r="H310">
-        <v>6</v>
-      </c>
       <c r="I310">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J310" t="str">
         <v>contra_incendios</v>
@@ -12209,7 +12209,7 @@
         <v>200</v>
       </c>
       <c r="E311">
-        <v>21812</v>
+        <v>15048</v>
       </c>
       <c r="F311" t="str">
         <v>OK_MIXTO</v>
@@ -12224,10 +12224,10 @@
         <v>4</v>
       </c>
       <c r="J311" t="str">
-        <v>cerrajeria</v>
+        <v>contra_incendios</v>
       </c>
       <c r="K311" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L311" t="str">
         <v/>
@@ -12247,7 +12247,7 @@
         <v>200</v>
       </c>
       <c r="E312">
-        <v>13207</v>
+        <v>12864</v>
       </c>
       <c r="F312" t="str">
         <v>OK_MIXTO</v>
@@ -12285,19 +12285,19 @@
         <v>200</v>
       </c>
       <c r="E313">
-        <v>28204</v>
+        <v>29515</v>
       </c>
       <c r="F313" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G313">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H313">
         <v>4</v>
       </c>
       <c r="I313">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J313" t="str">
         <v>contra_incendios</v>
@@ -12323,7 +12323,7 @@
         <v>200</v>
       </c>
       <c r="E314">
-        <v>13826</v>
+        <v>13027</v>
       </c>
       <c r="F314" t="str">
         <v>OK_MIXTO</v>
@@ -12361,16 +12361,16 @@
         <v>200</v>
       </c>
       <c r="E315">
-        <v>22471</v>
+        <v>28685</v>
       </c>
       <c r="F315" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G315">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I315">
         <v>7</v>
@@ -12399,7 +12399,7 @@
         <v>200</v>
       </c>
       <c r="E316">
-        <v>18172</v>
+        <v>15997</v>
       </c>
       <c r="F316" t="str">
         <v>OK_MIXTO</v>
@@ -12408,10 +12408,10 @@
         <v>6</v>
       </c>
       <c r="H316">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I316">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J316" t="str">
         <v>climatizacion</v>
@@ -12437,19 +12437,19 @@
         <v>200</v>
       </c>
       <c r="E317">
-        <v>15343</v>
+        <v>16341</v>
       </c>
       <c r="F317" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G317">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H317">
         <v>3</v>
       </c>
       <c r="I317">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J317" t="str">
         <v>mecanica_especializada</v>
@@ -12475,16 +12475,16 @@
         <v>200</v>
       </c>
       <c r="E318">
-        <v>29129</v>
+        <v>22069</v>
       </c>
       <c r="F318" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G318">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H318">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I318">
         <v>5</v>
@@ -12513,19 +12513,19 @@
         <v>200</v>
       </c>
       <c r="E319">
-        <v>25492</v>
+        <v>28353</v>
       </c>
       <c r="F319" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G319">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H319">
         <v>0</v>
       </c>
       <c r="I319">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J319" t="str">
         <v>contra_incendios</v>
@@ -12551,19 +12551,19 @@
         <v>200</v>
       </c>
       <c r="E320">
-        <v>18325</v>
+        <v>15892</v>
       </c>
       <c r="F320" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G320">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H320">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I320">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J320" t="str">
         <v>contra_incendios</v>
@@ -12589,25 +12589,25 @@
         <v>200</v>
       </c>
       <c r="E321">
-        <v>30714</v>
+        <v>28010</v>
       </c>
       <c r="F321" t="str">
-        <v>VACIO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G321">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H321">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I321">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J321" t="str">
-        <v/>
+        <v>contra_incendios</v>
       </c>
       <c r="K321" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L321" t="str">
         <v/>
@@ -12627,19 +12627,19 @@
         <v>200</v>
       </c>
       <c r="E322">
-        <v>34707</v>
+        <v>24590</v>
       </c>
       <c r="F322" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G322">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I322">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J322" t="str">
         <v>fachadas</v>
@@ -12665,19 +12665,19 @@
         <v>200</v>
       </c>
       <c r="E323">
-        <v>30711</v>
+        <v>28670</v>
       </c>
       <c r="F323" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G323">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H323">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I323">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J323" t="str">
         <v>fachadas</v>
@@ -12703,19 +12703,19 @@
         <v>200</v>
       </c>
       <c r="E324">
-        <v>15790</v>
+        <v>15043</v>
       </c>
       <c r="F324" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G324">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H324">
         <v>1</v>
       </c>
       <c r="I324">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J324" t="str">
         <v>fachadas</v>
@@ -12741,7 +12741,7 @@
         <v>200</v>
       </c>
       <c r="E325">
-        <v>20470</v>
+        <v>16340</v>
       </c>
       <c r="F325" t="str">
         <v>OK_MIXTO</v>
@@ -12779,16 +12779,16 @@
         <v>200</v>
       </c>
       <c r="E326">
-        <v>26205</v>
+        <v>27038</v>
       </c>
       <c r="F326" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G326">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H326">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I326">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>200</v>
       </c>
       <c r="E327">
-        <v>22007</v>
+        <v>13395</v>
       </c>
       <c r="F327" t="str">
         <v>OK_MIXTO</v>
@@ -12826,10 +12826,10 @@
         <v>6</v>
       </c>
       <c r="H327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I327">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J327" t="str">
         <v>fachadas</v>
@@ -12855,7 +12855,7 @@
         <v>200</v>
       </c>
       <c r="E328">
-        <v>19754</v>
+        <v>22078</v>
       </c>
       <c r="F328" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -12893,7 +12893,7 @@
         <v>200</v>
       </c>
       <c r="E329">
-        <v>12889</v>
+        <v>12207</v>
       </c>
       <c r="F329" t="str">
         <v>OK_MIXTO</v>
@@ -12931,16 +12931,16 @@
         <v>200</v>
       </c>
       <c r="E330">
-        <v>27540</v>
+        <v>28037</v>
       </c>
       <c r="F330" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G330">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H330">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I330">
         <v>8</v>
@@ -12969,7 +12969,7 @@
         <v>200</v>
       </c>
       <c r="E331">
-        <v>20263</v>
+        <v>21175</v>
       </c>
       <c r="F331" t="str">
         <v>OK_MIXTO</v>
@@ -13007,16 +13007,16 @@
         <v>200</v>
       </c>
       <c r="E332">
-        <v>22979</v>
+        <v>24230</v>
       </c>
       <c r="F332" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G332">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H332">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I332">
         <v>6</v>
@@ -13045,7 +13045,7 @@
         <v>200</v>
       </c>
       <c r="E333">
-        <v>14338</v>
+        <v>16640</v>
       </c>
       <c r="F333" t="str">
         <v>OK_MIXTO</v>
@@ -13083,19 +13083,19 @@
         <v>200</v>
       </c>
       <c r="E334">
-        <v>14165</v>
+        <v>12744</v>
       </c>
       <c r="F334" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G334">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H334">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I334">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J334" t="str">
         <v>fachadas</v>
@@ -13121,19 +13121,19 @@
         <v>200</v>
       </c>
       <c r="E335">
-        <v>16688</v>
+        <v>15136</v>
       </c>
       <c r="F335" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G335">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H335">
         <v>1</v>
       </c>
       <c r="I335">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J335" t="str">
         <v>fachadas</v>
@@ -13159,16 +13159,16 @@
         <v>200</v>
       </c>
       <c r="E336">
-        <v>17442</v>
+        <v>17287</v>
       </c>
       <c r="F336" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G336">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H336">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I336">
         <v>3</v>
@@ -13197,19 +13197,19 @@
         <v>200</v>
       </c>
       <c r="E337">
-        <v>19758</v>
+        <v>20135</v>
       </c>
       <c r="F337" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G337">
+        <v>11</v>
+      </c>
+      <c r="H337">
+        <v>2</v>
+      </c>
+      <c r="I337">
         <v>9</v>
-      </c>
-      <c r="H337">
-        <v>4</v>
-      </c>
-      <c r="I337">
-        <v>5</v>
       </c>
       <c r="J337" t="str">
         <v>fachadas</v>
@@ -13235,7 +13235,7 @@
         <v>200</v>
       </c>
       <c r="E338">
-        <v>15903</v>
+        <v>12201</v>
       </c>
       <c r="F338" t="str">
         <v>OK_MIXTO</v>
@@ -13273,22 +13273,22 @@
         <v>200</v>
       </c>
       <c r="E339">
-        <v>16416</v>
+        <v>13639</v>
       </c>
       <c r="F339" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G339">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H339">
         <v>3</v>
       </c>
       <c r="I339">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J339" t="str">
-        <v>cristaleria</v>
+        <v>electricidad</v>
       </c>
       <c r="K339" t="str">
         <v>NO</v>
@@ -13311,25 +13311,25 @@
         <v>200</v>
       </c>
       <c r="E340">
-        <v>19917</v>
+        <v>13454</v>
       </c>
       <c r="F340" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G340">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H340">
+        <v>1</v>
+      </c>
+      <c r="I340">
         <v>5</v>
       </c>
-      <c r="I340">
-        <v>3</v>
-      </c>
       <c r="J340" t="str">
-        <v>suelos_alicatados</v>
+        <v>fachadas</v>
       </c>
       <c r="K340" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L340" t="str">
         <v/>
@@ -13349,19 +13349,19 @@
         <v>200</v>
       </c>
       <c r="E341">
-        <v>14572</v>
+        <v>17913</v>
       </c>
       <c r="F341" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H341">
         <v>1</v>
       </c>
       <c r="I341">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J341" t="str">
         <v>energia_solar</v>
@@ -13387,7 +13387,7 @@
         <v>403</v>
       </c>
       <c r="E342">
-        <v>788</v>
+        <v>217</v>
       </c>
       <c r="F342" t="str">
         <v>ERROR_TECNICO</v>
@@ -13425,19 +13425,19 @@
         <v>200</v>
       </c>
       <c r="E343">
-        <v>13751</v>
+        <v>14501</v>
       </c>
       <c r="F343" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G343">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H343">
         <v>5</v>
       </c>
       <c r="I343">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J343" t="str">
         <v>mantenimiento_general</v>
@@ -13463,7 +13463,7 @@
         <v>200</v>
       </c>
       <c r="E344">
-        <v>9602</v>
+        <v>8488</v>
       </c>
       <c r="F344" t="str">
         <v>OK_MIXTO</v>
@@ -13501,7 +13501,7 @@
         <v>200</v>
       </c>
       <c r="E345">
-        <v>17951</v>
+        <v>17433</v>
       </c>
       <c r="F345" t="str">
         <v>OK_MIXTO</v>
@@ -13539,19 +13539,19 @@
         <v>200</v>
       </c>
       <c r="E346">
-        <v>11753</v>
+        <v>15329</v>
       </c>
       <c r="F346" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G346">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H346">
         <v>5</v>
       </c>
       <c r="I346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J346" t="str">
         <v>mantenimiento_general</v>
@@ -13577,7 +13577,7 @@
         <v>403</v>
       </c>
       <c r="E347">
-        <v>732</v>
+        <v>194</v>
       </c>
       <c r="F347" t="str">
         <v>ERROR_TECNICO</v>
@@ -13615,19 +13615,19 @@
         <v>200</v>
       </c>
       <c r="E348">
-        <v>15779</v>
+        <v>15647</v>
       </c>
       <c r="F348" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G348">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H348">
         <v>4</v>
       </c>
       <c r="I348">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J348" t="str">
         <v>tejados_cubiertas</v>
@@ -13653,19 +13653,19 @@
         <v>200</v>
       </c>
       <c r="E349">
-        <v>24277</v>
+        <v>17474</v>
       </c>
       <c r="F349" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G349">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H349">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I349">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J349" t="str">
         <v>mantenimiento_general</v>
@@ -13691,7 +13691,7 @@
         <v>200</v>
       </c>
       <c r="E350">
-        <v>11670</v>
+        <v>12075</v>
       </c>
       <c r="F350" t="str">
         <v>OK_MIXTO</v>
@@ -13729,19 +13729,19 @@
         <v>200</v>
       </c>
       <c r="E351">
-        <v>15347</v>
+        <v>14155</v>
       </c>
       <c r="F351" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G351">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H351">
         <v>3</v>
       </c>
       <c r="I351">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J351" t="str">
         <v>pintura</v>
@@ -13767,19 +13767,19 @@
         <v>200</v>
       </c>
       <c r="E352">
-        <v>24153</v>
+        <v>20660</v>
       </c>
       <c r="F352" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G352">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H352">
         <v>4</v>
       </c>
       <c r="I352">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J352" t="str">
         <v>albanileria</v>
@@ -13805,25 +13805,25 @@
         <v>200</v>
       </c>
       <c r="E353">
-        <v>12905</v>
+        <v>13256</v>
       </c>
       <c r="F353" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G353">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H353">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I353">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J353" t="str">
-        <v>multiservicio</v>
+        <v>mantenimiento_general</v>
       </c>
       <c r="K353" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L353" t="str">
         <v/>
@@ -13843,16 +13843,16 @@
         <v>200</v>
       </c>
       <c r="E354">
-        <v>13813</v>
+        <v>13715</v>
       </c>
       <c r="F354" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G354">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H354">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I354">
         <v>2</v>
@@ -13881,25 +13881,25 @@
         <v>200</v>
       </c>
       <c r="E355">
-        <v>17459</v>
+        <v>18255</v>
       </c>
       <c r="F355" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G355">
+        <v>11</v>
+      </c>
+      <c r="H355">
         <v>7</v>
       </c>
-      <c r="H355">
-        <v>4</v>
-      </c>
       <c r="I355">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J355" t="str">
-        <v>mantenimiento_general</v>
+        <v>mecanica_especializada</v>
       </c>
       <c r="K355" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L355" t="str">
         <v/>
@@ -13919,7 +13919,7 @@
         <v>200</v>
       </c>
       <c r="E356">
-        <v>11105</v>
+        <v>11192</v>
       </c>
       <c r="F356" t="str">
         <v>OK_MIXTO</v>
@@ -13957,19 +13957,19 @@
         <v>200</v>
       </c>
       <c r="E357">
-        <v>15610</v>
+        <v>14259</v>
       </c>
       <c r="F357" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G357">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H357">
         <v>3</v>
       </c>
       <c r="I357">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J357" t="str">
         <v>albanileria</v>
@@ -13995,7 +13995,7 @@
         <v>200</v>
       </c>
       <c r="E358">
-        <v>11858</v>
+        <v>14662</v>
       </c>
       <c r="F358" t="str">
         <v>OK_MIXTO</v>
@@ -14033,19 +14033,19 @@
         <v>200</v>
       </c>
       <c r="E359">
-        <v>14902</v>
+        <v>17078</v>
       </c>
       <c r="F359" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G359">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H359">
         <v>6</v>
       </c>
       <c r="I359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J359" t="str">
         <v>mantenimiento_general</v>
@@ -14071,19 +14071,19 @@
         <v>200</v>
       </c>
       <c r="E360">
-        <v>13665</v>
+        <v>15029</v>
       </c>
       <c r="F360" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G360">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H360">
         <v>3</v>
       </c>
       <c r="I360">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J360" t="str">
         <v>electricidad</v>
@@ -14109,19 +14109,19 @@
         <v>200</v>
       </c>
       <c r="E361">
-        <v>16121</v>
+        <v>13528</v>
       </c>
       <c r="F361" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G361">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H361">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I361">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J361" t="str">
         <v>jardineria</v>
@@ -14147,19 +14147,19 @@
         <v>200</v>
       </c>
       <c r="E362">
-        <v>30307</v>
+        <v>19336</v>
       </c>
       <c r="F362" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G362">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H362">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I362">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J362" t="str">
         <v>reforma_integral</v>
@@ -14185,19 +14185,19 @@
         <v>200</v>
       </c>
       <c r="E363">
-        <v>24569</v>
+        <v>25072</v>
       </c>
       <c r="F363" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G363">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H363">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I363">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J363" t="str">
         <v>reforma_integral</v>
@@ -14223,19 +14223,19 @@
         <v>200</v>
       </c>
       <c r="E364">
-        <v>47710</v>
+        <v>39276</v>
       </c>
       <c r="F364" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G364">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H364">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I364">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J364" t="str">
         <v>reforma_integral</v>
@@ -14261,22 +14261,22 @@
         <v>200</v>
       </c>
       <c r="E365">
-        <v>48627</v>
+        <v>51505</v>
       </c>
       <c r="F365" t="str">
-        <v>VACIO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G365">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H365">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I365">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J365" t="str">
-        <v/>
+        <v>reforma_integral</v>
       </c>
       <c r="K365" t="str">
         <v>NO</v>
@@ -14299,19 +14299,19 @@
         <v>200</v>
       </c>
       <c r="E366">
-        <v>30302</v>
+        <v>35903</v>
       </c>
       <c r="F366" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G366">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H366">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I366">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J366" t="str">
         <v>reforma_integral</v>
@@ -14337,19 +14337,19 @@
         <v>200</v>
       </c>
       <c r="E367">
-        <v>30761</v>
+        <v>35312</v>
       </c>
       <c r="F367" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G367">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H367">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I367">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J367" t="str">
         <v>reforma_integral</v>
@@ -14375,19 +14375,19 @@
         <v>200</v>
       </c>
       <c r="E368">
-        <v>37067</v>
+        <v>44682</v>
       </c>
       <c r="F368" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G368">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H368">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I368">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J368" t="str">
         <v>reforma_integral</v>
@@ -14413,16 +14413,16 @@
         <v>200</v>
       </c>
       <c r="E369">
-        <v>42798</v>
+        <v>41117</v>
       </c>
       <c r="F369" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G369">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H369">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I369">
         <v>7</v>
@@ -14451,19 +14451,19 @@
         <v>200</v>
       </c>
       <c r="E370">
-        <v>28362</v>
+        <v>28815</v>
       </c>
       <c r="F370" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G370">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H370">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I370">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J370" t="str">
         <v>reforma_integral</v>
@@ -14489,7 +14489,7 @@
         <v>200</v>
       </c>
       <c r="E371">
-        <v>29279</v>
+        <v>28638</v>
       </c>
       <c r="F371" t="str">
         <v>OK_MIXTO</v>
@@ -14527,7 +14527,7 @@
         <v>200</v>
       </c>
       <c r="E372">
-        <v>28010</v>
+        <v>25543</v>
       </c>
       <c r="F372" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14565,7 +14565,7 @@
         <v>200</v>
       </c>
       <c r="E373">
-        <v>28359</v>
+        <v>29034</v>
       </c>
       <c r="F373" t="str">
         <v>OK_MIXTO</v>
@@ -14603,7 +14603,7 @@
         <v>200</v>
       </c>
       <c r="E374">
-        <v>27844</v>
+        <v>26057</v>
       </c>
       <c r="F374" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14641,19 +14641,19 @@
         <v>200</v>
       </c>
       <c r="E375">
-        <v>31361</v>
+        <v>20010</v>
       </c>
       <c r="F375" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G375">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H375">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I375">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J375" t="str">
         <v>reforma_integral</v>
@@ -14679,19 +14679,19 @@
         <v>200</v>
       </c>
       <c r="E376">
-        <v>32597</v>
+        <v>32454</v>
       </c>
       <c r="F376" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G376">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H376">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I376">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J376" t="str">
         <v>reforma_integral</v>
@@ -14717,7 +14717,7 @@
         <v>200</v>
       </c>
       <c r="E377">
-        <v>24467</v>
+        <v>25042</v>
       </c>
       <c r="F377" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14755,19 +14755,19 @@
         <v>200</v>
       </c>
       <c r="E378">
-        <v>29891</v>
+        <v>28523</v>
       </c>
       <c r="F378" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G378">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H378">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I378">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J378" t="str">
         <v>reforma_integral</v>
@@ -14793,19 +14793,19 @@
         <v>200</v>
       </c>
       <c r="E379">
-        <v>24177</v>
+        <v>27052</v>
       </c>
       <c r="F379" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G379">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H379">
         <v>0</v>
       </c>
       <c r="I379">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J379" t="str">
         <v>reforma_integral</v>
@@ -14831,19 +14831,19 @@
         <v>200</v>
       </c>
       <c r="E380">
-        <v>31937</v>
+        <v>36703</v>
       </c>
       <c r="F380" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G380">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H380">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I380">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J380" t="str">
         <v>reforma_integral</v>
@@ -14869,19 +14869,19 @@
         <v>200</v>
       </c>
       <c r="E381">
-        <v>14835</v>
+        <v>39299</v>
       </c>
       <c r="F381" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G381">
+        <v>13</v>
+      </c>
+      <c r="H381">
         <v>1</v>
       </c>
-      <c r="H381">
-        <v>0</v>
-      </c>
       <c r="I381">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J381" t="str">
         <v>reforma_integral</v>
@@ -14907,19 +14907,19 @@
         <v>200</v>
       </c>
       <c r="E382">
-        <v>11792</v>
+        <v>11121</v>
       </c>
       <c r="F382" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G382">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H382">
         <v>1</v>
       </c>
       <c r="I382">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J382" t="str">
         <v>persianas</v>
@@ -14945,19 +14945,19 @@
         <v>200</v>
       </c>
       <c r="E383">
-        <v>17970</v>
+        <v>13369</v>
       </c>
       <c r="F383" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G383">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H383">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I383">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J383" t="str">
         <v>persianas</v>
@@ -14983,7 +14983,7 @@
         <v>200</v>
       </c>
       <c r="E384">
-        <v>12223</v>
+        <v>12193</v>
       </c>
       <c r="F384" t="str">
         <v>OK_MIXTO</v>
@@ -15021,19 +15021,19 @@
         <v>200</v>
       </c>
       <c r="E385">
-        <v>12590</v>
+        <v>13653</v>
       </c>
       <c r="F385" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G385">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H385">
         <v>2</v>
       </c>
       <c r="I385">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J385" t="str">
         <v>persianas</v>
@@ -15059,7 +15059,7 @@
         <v>200</v>
       </c>
       <c r="E386">
-        <v>15578</v>
+        <v>17762</v>
       </c>
       <c r="F386" t="str">
         <v>OK_MIXTO</v>
@@ -15097,25 +15097,25 @@
         <v>200</v>
       </c>
       <c r="E387">
-        <v>11830</v>
+        <v>12210</v>
       </c>
       <c r="F387" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G387">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H387">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I387">
         <v>3</v>
       </c>
       <c r="J387" t="str">
-        <v>persianas</v>
+        <v>carpinteria</v>
       </c>
       <c r="K387" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L387" t="str">
         <v/>
@@ -15135,7 +15135,7 @@
         <v>200</v>
       </c>
       <c r="E388">
-        <v>18118</v>
+        <v>18663</v>
       </c>
       <c r="F388" t="str">
         <v>OK_MIXTO</v>
@@ -15173,16 +15173,16 @@
         <v>200</v>
       </c>
       <c r="E389">
-        <v>17940</v>
+        <v>15963</v>
       </c>
       <c r="F389" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G389">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H389">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I389">
         <v>4</v>
@@ -15211,7 +15211,7 @@
         <v>200</v>
       </c>
       <c r="E390">
-        <v>17937</v>
+        <v>19468</v>
       </c>
       <c r="F390" t="str">
         <v>OK_MIXTO</v>
@@ -15249,16 +15249,16 @@
         <v>200</v>
       </c>
       <c r="E391">
-        <v>10812</v>
+        <v>11230</v>
       </c>
       <c r="F391" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G391">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H391">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I391">
         <v>1</v>
@@ -15287,7 +15287,7 @@
         <v>200</v>
       </c>
       <c r="E392">
-        <v>19667</v>
+        <v>15346</v>
       </c>
       <c r="F392" t="str">
         <v>OK_MIXTO</v>
@@ -15325,7 +15325,7 @@
         <v>200</v>
       </c>
       <c r="E393">
-        <v>13063</v>
+        <v>16266</v>
       </c>
       <c r="F393" t="str">
         <v>OK_MIXTO</v>
@@ -15363,19 +15363,19 @@
         <v>200</v>
       </c>
       <c r="E394">
-        <v>18078</v>
+        <v>21306</v>
       </c>
       <c r="F394" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G394">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H394">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I394">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J394" t="str">
         <v>persianas</v>
@@ -15401,19 +15401,19 @@
         <v>200</v>
       </c>
       <c r="E395">
-        <v>23647</v>
+        <v>18005</v>
       </c>
       <c r="F395" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G395">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H395">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I395">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J395" t="str">
         <v>persianas</v>
@@ -15439,16 +15439,16 @@
         <v>200</v>
       </c>
       <c r="E396">
-        <v>11217</v>
+        <v>12212</v>
       </c>
       <c r="F396" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G396">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H396">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I396">
         <v>2</v>
@@ -15477,16 +15477,16 @@
         <v>200</v>
       </c>
       <c r="E397">
-        <v>13878</v>
+        <v>14211</v>
       </c>
       <c r="F397" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G397">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H397">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I397">
         <v>2</v>
@@ -15515,7 +15515,7 @@
         <v>200</v>
       </c>
       <c r="E398">
-        <v>11940</v>
+        <v>12054</v>
       </c>
       <c r="F398" t="str">
         <v>OK_MIXTO</v>
@@ -15553,7 +15553,7 @@
         <v>200</v>
       </c>
       <c r="E399">
-        <v>11237</v>
+        <v>10946</v>
       </c>
       <c r="F399" t="str">
         <v>OK_MIXTO</v>
@@ -15591,16 +15591,16 @@
         <v>200</v>
       </c>
       <c r="E400">
-        <v>13776</v>
+        <v>16666</v>
       </c>
       <c r="F400" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G400">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H400">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I400">
         <v>5</v>
@@ -15629,19 +15629,19 @@
         <v>200</v>
       </c>
       <c r="E401">
-        <v>22582</v>
+        <v>22737</v>
       </c>
       <c r="F401" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G401">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H401">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I401">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J401" t="str">
         <v>cerrajeria</v>
@@ -15741,10 +15741,10 @@
         <v>95%</v>
       </c>
       <c r="J2" t="str">
-        <v>60%</v>
+        <v>55%</v>
       </c>
       <c r="K2">
-        <v>19363</v>
+        <v>19284</v>
       </c>
     </row>
     <row r="3">
@@ -15758,10 +15758,10 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -15773,13 +15773,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>90%</v>
+        <v>95%</v>
       </c>
       <c r="J3" t="str">
-        <v>80%</v>
+        <v>85%</v>
       </c>
       <c r="K3">
-        <v>16648</v>
+        <v>15879</v>
       </c>
     </row>
     <row r="4">
@@ -15814,7 +15814,7 @@
         <v>80%</v>
       </c>
       <c r="K4">
-        <v>15024</v>
+        <v>13705</v>
       </c>
     </row>
     <row r="5">
@@ -15831,10 +15831,10 @@
         <v>19</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -15846,10 +15846,10 @@
         <v>95%</v>
       </c>
       <c r="J5" t="str">
-        <v>75%</v>
+        <v>80%</v>
       </c>
       <c r="K5">
-        <v>21546</v>
+        <v>20142</v>
       </c>
     </row>
     <row r="6">
@@ -15863,13 +15863,13 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -15878,13 +15878,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>75%</v>
+        <v>90%</v>
       </c>
       <c r="J6" t="str">
-        <v>80%</v>
+        <v>90%</v>
       </c>
       <c r="K6">
-        <v>21372</v>
+        <v>20694</v>
       </c>
     </row>
     <row r="7">
@@ -15919,7 +15919,7 @@
         <v>85%</v>
       </c>
       <c r="K7">
-        <v>15460</v>
+        <v>15266</v>
       </c>
     </row>
     <row r="8">
@@ -15933,10 +15933,10 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -15948,13 +15948,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v>95%</v>
+        <v>100%</v>
       </c>
       <c r="J8" t="str">
-        <v>80%</v>
+        <v>75%</v>
       </c>
       <c r="K8">
-        <v>16378</v>
+        <v>16894</v>
       </c>
     </row>
     <row r="9">
@@ -15965,13 +15965,13 @@
         <v>20</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>16</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>2</v>
@@ -15983,13 +15983,13 @@
         <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v>80%</v>
+        <v>85%</v>
       </c>
       <c r="J9" t="str">
         <v>85%</v>
       </c>
       <c r="K9">
-        <v>21698</v>
+        <v>21066</v>
       </c>
     </row>
     <row r="10">
@@ -16003,10 +16003,10 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -16018,13 +16018,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>95%</v>
+        <v>90%</v>
       </c>
       <c r="J10" t="str">
-        <v>70%</v>
+        <v>75%</v>
       </c>
       <c r="K10">
-        <v>20126</v>
+        <v>18598</v>
       </c>
     </row>
     <row r="11">
@@ -16038,13 +16038,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -16053,13 +16053,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>85%</v>
+        <v>100%</v>
       </c>
       <c r="J11" t="str">
-        <v>70%</v>
+        <v>75%</v>
       </c>
       <c r="K11">
-        <v>16837</v>
+        <v>16893</v>
       </c>
     </row>
     <row r="12">
@@ -16073,10 +16073,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -16088,13 +16088,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>85%</v>
+        <v>80%</v>
       </c>
       <c r="J12" t="str">
-        <v>80%</v>
+        <v>95%</v>
       </c>
       <c r="K12">
-        <v>20266</v>
+        <v>20224</v>
       </c>
     </row>
     <row r="13">
@@ -16105,13 +16105,13 @@
         <v>20</v>
       </c>
       <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>19</v>
+      </c>
+      <c r="E13">
         <v>1</v>
-      </c>
-      <c r="D13">
-        <v>17</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -16123,13 +16123,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>90%</v>
+        <v>95%</v>
       </c>
       <c r="J13" t="str">
         <v>85%</v>
       </c>
       <c r="K13">
-        <v>16543</v>
+        <v>15492</v>
       </c>
     </row>
     <row r="14">
@@ -16164,7 +16164,7 @@
         <v>30%</v>
       </c>
       <c r="K14">
-        <v>13662</v>
+        <v>13357</v>
       </c>
     </row>
     <row r="15">
@@ -16196,10 +16196,10 @@
         <v>100%</v>
       </c>
       <c r="J15" t="str">
-        <v>75%</v>
+        <v>70%</v>
       </c>
       <c r="K15">
-        <v>15294</v>
+        <v>15269</v>
       </c>
     </row>
     <row r="16">
@@ -16213,10 +16213,10 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -16228,13 +16228,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="str">
-        <v>85%</v>
+        <v>90%</v>
       </c>
       <c r="J16" t="str">
-        <v>75%</v>
+        <v>70%</v>
       </c>
       <c r="K16">
-        <v>14832</v>
+        <v>14117</v>
       </c>
     </row>
     <row r="17">
@@ -16248,10 +16248,10 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -16263,13 +16263,13 @@
         <v>0</v>
       </c>
       <c r="I17" t="str">
-        <v>100%</v>
+        <v>95%</v>
       </c>
       <c r="J17" t="str">
         <v>95%</v>
       </c>
       <c r="K17">
-        <v>19391</v>
+        <v>17992</v>
       </c>
     </row>
     <row r="18">
@@ -16283,13 +16283,13 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18">
         <v>7</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -16298,13 +16298,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>60%</v>
+        <v>65%</v>
       </c>
       <c r="J18" t="str">
         <v>0%</v>
       </c>
       <c r="K18">
-        <v>31163</v>
+        <v>31969</v>
       </c>
     </row>
     <row r="19">
@@ -16318,10 +16318,10 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -16333,13 +16333,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>95%</v>
+        <v>90%</v>
       </c>
       <c r="J19" t="str">
         <v>75%</v>
       </c>
       <c r="K19">
-        <v>18290</v>
+        <v>17499</v>
       </c>
     </row>
     <row r="20">
@@ -16353,10 +16353,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -16368,13 +16368,13 @@
         <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>90%</v>
+        <v>95%</v>
       </c>
       <c r="J20" t="str">
         <v>70%</v>
       </c>
       <c r="K20">
-        <v>20187</v>
+        <v>17528</v>
       </c>
     </row>
     <row r="21">
@@ -16388,10 +16388,10 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -16403,13 +16403,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="str">
-        <v>95%</v>
+        <v>100%</v>
       </c>
       <c r="J21" t="str">
         <v>100%</v>
       </c>
       <c r="K21">
-        <v>18073</v>
+        <v>16493</v>
       </c>
     </row>
     <row r="22">
@@ -16423,13 +16423,13 @@
         <v>2</v>
       </c>
       <c r="D22">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="E22">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -16438,13 +16438,13 @@
         <v>0</v>
       </c>
       <c r="I22" t="str">
-        <v>90%</v>
+        <v>92%</v>
       </c>
       <c r="J22" t="str">
-        <v>73%</v>
+        <v>74%</v>
       </c>
       <c r="K22">
-        <v>18608</v>
+        <v>17918</v>
       </c>
     </row>
   </sheetData>
@@ -16456,7 +16456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H5"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -16496,19 +16496,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="B2" t="str">
-        <v>Fontanería</v>
+        <v>Energía Solar</v>
       </c>
       <c r="C2" t="str">
-        <v>Cambio de bañera por plato de ducha en baño principal de 90x90 con mamparas</v>
+        <v>Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético</v>
       </c>
       <c r="D2">
         <v>200</v>
       </c>
       <c r="E2">
-        <v>28714</v>
+        <v>27042</v>
       </c>
       <c r="F2" t="str">
         <v>VACIO</v>
@@ -16517,24 +16517,24 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>{"transcript":"Cambio de bañera por plato de ducha en baño principal de 90x90 con mamparas","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":{"subtotal":0,"</v>
+        <v>{"transcript":"Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>7</v>
+        <v>239</v>
       </c>
       <c r="B3" t="str">
-        <v>Fontanería</v>
+        <v>Energía Solar</v>
       </c>
       <c r="C3" t="str">
-        <v>Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad</v>
+        <v>Proyecto de comunidad energética solar en barrio, 20 viviendas participantes, gestoría incluida</v>
       </c>
       <c r="D3">
         <v>200</v>
       </c>
       <c r="E3">
-        <v>25516</v>
+        <v>26750</v>
       </c>
       <c r="F3" t="str">
         <v>VACIO</v>
@@ -16543,194 +16543,64 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>{"transcript":"Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados</v>
+        <v>{"transcript":"Proyecto de comunidad energética solar en barrio, 20 viviendas participantes, gestoría incluida","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calcu</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>106</v>
+        <v>341</v>
       </c>
       <c r="B4" t="str">
-        <v>Climatización</v>
+        <v>Mantenimiento General</v>
       </c>
       <c r="C4" t="str">
-        <v>Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados</v>
+        <v>Contrato de mantenimiento mensual de edificio de oficinas, electricidad, fontanería y carpintería</v>
       </c>
       <c r="D4">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="E4">
-        <v>25810</v>
+        <v>217</v>
       </c>
       <c r="F4" t="str">
-        <v>VACIO</v>
+        <v>ERROR_TECNICO</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
       </c>
       <c r="H4" t="str">
-        <v>{"transcript":"Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":{"su</v>
+        <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>229</v>
+        <v>346</v>
       </c>
       <c r="B5" t="str">
-        <v>Energía Solar</v>
+        <v>Mantenimiento General</v>
       </c>
       <c r="C5" t="str">
-        <v>Instalar cargador de coche eléctrico alimentado por energía solar con gestión inteligente de carga</v>
+        <v>Contrato anual de mantenimiento de comunidad de vecinos, incluye piscina, jardines y zonas comunes</v>
       </c>
       <c r="D5">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="E5">
-        <v>29018</v>
+        <v>194</v>
       </c>
       <c r="F5" t="str">
-        <v>VACIO</v>
+        <v>ERROR_TECNICO</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
       </c>
       <c r="H5" t="str">
-        <v>{"transcript":"Instalar cargador de coche eléctrico alimentado por energía solar con gestión inteligente de carga","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"ca</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>235</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Energía Solar</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético</v>
-      </c>
-      <c r="D6">
-        <v>200</v>
-      </c>
-      <c r="E6">
-        <v>27526</v>
-      </c>
-      <c r="F6" t="str">
-        <v>VACIO</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v>{"transcript":"Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>320</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Contra Incendios</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Instalar detección temprana de incendios en archivo de documentación, sistema de aspiración VESDA</v>
-      </c>
-      <c r="D7">
-        <v>200</v>
-      </c>
-      <c r="E7">
-        <v>30714</v>
-      </c>
-      <c r="F7" t="str">
-        <v>VACIO</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v>{"transcript":"Instalar detección temprana de incendios en archivo de documentación, sistema de aspiración VESDA","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>341</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Mantenimiento General</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Contrato de mantenimiento mensual de edificio de oficinas, electricidad, fontanería y carpintería</v>
-      </c>
-      <c r="D8">
-        <v>403</v>
-      </c>
-      <c r="E8">
-        <v>788</v>
-      </c>
-      <c r="F8" t="str">
-        <v>ERROR_TECNICO</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
-      </c>
-      <c r="H8" t="str">
         <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>346</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Mantenimiento General</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Contrato anual de mantenimiento de comunidad de vecinos, incluye piscina, jardines y zonas comunes</v>
-      </c>
-      <c r="D9">
-        <v>403</v>
-      </c>
-      <c r="E9">
-        <v>732</v>
-      </c>
-      <c r="F9" t="str">
-        <v>ERROR_TECNICO</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
-      </c>
-      <c r="H9" t="str">
-        <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>364</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Reformas Integrales</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Convertir local comercial en vivienda de 60 metros cuadrados con licencia de cambio de uso</v>
-      </c>
-      <c r="D10">
-        <v>200</v>
-      </c>
-      <c r="E10">
-        <v>48627</v>
-      </c>
-      <c r="F10" t="str">
-        <v>VACIO</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v>{"transcript":"Convertir local comercial en vivienda de 60 metros cuadrados con licencia de cambio de uso","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/scripts/test-motor-ia/output/test_results.xlsx
+++ b/scripts/test-motor-ia/output/test_results.xlsx
@@ -467,7 +467,7 @@
         <v>200</v>
       </c>
       <c r="E2">
-        <v>10736</v>
+        <v>11045</v>
       </c>
       <c r="F2" t="str">
         <v>OK_MIXTO</v>
@@ -505,7 +505,7 @@
         <v>200</v>
       </c>
       <c r="E3">
-        <v>19738</v>
+        <v>20289</v>
       </c>
       <c r="F3" t="str">
         <v>OK_MIXTO</v>
@@ -514,10 +514,10 @@
         <v>11</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J3" t="str">
         <v>fontaneria</v>
@@ -543,19 +543,19 @@
         <v>200</v>
       </c>
       <c r="E4">
-        <v>11222</v>
+        <v>14072</v>
       </c>
       <c r="F4" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="str">
         <v>fontaneria</v>
@@ -581,7 +581,7 @@
         <v>200</v>
       </c>
       <c r="E5">
-        <v>12437</v>
+        <v>11950</v>
       </c>
       <c r="F5" t="str">
         <v>OK_MIXTO</v>
@@ -619,19 +619,19 @@
         <v>200</v>
       </c>
       <c r="E6">
-        <v>16294</v>
+        <v>17471</v>
       </c>
       <c r="F6" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J6" t="str">
         <v>fontaneria</v>
@@ -657,7 +657,7 @@
         <v>200</v>
       </c>
       <c r="E7">
-        <v>17511</v>
+        <v>15927</v>
       </c>
       <c r="F7" t="str">
         <v>OK_MIXTO</v>
@@ -695,22 +695,22 @@
         <v>200</v>
       </c>
       <c r="E8">
-        <v>23451</v>
+        <v>23251</v>
       </c>
       <c r="F8" t="str">
-        <v>OK_MIXTO</v>
+        <v>VACIO</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" t="str">
-        <v>reforma_integral</v>
+        <v/>
       </c>
       <c r="K8" t="str">
         <v>NO</v>
@@ -733,7 +733,7 @@
         <v>200</v>
       </c>
       <c r="E9">
-        <v>17907</v>
+        <v>15650</v>
       </c>
       <c r="F9" t="str">
         <v>OK_MIXTO</v>
@@ -742,10 +742,10 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="str">
         <v>climatizacion</v>
@@ -771,19 +771,19 @@
         <v>200</v>
       </c>
       <c r="E10">
-        <v>18601</v>
+        <v>17661</v>
       </c>
       <c r="F10" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H10">
         <v>5</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" t="str">
         <v>fontaneria</v>
@@ -809,19 +809,19 @@
         <v>200</v>
       </c>
       <c r="E11">
-        <v>13736</v>
+        <v>11770</v>
       </c>
       <c r="F11" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J11" t="str">
         <v>fontaneria</v>
@@ -847,7 +847,7 @@
         <v>200</v>
       </c>
       <c r="E12">
-        <v>12937</v>
+        <v>13856</v>
       </c>
       <c r="F12" t="str">
         <v>OK_MIXTO</v>
@@ -885,19 +885,19 @@
         <v>200</v>
       </c>
       <c r="E13">
-        <v>18383</v>
+        <v>17364</v>
       </c>
       <c r="F13" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" t="str">
         <v>fontaneria</v>
@@ -923,7 +923,7 @@
         <v>200</v>
       </c>
       <c r="E14">
-        <v>16971</v>
+        <v>15850</v>
       </c>
       <c r="F14" t="str">
         <v>OK_MIXTO</v>
@@ -961,7 +961,7 @@
         <v>200</v>
       </c>
       <c r="E15">
-        <v>12442</v>
+        <v>12211</v>
       </c>
       <c r="F15" t="str">
         <v>OK_MIXTO</v>
@@ -999,7 +999,7 @@
         <v>200</v>
       </c>
       <c r="E16">
-        <v>19812</v>
+        <v>16991</v>
       </c>
       <c r="F16" t="str">
         <v>OK_MIXTO</v>
@@ -1037,7 +1037,7 @@
         <v>200</v>
       </c>
       <c r="E17">
-        <v>27310</v>
+        <v>21587</v>
       </c>
       <c r="F17" t="str">
         <v>OK_MIXTO</v>
@@ -1075,19 +1075,19 @@
         <v>200</v>
       </c>
       <c r="E18">
-        <v>22851</v>
+        <v>22701</v>
       </c>
       <c r="F18" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18" t="str">
         <v>fontaneria</v>
@@ -1113,19 +1113,19 @@
         <v>200</v>
       </c>
       <c r="E19">
-        <v>20529</v>
+        <v>12846</v>
       </c>
       <c r="F19" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J19" t="str">
         <v>fontaneria</v>
@@ -1151,16 +1151,16 @@
         <v>200</v>
       </c>
       <c r="E20">
-        <v>14196</v>
+        <v>13565</v>
       </c>
       <c r="F20" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I20">
         <v>3</v>
@@ -1189,7 +1189,7 @@
         <v>200</v>
       </c>
       <c r="E21">
-        <v>10797</v>
+        <v>10902</v>
       </c>
       <c r="F21" t="str">
         <v>OK_MIXTO</v>
@@ -1227,7 +1227,7 @@
         <v>200</v>
       </c>
       <c r="E22">
-        <v>15634</v>
+        <v>14719</v>
       </c>
       <c r="F22" t="str">
         <v>OK_MIXTO</v>
@@ -1265,19 +1265,19 @@
         <v>200</v>
       </c>
       <c r="E23">
-        <v>22540</v>
+        <v>19466</v>
       </c>
       <c r="F23" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J23" t="str">
         <v>electricidad</v>
@@ -1286,7 +1286,7 @@
         <v>SI</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="24">
@@ -1303,16 +1303,16 @@
         <v>200</v>
       </c>
       <c r="E24">
-        <v>23008</v>
+        <v>21630</v>
       </c>
       <c r="F24" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I24">
         <v>5</v>
@@ -1341,7 +1341,7 @@
         <v>200</v>
       </c>
       <c r="E25">
-        <v>23650</v>
+        <v>21832</v>
       </c>
       <c r="F25" t="str">
         <v>OK_MIXTO</v>
@@ -1350,10 +1350,10 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J25" t="str">
         <v>electricidad</v>
@@ -1379,19 +1379,19 @@
         <v>200</v>
       </c>
       <c r="E26">
-        <v>8730</v>
+        <v>11160</v>
       </c>
       <c r="F26" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>2</v>
       </c>
       <c r="I26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" t="str">
         <v>electricidad</v>
@@ -1417,7 +1417,7 @@
         <v>200</v>
       </c>
       <c r="E27">
-        <v>13599</v>
+        <v>12842</v>
       </c>
       <c r="F27" t="str">
         <v>OK_MIXTO</v>
@@ -1426,10 +1426,10 @@
         <v>6</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" t="str">
         <v>electricidad</v>
@@ -1455,7 +1455,7 @@
         <v>200</v>
       </c>
       <c r="E28">
-        <v>14629</v>
+        <v>13611</v>
       </c>
       <c r="F28" t="str">
         <v>OK_MIXTO</v>
@@ -1493,19 +1493,19 @@
         <v>200</v>
       </c>
       <c r="E29">
-        <v>19489</v>
+        <v>19505</v>
       </c>
       <c r="F29" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>4</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" t="str">
         <v>electricidad</v>
@@ -1531,7 +1531,7 @@
         <v>200</v>
       </c>
       <c r="E30">
-        <v>10691</v>
+        <v>10564</v>
       </c>
       <c r="F30" t="str">
         <v>OK_MIXTO</v>
@@ -1569,7 +1569,7 @@
         <v>200</v>
       </c>
       <c r="E31">
-        <v>20583</v>
+        <v>19840</v>
       </c>
       <c r="F31" t="str">
         <v>OK_MIXTO</v>
@@ -1607,16 +1607,16 @@
         <v>200</v>
       </c>
       <c r="E32">
-        <v>21782</v>
+        <v>20456</v>
       </c>
       <c r="F32" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>3</v>
@@ -1645,7 +1645,7 @@
         <v>200</v>
       </c>
       <c r="E33">
-        <v>13230</v>
+        <v>13643</v>
       </c>
       <c r="F33" t="str">
         <v>OK_MIXTO</v>
@@ -1683,19 +1683,19 @@
         <v>200</v>
       </c>
       <c r="E34">
-        <v>14135</v>
+        <v>15217</v>
       </c>
       <c r="F34" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" t="str">
         <v>pladur_escayola</v>
@@ -1721,19 +1721,19 @@
         <v>200</v>
       </c>
       <c r="E35">
-        <v>20881</v>
+        <v>21902</v>
       </c>
       <c r="F35" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J35" t="str">
         <v>climatizacion</v>
@@ -1759,16 +1759,16 @@
         <v>200</v>
       </c>
       <c r="E36">
-        <v>17604</v>
+        <v>19089</v>
       </c>
       <c r="F36" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36">
         <v>5</v>
@@ -1797,16 +1797,16 @@
         <v>200</v>
       </c>
       <c r="E37">
-        <v>12649</v>
+        <v>12403</v>
       </c>
       <c r="F37" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>3</v>
@@ -1835,19 +1835,19 @@
         <v>200</v>
       </c>
       <c r="E38">
-        <v>18061</v>
+        <v>15734</v>
       </c>
       <c r="F38" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38">
         <v>5</v>
       </c>
       <c r="I38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J38" t="str">
         <v>electricidad</v>
@@ -1873,19 +1873,19 @@
         <v>200</v>
       </c>
       <c r="E39">
-        <v>22144</v>
+        <v>18635</v>
       </c>
       <c r="F39" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G39">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J39" t="str">
         <v>electricidad</v>
@@ -1911,16 +1911,16 @@
         <v>200</v>
       </c>
       <c r="E40">
-        <v>15651</v>
+        <v>12978</v>
       </c>
       <c r="F40" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40">
         <v>3</v>
@@ -1949,19 +1949,19 @@
         <v>200</v>
       </c>
       <c r="E41">
-        <v>9192</v>
+        <v>10323</v>
       </c>
       <c r="F41" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="str">
         <v>electricidad</v>
@@ -1987,7 +1987,7 @@
         <v>200</v>
       </c>
       <c r="E42">
-        <v>17459</v>
+        <v>16587</v>
       </c>
       <c r="F42" t="str">
         <v>OK_MIXTO</v>
@@ -2025,7 +2025,7 @@
         <v>200</v>
       </c>
       <c r="E43">
-        <v>10398</v>
+        <v>11287</v>
       </c>
       <c r="F43" t="str">
         <v>OK_MIXTO</v>
@@ -2034,10 +2034,10 @@
         <v>4</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="str">
         <v>carpinteria</v>
@@ -2063,16 +2063,16 @@
         <v>200</v>
       </c>
       <c r="E44">
-        <v>16206</v>
+        <v>17068</v>
       </c>
       <c r="F44" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44">
         <v>5</v>
@@ -2101,19 +2101,19 @@
         <v>200</v>
       </c>
       <c r="E45">
-        <v>11881</v>
+        <v>16180</v>
       </c>
       <c r="F45" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G45">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H45">
         <v>4</v>
       </c>
       <c r="I45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" t="str">
         <v>carpinteria</v>
@@ -2139,7 +2139,7 @@
         <v>200</v>
       </c>
       <c r="E46">
-        <v>13362</v>
+        <v>14881</v>
       </c>
       <c r="F46" t="str">
         <v>OK_MIXTO</v>
@@ -2154,10 +2154,10 @@
         <v>5</v>
       </c>
       <c r="J46" t="str">
-        <v>carpinteria</v>
+        <v>suelos_tarimas</v>
       </c>
       <c r="K46" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2177,7 +2177,7 @@
         <v>200</v>
       </c>
       <c r="E47">
-        <v>14960</v>
+        <v>14442</v>
       </c>
       <c r="F47" t="str">
         <v>OK_MIXTO</v>
@@ -2215,7 +2215,7 @@
         <v>200</v>
       </c>
       <c r="E48">
-        <v>14160</v>
+        <v>14453</v>
       </c>
       <c r="F48" t="str">
         <v>OK_MIXTO</v>
@@ -2253,19 +2253,19 @@
         <v>200</v>
       </c>
       <c r="E49">
-        <v>11738</v>
+        <v>12044</v>
       </c>
       <c r="F49" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J49" t="str">
         <v>carpinteria</v>
@@ -2291,16 +2291,16 @@
         <v>200</v>
       </c>
       <c r="E50">
-        <v>19229</v>
+        <v>19394</v>
       </c>
       <c r="F50" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50">
         <v>5</v>
@@ -2329,19 +2329,19 @@
         <v>200</v>
       </c>
       <c r="E51">
-        <v>22985</v>
+        <v>18420</v>
       </c>
       <c r="F51" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" t="str">
         <v>carpinteria</v>
@@ -2367,7 +2367,7 @@
         <v>200</v>
       </c>
       <c r="E52">
-        <v>14588</v>
+        <v>14279</v>
       </c>
       <c r="F52" t="str">
         <v>OK_MIXTO</v>
@@ -2405,19 +2405,19 @@
         <v>200</v>
       </c>
       <c r="E53">
-        <v>18252</v>
+        <v>19998</v>
       </c>
       <c r="F53" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G53">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H53">
         <v>3</v>
       </c>
       <c r="I53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J53" t="str">
         <v>cerrajeria</v>
@@ -2443,19 +2443,19 @@
         <v>200</v>
       </c>
       <c r="E54">
-        <v>12746</v>
+        <v>16480</v>
       </c>
       <c r="F54" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J54" t="str">
         <v>carpinteria</v>
@@ -2481,7 +2481,7 @@
         <v>200</v>
       </c>
       <c r="E55">
-        <v>21514</v>
+        <v>17308</v>
       </c>
       <c r="F55" t="str">
         <v>OK_MIXTO</v>
@@ -2519,7 +2519,7 @@
         <v>200</v>
       </c>
       <c r="E56">
-        <v>14579</v>
+        <v>14969</v>
       </c>
       <c r="F56" t="str">
         <v>OK_MIXTO</v>
@@ -2557,7 +2557,7 @@
         <v>200</v>
       </c>
       <c r="E57">
-        <v>13659</v>
+        <v>13157</v>
       </c>
       <c r="F57" t="str">
         <v>OK_MIXTO</v>
@@ -2595,16 +2595,16 @@
         <v>200</v>
       </c>
       <c r="E58">
-        <v>15684</v>
+        <v>17964</v>
       </c>
       <c r="F58" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G58">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58">
         <v>3</v>
@@ -2633,19 +2633,19 @@
         <v>200</v>
       </c>
       <c r="E59">
-        <v>23976</v>
+        <v>14892</v>
       </c>
       <c r="F59" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G59">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I59">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J59" t="str">
         <v>carpinteria</v>
@@ -2671,19 +2671,19 @@
         <v>200</v>
       </c>
       <c r="E60">
-        <v>12656</v>
+        <v>14944</v>
       </c>
       <c r="F60" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H60">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" t="str">
         <v>persianas</v>
@@ -2709,7 +2709,7 @@
         <v>200</v>
       </c>
       <c r="E61">
-        <v>17554</v>
+        <v>15616</v>
       </c>
       <c r="F61" t="str">
         <v>OK_MIXTO</v>
@@ -2747,7 +2747,7 @@
         <v>200</v>
       </c>
       <c r="E62">
-        <v>11485</v>
+        <v>11414</v>
       </c>
       <c r="F62" t="str">
         <v>OK_MIXTO</v>
@@ -2785,16 +2785,16 @@
         <v>200</v>
       </c>
       <c r="E63">
-        <v>13451</v>
+        <v>13135</v>
       </c>
       <c r="F63" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G63">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I63">
         <v>3</v>
@@ -2823,25 +2823,25 @@
         <v>200</v>
       </c>
       <c r="E64">
-        <v>21606</v>
+        <v>15053</v>
       </c>
       <c r="F64" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>5</v>
       </c>
       <c r="J64" t="str">
-        <v>pladur_escayola</v>
+        <v>pintura</v>
       </c>
       <c r="K64" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -2861,19 +2861,19 @@
         <v>200</v>
       </c>
       <c r="E65">
-        <v>24951</v>
+        <v>21766</v>
       </c>
       <c r="F65" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G65">
         <v>7</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J65" t="str">
         <v>impermeabilizacion</v>
@@ -2899,19 +2899,19 @@
         <v>200</v>
       </c>
       <c r="E66">
-        <v>10188</v>
+        <v>14339</v>
       </c>
       <c r="F66" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H66">
         <v>2</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66" t="str">
         <v>pintura</v>
@@ -2937,19 +2937,19 @@
         <v>200</v>
       </c>
       <c r="E67">
-        <v>12482</v>
+        <v>12508</v>
       </c>
       <c r="F67" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H67">
         <v>3</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J67" t="str">
         <v>pintura</v>
@@ -2975,19 +2975,19 @@
         <v>200</v>
       </c>
       <c r="E68">
-        <v>10628</v>
+        <v>13486</v>
       </c>
       <c r="F68" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H68">
         <v>2</v>
       </c>
       <c r="I68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J68" t="str">
         <v>pintura</v>
@@ -3013,19 +3013,19 @@
         <v>200</v>
       </c>
       <c r="E69">
-        <v>11541</v>
+        <v>15042</v>
       </c>
       <c r="F69" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G69">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H69">
         <v>5</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J69" t="str">
         <v>pintura</v>
@@ -3051,7 +3051,7 @@
         <v>200</v>
       </c>
       <c r="E70">
-        <v>16129</v>
+        <v>13479</v>
       </c>
       <c r="F70" t="str">
         <v>OK_MIXTO</v>
@@ -3089,7 +3089,7 @@
         <v>200</v>
       </c>
       <c r="E71">
-        <v>16917</v>
+        <v>14707</v>
       </c>
       <c r="F71" t="str">
         <v>OK_MIXTO</v>
@@ -3098,10 +3098,10 @@
         <v>6</v>
       </c>
       <c r="H71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" t="str">
         <v>pintura</v>
@@ -3127,7 +3127,7 @@
         <v>200</v>
       </c>
       <c r="E72">
-        <v>12815</v>
+        <v>11467</v>
       </c>
       <c r="F72" t="str">
         <v>OK_MIXTO</v>
@@ -3165,7 +3165,7 @@
         <v>200</v>
       </c>
       <c r="E73">
-        <v>15627</v>
+        <v>14141</v>
       </c>
       <c r="F73" t="str">
         <v>OK_MIXTO</v>
@@ -3203,7 +3203,7 @@
         <v>200</v>
       </c>
       <c r="E74">
-        <v>16298</v>
+        <v>16913</v>
       </c>
       <c r="F74" t="str">
         <v>OK_MIXTO</v>
@@ -3212,10 +3212,10 @@
         <v>6</v>
       </c>
       <c r="H74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="str">
         <v>pintura</v>
@@ -3241,19 +3241,19 @@
         <v>200</v>
       </c>
       <c r="E75">
-        <v>20117</v>
+        <v>18551</v>
       </c>
       <c r="F75" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G75">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J75" t="str">
         <v>albanileria</v>
@@ -3279,7 +3279,7 @@
         <v>200</v>
       </c>
       <c r="E76">
-        <v>12903</v>
+        <v>12380</v>
       </c>
       <c r="F76" t="str">
         <v>OK_MIXTO</v>
@@ -3317,19 +3317,19 @@
         <v>200</v>
       </c>
       <c r="E77">
-        <v>8188</v>
+        <v>9492</v>
       </c>
       <c r="F77" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H77">
         <v>2</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J77" t="str">
         <v>pintura</v>
@@ -3355,7 +3355,7 @@
         <v>200</v>
       </c>
       <c r="E78">
-        <v>11875</v>
+        <v>11680</v>
       </c>
       <c r="F78" t="str">
         <v>OK_MIXTO</v>
@@ -3364,10 +3364,10 @@
         <v>5</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J78" t="str">
         <v>fachadas</v>
@@ -3393,7 +3393,7 @@
         <v>200</v>
       </c>
       <c r="E79">
-        <v>12661</v>
+        <v>12862</v>
       </c>
       <c r="F79" t="str">
         <v>OK_MIXTO</v>
@@ -3402,10 +3402,10 @@
         <v>6</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J79" t="str">
         <v>pintura</v>
@@ -3431,16 +3431,16 @@
         <v>200</v>
       </c>
       <c r="E80">
-        <v>10854</v>
+        <v>12436</v>
       </c>
       <c r="F80" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G80">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I80">
         <v>4</v>
@@ -3469,19 +3469,19 @@
         <v>200</v>
       </c>
       <c r="E81">
-        <v>11615</v>
+        <v>11414</v>
       </c>
       <c r="F81" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G81">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H81">
         <v>3</v>
       </c>
       <c r="I81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J81" t="str">
         <v>pintura</v>
@@ -3507,19 +3507,19 @@
         <v>200</v>
       </c>
       <c r="E82">
-        <v>16698</v>
+        <v>16138</v>
       </c>
       <c r="F82" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82">
+        <v>3</v>
+      </c>
+      <c r="I82">
         <v>1</v>
-      </c>
-      <c r="I82">
-        <v>2</v>
       </c>
       <c r="J82" t="str">
         <v>albanileria</v>
@@ -3545,7 +3545,7 @@
         <v>200</v>
       </c>
       <c r="E83">
-        <v>17040</v>
+        <v>15303</v>
       </c>
       <c r="F83" t="str">
         <v>OK_MIXTO</v>
@@ -3554,10 +3554,10 @@
         <v>6</v>
       </c>
       <c r="H83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J83" t="str">
         <v>albanileria</v>
@@ -3583,19 +3583,19 @@
         <v>200</v>
       </c>
       <c r="E84">
-        <v>17332</v>
+        <v>15171</v>
       </c>
       <c r="F84" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G84">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H84">
         <v>3</v>
       </c>
       <c r="I84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J84" t="str">
         <v>fachadas</v>
@@ -3621,19 +3621,19 @@
         <v>200</v>
       </c>
       <c r="E85">
-        <v>18956</v>
+        <v>19079</v>
       </c>
       <c r="F85" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G85">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H85">
         <v>4</v>
       </c>
       <c r="I85">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J85" t="str">
         <v>albanileria</v>
@@ -3659,7 +3659,7 @@
         <v>200</v>
       </c>
       <c r="E86">
-        <v>23089</v>
+        <v>17056</v>
       </c>
       <c r="F86" t="str">
         <v>OK_MIXTO</v>
@@ -3697,16 +3697,16 @@
         <v>200</v>
       </c>
       <c r="E87">
-        <v>12167</v>
+        <v>19608</v>
       </c>
       <c r="F87" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G87">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I87">
         <v>4</v>
@@ -3735,7 +3735,7 @@
         <v>200</v>
       </c>
       <c r="E88">
-        <v>13789</v>
+        <v>12828</v>
       </c>
       <c r="F88" t="str">
         <v>OK_MIXTO</v>
@@ -3773,19 +3773,19 @@
         <v>200</v>
       </c>
       <c r="E89">
-        <v>14155</v>
+        <v>15931</v>
       </c>
       <c r="F89" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G89">
+        <v>9</v>
+      </c>
+      <c r="H89">
+        <v>3</v>
+      </c>
+      <c r="I89">
         <v>6</v>
-      </c>
-      <c r="H89">
-        <v>2</v>
-      </c>
-      <c r="I89">
-        <v>4</v>
       </c>
       <c r="J89" t="str">
         <v>albanileria</v>
@@ -3811,7 +3811,7 @@
         <v>200</v>
       </c>
       <c r="E90">
-        <v>18637</v>
+        <v>17995</v>
       </c>
       <c r="F90" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -3849,19 +3849,19 @@
         <v>200</v>
       </c>
       <c r="E91">
-        <v>14032</v>
+        <v>19675</v>
       </c>
       <c r="F91" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G91">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H91">
         <v>4</v>
       </c>
       <c r="I91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J91" t="str">
         <v>fachadas</v>
@@ -3887,7 +3887,7 @@
         <v>200</v>
       </c>
       <c r="E92">
-        <v>14178</v>
+        <v>15394</v>
       </c>
       <c r="F92" t="str">
         <v>OK_MIXTO</v>
@@ -3896,10 +3896,10 @@
         <v>8</v>
       </c>
       <c r="H92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J92" t="str">
         <v>albanileria</v>
@@ -3925,7 +3925,7 @@
         <v>200</v>
       </c>
       <c r="E93">
-        <v>17512</v>
+        <v>19940</v>
       </c>
       <c r="F93" t="str">
         <v>OK_MIXTO</v>
@@ -3963,19 +3963,19 @@
         <v>200</v>
       </c>
       <c r="E94">
-        <v>41007</v>
+        <v>40737</v>
       </c>
       <c r="F94" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G94">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H94">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I94">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J94" t="str">
         <v>albanileria</v>
@@ -4001,7 +4001,7 @@
         <v>200</v>
       </c>
       <c r="E95">
-        <v>17451</v>
+        <v>17549</v>
       </c>
       <c r="F95" t="str">
         <v>OK_MIXTO</v>
@@ -4039,7 +4039,7 @@
         <v>200</v>
       </c>
       <c r="E96">
-        <v>24457</v>
+        <v>24300</v>
       </c>
       <c r="F96" t="str">
         <v>OK_MIXTO</v>
@@ -4077,19 +4077,19 @@
         <v>200</v>
       </c>
       <c r="E97">
-        <v>21273</v>
+        <v>20934</v>
       </c>
       <c r="F97" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H97">
         <v>3</v>
       </c>
       <c r="I97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J97" t="str">
         <v>persianas</v>
@@ -4115,7 +4115,7 @@
         <v>200</v>
       </c>
       <c r="E98">
-        <v>16906</v>
+        <v>16779</v>
       </c>
       <c r="F98" t="str">
         <v>OK_MIXTO</v>
@@ -4153,19 +4153,19 @@
         <v>200</v>
       </c>
       <c r="E99">
-        <v>28181</v>
+        <v>26721</v>
       </c>
       <c r="F99" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G99">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H99">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J99" t="str">
         <v>reforma_integral</v>
@@ -4191,19 +4191,19 @@
         <v>200</v>
       </c>
       <c r="E100">
-        <v>19754</v>
+        <v>18889</v>
       </c>
       <c r="F100" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G100">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I100">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J100" t="str">
         <v>suelos_alicatados</v>
@@ -4229,7 +4229,7 @@
         <v>200</v>
       </c>
       <c r="E101">
-        <v>19061</v>
+        <v>20421</v>
       </c>
       <c r="F101" t="str">
         <v>OK_MIXTO</v>
@@ -4267,19 +4267,19 @@
         <v>200</v>
       </c>
       <c r="E102">
-        <v>17048</v>
+        <v>15408</v>
       </c>
       <c r="F102" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G102">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H102">
         <v>1</v>
       </c>
       <c r="I102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J102" t="str">
         <v>climatizacion</v>
@@ -4305,7 +4305,7 @@
         <v>200</v>
       </c>
       <c r="E103">
-        <v>32445</v>
+        <v>29793</v>
       </c>
       <c r="F103" t="str">
         <v>OK_MIXTO</v>
@@ -4314,13 +4314,13 @@
         <v>12</v>
       </c>
       <c r="H103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I103">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J103" t="str">
-        <v>reforma_integral</v>
+        <v>energia_solar</v>
       </c>
       <c r="K103" t="str">
         <v>NO</v>
@@ -4343,19 +4343,19 @@
         <v>200</v>
       </c>
       <c r="E104">
-        <v>23865</v>
+        <v>24135</v>
       </c>
       <c r="F104" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G104">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H104">
         <v>5</v>
       </c>
       <c r="I104">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J104" t="str">
         <v>climatizacion</v>
@@ -4381,19 +4381,19 @@
         <v>200</v>
       </c>
       <c r="E105">
-        <v>12496</v>
+        <v>16666</v>
       </c>
       <c r="F105" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J105" t="str">
         <v>climatizacion</v>
@@ -4402,7 +4402,7 @@
         <v>SI</v>
       </c>
       <c r="L105" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="106">
@@ -4419,16 +4419,16 @@
         <v>200</v>
       </c>
       <c r="E106">
-        <v>21025</v>
+        <v>19228</v>
       </c>
       <c r="F106" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G106">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106">
         <v>7</v>
@@ -4457,25 +4457,25 @@
         <v>200</v>
       </c>
       <c r="E107">
-        <v>28030</v>
+        <v>25232</v>
       </c>
       <c r="F107" t="str">
-        <v>OK_MIXTO</v>
+        <v>VACIO</v>
       </c>
       <c r="G107">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I107">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J107" t="str">
-        <v>climatizacion</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -4495,16 +4495,16 @@
         <v>200</v>
       </c>
       <c r="E108">
-        <v>21526</v>
+        <v>20528</v>
       </c>
       <c r="F108" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G108">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I108">
         <v>9</v>
@@ -4533,7 +4533,7 @@
         <v>200</v>
       </c>
       <c r="E109">
-        <v>17571</v>
+        <v>16432</v>
       </c>
       <c r="F109" t="str">
         <v>OK_MIXTO</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="E110">
-        <v>11566</v>
+        <v>10770</v>
       </c>
       <c r="F110" t="str">
         <v>OK_MIXTO</v>
@@ -4580,10 +4580,10 @@
         <v>6</v>
       </c>
       <c r="H110">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="str">
         <v>climatizacion</v>
@@ -4609,25 +4609,25 @@
         <v>200</v>
       </c>
       <c r="E111">
-        <v>21593</v>
+        <v>18513</v>
       </c>
       <c r="F111" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G111">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H111">
         <v>6</v>
       </c>
       <c r="I111">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J111" t="str">
-        <v>climatizacion</v>
+        <v>electricidad</v>
       </c>
       <c r="K111" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -4647,7 +4647,7 @@
         <v>200</v>
       </c>
       <c r="E112">
-        <v>26717</v>
+        <v>27396</v>
       </c>
       <c r="F112" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -4685,7 +4685,7 @@
         <v>200</v>
       </c>
       <c r="E113">
-        <v>12291</v>
+        <v>12021</v>
       </c>
       <c r="F113" t="str">
         <v>OK_MIXTO</v>
@@ -4694,10 +4694,10 @@
         <v>5</v>
       </c>
       <c r="H113">
+        <v>3</v>
+      </c>
+      <c r="I113">
         <v>2</v>
-      </c>
-      <c r="I113">
-        <v>3</v>
       </c>
       <c r="J113" t="str">
         <v>climatizacion</v>
@@ -4723,19 +4723,19 @@
         <v>200</v>
       </c>
       <c r="E114">
-        <v>20835</v>
+        <v>22509</v>
       </c>
       <c r="F114" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G114">
+        <v>12</v>
+      </c>
+      <c r="H114">
+        <v>5</v>
+      </c>
+      <c r="I114">
         <v>7</v>
-      </c>
-      <c r="H114">
-        <v>1</v>
-      </c>
-      <c r="I114">
-        <v>6</v>
       </c>
       <c r="J114" t="str">
         <v>climatizacion</v>
@@ -4761,16 +4761,16 @@
         <v>200</v>
       </c>
       <c r="E115">
-        <v>11734</v>
+        <v>16058</v>
       </c>
       <c r="F115" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G115">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I115">
         <v>3</v>
@@ -4799,19 +4799,19 @@
         <v>200</v>
       </c>
       <c r="E116">
-        <v>21832</v>
+        <v>17396</v>
       </c>
       <c r="F116" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G116">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I116">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J116" t="str">
         <v>climatizacion</v>
@@ -4837,19 +4837,19 @@
         <v>200</v>
       </c>
       <c r="E117">
-        <v>10949</v>
+        <v>18689</v>
       </c>
       <c r="F117" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G117">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H117">
         <v>2</v>
       </c>
       <c r="I117">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J117" t="str">
         <v>mecanica_especializada</v>
@@ -4875,19 +4875,19 @@
         <v>200</v>
       </c>
       <c r="E118">
-        <v>16571</v>
+        <v>11602</v>
       </c>
       <c r="F118" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G118">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H118">
         <v>2</v>
       </c>
       <c r="I118">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J118" t="str">
         <v>electricidad</v>
@@ -4913,7 +4913,7 @@
         <v>200</v>
       </c>
       <c r="E119">
-        <v>20546</v>
+        <v>17872</v>
       </c>
       <c r="F119" t="str">
         <v>OK_MIXTO</v>
@@ -4922,10 +4922,10 @@
         <v>7</v>
       </c>
       <c r="H119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J119" t="str">
         <v>climatizacion</v>
@@ -4951,16 +4951,16 @@
         <v>200</v>
       </c>
       <c r="E120">
-        <v>24791</v>
+        <v>21336</v>
       </c>
       <c r="F120" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G120">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H120">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I120">
         <v>6</v>
@@ -4989,19 +4989,19 @@
         <v>200</v>
       </c>
       <c r="E121">
-        <v>29417</v>
+        <v>27491</v>
       </c>
       <c r="F121" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G121">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H121">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I121">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J121" t="str">
         <v>fontaneria</v>
@@ -5027,7 +5027,7 @@
         <v>200</v>
       </c>
       <c r="E122">
-        <v>15172</v>
+        <v>14656</v>
       </c>
       <c r="F122" t="str">
         <v>OK_MIXTO</v>
@@ -5065,19 +5065,19 @@
         <v>200</v>
       </c>
       <c r="E123">
-        <v>21507</v>
+        <v>24035</v>
       </c>
       <c r="F123" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G123">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H123">
+        <v>11</v>
+      </c>
+      <c r="I123">
         <v>0</v>
-      </c>
-      <c r="I123">
-        <v>6</v>
       </c>
       <c r="J123" t="str">
         <v>impermeabilizacion</v>
@@ -5086,7 +5086,7 @@
         <v>NO</v>
       </c>
       <c r="L123" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="124">
@@ -5103,7 +5103,7 @@
         <v>200</v>
       </c>
       <c r="E124">
-        <v>10752</v>
+        <v>10979</v>
       </c>
       <c r="F124" t="str">
         <v>OK_MIXTO</v>
@@ -5141,7 +5141,7 @@
         <v>200</v>
       </c>
       <c r="E125">
-        <v>12444</v>
+        <v>13561</v>
       </c>
       <c r="F125" t="str">
         <v>OK_MIXTO</v>
@@ -5150,10 +5150,10 @@
         <v>6</v>
       </c>
       <c r="H125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J125" t="str">
         <v>tejados_cubiertas</v>
@@ -5179,19 +5179,19 @@
         <v>200</v>
       </c>
       <c r="E126">
-        <v>12826</v>
+        <v>14637</v>
       </c>
       <c r="F126" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G126">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H126">
         <v>3</v>
       </c>
       <c r="I126">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J126" t="str">
         <v>impermeabilizacion</v>
@@ -5217,19 +5217,19 @@
         <v>200</v>
       </c>
       <c r="E127">
-        <v>17230</v>
+        <v>17533</v>
       </c>
       <c r="F127" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G127">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H127">
         <v>3</v>
       </c>
       <c r="I127">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J127" t="str">
         <v>tejados_cubiertas</v>
@@ -5255,19 +5255,19 @@
         <v>200</v>
       </c>
       <c r="E128">
-        <v>14873</v>
+        <v>15915</v>
       </c>
       <c r="F128" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H128">
         <v>2</v>
       </c>
       <c r="I128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J128" t="str">
         <v>tejados_cubiertas</v>
@@ -5293,19 +5293,19 @@
         <v>200</v>
       </c>
       <c r="E129">
-        <v>17854</v>
+        <v>19095</v>
       </c>
       <c r="F129" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G129">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H129">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J129" t="str">
         <v>tejados_cubiertas</v>
@@ -5331,19 +5331,19 @@
         <v>200</v>
       </c>
       <c r="E130">
-        <v>18609</v>
+        <v>16106</v>
       </c>
       <c r="F130" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G130">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H130">
         <v>5</v>
       </c>
       <c r="I130">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J130" t="str">
         <v>tejados_cubiertas</v>
@@ -5369,7 +5369,7 @@
         <v>200</v>
       </c>
       <c r="E131">
-        <v>15127</v>
+        <v>18187</v>
       </c>
       <c r="F131" t="str">
         <v>OK_MIXTO</v>
@@ -5378,10 +5378,10 @@
         <v>6</v>
       </c>
       <c r="H131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I131">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J131" t="str">
         <v>tejados_cubiertas</v>
@@ -5407,19 +5407,19 @@
         <v>200</v>
       </c>
       <c r="E132">
-        <v>18983</v>
+        <v>24070</v>
       </c>
       <c r="F132" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G132">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H132">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I132">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J132" t="str">
         <v>tejados_cubiertas</v>
@@ -5445,16 +5445,16 @@
         <v>200</v>
       </c>
       <c r="E133">
-        <v>25448</v>
+        <v>26570</v>
       </c>
       <c r="F133" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G133">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H133">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I133">
         <v>8</v>
@@ -5483,19 +5483,19 @@
         <v>200</v>
       </c>
       <c r="E134">
-        <v>14043</v>
+        <v>12301</v>
       </c>
       <c r="F134" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G134">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H134">
         <v>2</v>
       </c>
       <c r="I134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J134" t="str">
         <v>impermeabilizacion</v>
@@ -5521,7 +5521,7 @@
         <v>200</v>
       </c>
       <c r="E135">
-        <v>19546</v>
+        <v>14917</v>
       </c>
       <c r="F135" t="str">
         <v>OK_MIXTO</v>
@@ -5559,19 +5559,19 @@
         <v>200</v>
       </c>
       <c r="E136">
-        <v>22786</v>
+        <v>26324</v>
       </c>
       <c r="F136" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G136">
+        <v>11</v>
+      </c>
+      <c r="H136">
         <v>6</v>
       </c>
-      <c r="H136">
-        <v>2</v>
-      </c>
       <c r="I136">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J136" t="str">
         <v>tejados_cubiertas</v>
@@ -5597,19 +5597,19 @@
         <v>200</v>
       </c>
       <c r="E137">
-        <v>35937</v>
+        <v>32609</v>
       </c>
       <c r="F137" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G137">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H137">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I137">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J137" t="str">
         <v>tejados_cubiertas</v>
@@ -5635,19 +5635,19 @@
         <v>200</v>
       </c>
       <c r="E138">
-        <v>13877</v>
+        <v>14983</v>
       </c>
       <c r="F138" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G138">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H138">
         <v>2</v>
       </c>
       <c r="I138">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J138" t="str">
         <v>tejados_cubiertas</v>
@@ -5673,7 +5673,7 @@
         <v>200</v>
       </c>
       <c r="E139">
-        <v>12948</v>
+        <v>13090</v>
       </c>
       <c r="F139" t="str">
         <v>OK_MIXTO</v>
@@ -5711,19 +5711,19 @@
         <v>200</v>
       </c>
       <c r="E140">
-        <v>17354</v>
+        <v>19394</v>
       </c>
       <c r="F140" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G140">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H140">
         <v>3</v>
       </c>
       <c r="I140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J140" t="str">
         <v>tejados_cubiertas</v>
@@ -5749,19 +5749,19 @@
         <v>200</v>
       </c>
       <c r="E141">
-        <v>13235</v>
+        <v>14875</v>
       </c>
       <c r="F141" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H141">
         <v>3</v>
       </c>
       <c r="I141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J141" t="str">
         <v>tejados_cubiertas</v>
@@ -5787,19 +5787,19 @@
         <v>200</v>
       </c>
       <c r="E142">
-        <v>22877</v>
+        <v>24188</v>
       </c>
       <c r="F142" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G142">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H142">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I142">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J142" t="str">
         <v>pladur_escayola</v>
@@ -5825,19 +5825,19 @@
         <v>200</v>
       </c>
       <c r="E143">
-        <v>21060</v>
+        <v>19663</v>
       </c>
       <c r="F143" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G143">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I143">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J143" t="str">
         <v>pladur_escayola</v>
@@ -5863,19 +5863,19 @@
         <v>200</v>
       </c>
       <c r="E144">
-        <v>19121</v>
+        <v>21815</v>
       </c>
       <c r="F144" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G144">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H144">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I144">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J144" t="str">
         <v>pladur_escayola</v>
@@ -5901,19 +5901,19 @@
         <v>200</v>
       </c>
       <c r="E145">
-        <v>19800</v>
+        <v>21473</v>
       </c>
       <c r="F145" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G145">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H145">
         <v>2</v>
       </c>
       <c r="I145">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J145" t="str">
         <v>pladur_escayola</v>
@@ -5939,7 +5939,7 @@
         <v>200</v>
       </c>
       <c r="E146">
-        <v>9585</v>
+        <v>8746</v>
       </c>
       <c r="F146" t="str">
         <v>OK_MIXTO</v>
@@ -5977,7 +5977,7 @@
         <v>200</v>
       </c>
       <c r="E147">
-        <v>24509</v>
+        <v>21636</v>
       </c>
       <c r="F147" t="str">
         <v>OK_MIXTO</v>
@@ -5986,10 +5986,10 @@
         <v>6</v>
       </c>
       <c r="H147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J147" t="str">
         <v>pladur_escayola</v>
@@ -6015,19 +6015,19 @@
         <v>200</v>
       </c>
       <c r="E148">
-        <v>20197</v>
+        <v>17031</v>
       </c>
       <c r="F148" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G148">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H148">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J148" t="str">
         <v>contra_incendios</v>
@@ -6053,7 +6053,7 @@
         <v>200</v>
       </c>
       <c r="E149">
-        <v>13785</v>
+        <v>15356</v>
       </c>
       <c r="F149" t="str">
         <v>OK_MIXTO</v>
@@ -6091,19 +6091,19 @@
         <v>200</v>
       </c>
       <c r="E150">
-        <v>19436</v>
+        <v>12428</v>
       </c>
       <c r="F150" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G150">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I150">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J150" t="str">
         <v>pladur_escayola</v>
@@ -6129,19 +6129,19 @@
         <v>200</v>
       </c>
       <c r="E151">
-        <v>16253</v>
+        <v>27596</v>
       </c>
       <c r="F151" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G151">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J151" t="str">
         <v>pladur_escayola</v>
@@ -6167,25 +6167,25 @@
         <v>200</v>
       </c>
       <c r="E152">
-        <v>20305</v>
+        <v>21350</v>
       </c>
       <c r="F152" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G152">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H152">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I152">
         <v>5</v>
       </c>
       <c r="J152" t="str">
-        <v>pladur_escayola</v>
+        <v>albanileria</v>
       </c>
       <c r="K152" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L152" t="str">
         <v/>
@@ -6205,19 +6205,19 @@
         <v>200</v>
       </c>
       <c r="E153">
-        <v>24370</v>
+        <v>19193</v>
       </c>
       <c r="F153" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G153">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I153">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J153" t="str">
         <v>pladur_escayola</v>
@@ -6243,7 +6243,7 @@
         <v>200</v>
       </c>
       <c r="E154">
-        <v>11185</v>
+        <v>11089</v>
       </c>
       <c r="F154" t="str">
         <v>OK_MIXTO</v>
@@ -6281,19 +6281,19 @@
         <v>200</v>
       </c>
       <c r="E155">
-        <v>18049</v>
+        <v>18733</v>
       </c>
       <c r="F155" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G155">
+        <v>7</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155">
         <v>6</v>
-      </c>
-      <c r="H155">
-        <v>2</v>
-      </c>
-      <c r="I155">
-        <v>4</v>
       </c>
       <c r="J155" t="str">
         <v>pladur_escayola</v>
@@ -6319,7 +6319,7 @@
         <v>200</v>
       </c>
       <c r="E156">
-        <v>15151</v>
+        <v>14229</v>
       </c>
       <c r="F156" t="str">
         <v>OK_MIXTO</v>
@@ -6328,10 +6328,10 @@
         <v>6</v>
       </c>
       <c r="H156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I156">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J156" t="str">
         <v>pladur_escayola</v>
@@ -6357,16 +6357,16 @@
         <v>200</v>
       </c>
       <c r="E157">
-        <v>20832</v>
+        <v>17502</v>
       </c>
       <c r="F157" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G157">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H157">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I157">
         <v>5</v>
@@ -6395,7 +6395,7 @@
         <v>200</v>
       </c>
       <c r="E158">
-        <v>16207</v>
+        <v>13720</v>
       </c>
       <c r="F158" t="str">
         <v>OK_MIXTO</v>
@@ -6404,10 +6404,10 @@
         <v>6</v>
       </c>
       <c r="H158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J158" t="str">
         <v>pladur_escayola</v>
@@ -6433,7 +6433,7 @@
         <v>200</v>
       </c>
       <c r="E159">
-        <v>13384</v>
+        <v>12597</v>
       </c>
       <c r="F159" t="str">
         <v>OK_MIXTO</v>
@@ -6471,19 +6471,19 @@
         <v>200</v>
       </c>
       <c r="E160">
-        <v>13607</v>
+        <v>18110</v>
       </c>
       <c r="F160" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G160">
+        <v>8</v>
+      </c>
+      <c r="H160">
+        <v>2</v>
+      </c>
+      <c r="I160">
         <v>6</v>
-      </c>
-      <c r="H160">
-        <v>1</v>
-      </c>
-      <c r="I160">
-        <v>5</v>
       </c>
       <c r="J160" t="str">
         <v>pladur_escayola</v>
@@ -6509,19 +6509,19 @@
         <v>200</v>
       </c>
       <c r="E161">
-        <v>20119</v>
+        <v>22722</v>
       </c>
       <c r="F161" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G161">
+        <v>13</v>
+      </c>
+      <c r="H161">
+        <v>4</v>
+      </c>
+      <c r="I161">
         <v>9</v>
-      </c>
-      <c r="H161">
-        <v>3</v>
-      </c>
-      <c r="I161">
-        <v>6</v>
       </c>
       <c r="J161" t="str">
         <v>pladur_escayola</v>
@@ -6547,7 +6547,7 @@
         <v>200</v>
       </c>
       <c r="E162">
-        <v>19250</v>
+        <v>17906</v>
       </c>
       <c r="F162" t="str">
         <v>OK_MIXTO</v>
@@ -6585,7 +6585,7 @@
         <v>200</v>
       </c>
       <c r="E163">
-        <v>14218</v>
+        <v>13314</v>
       </c>
       <c r="F163" t="str">
         <v>OK_MIXTO</v>
@@ -6623,19 +6623,19 @@
         <v>200</v>
       </c>
       <c r="E164">
-        <v>12589</v>
+        <v>10413</v>
       </c>
       <c r="F164" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G164">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J164" t="str">
         <v>albanileria</v>
@@ -6661,19 +6661,19 @@
         <v>200</v>
       </c>
       <c r="E165">
-        <v>15205</v>
+        <v>11451</v>
       </c>
       <c r="F165" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G165">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H165">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J165" t="str">
         <v>suelos_alicatados</v>
@@ -6699,19 +6699,19 @@
         <v>200</v>
       </c>
       <c r="E166">
-        <v>18421</v>
+        <v>11862</v>
       </c>
       <c r="F166" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H166">
         <v>2</v>
       </c>
       <c r="I166">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J166" t="str">
         <v>suelos_tarimas</v>
@@ -6737,19 +6737,19 @@
         <v>200</v>
       </c>
       <c r="E167">
-        <v>16479</v>
+        <v>15790</v>
       </c>
       <c r="F167" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G167">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H167">
         <v>4</v>
       </c>
       <c r="I167">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J167" t="str">
         <v>suelos_alicatados</v>
@@ -6775,16 +6775,16 @@
         <v>200</v>
       </c>
       <c r="E168">
-        <v>20522</v>
+        <v>21349</v>
       </c>
       <c r="F168" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G168">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I168">
         <v>4</v>
@@ -6796,7 +6796,7 @@
         <v>NO</v>
       </c>
       <c r="L168" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="169">
@@ -6813,16 +6813,16 @@
         <v>200</v>
       </c>
       <c r="E169">
-        <v>13472</v>
+        <v>13017</v>
       </c>
       <c r="F169" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G169">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I169">
         <v>4</v>
@@ -6851,19 +6851,19 @@
         <v>200</v>
       </c>
       <c r="E170">
-        <v>13327</v>
+        <v>9994</v>
       </c>
       <c r="F170" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G170">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H170">
         <v>1</v>
       </c>
       <c r="I170">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J170" t="str">
         <v>suelos_alicatados</v>
@@ -6889,16 +6889,16 @@
         <v>200</v>
       </c>
       <c r="E171">
-        <v>16208</v>
+        <v>18181</v>
       </c>
       <c r="F171" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G171">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I171">
         <v>4</v>
@@ -6927,19 +6927,19 @@
         <v>200</v>
       </c>
       <c r="E172">
-        <v>14396</v>
+        <v>12334</v>
       </c>
       <c r="F172" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G172">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H172">
         <v>2</v>
       </c>
       <c r="I172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J172" t="str">
         <v>suelos_alicatados</v>
@@ -6965,19 +6965,19 @@
         <v>200</v>
       </c>
       <c r="E173">
-        <v>19473</v>
+        <v>19252</v>
       </c>
       <c r="F173" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G173">
+        <v>9</v>
+      </c>
+      <c r="H173">
+        <v>2</v>
+      </c>
+      <c r="I173">
         <v>7</v>
-      </c>
-      <c r="H173">
-        <v>1</v>
-      </c>
-      <c r="I173">
-        <v>6</v>
       </c>
       <c r="J173" t="str">
         <v>suelos_alicatados</v>
@@ -7003,7 +7003,7 @@
         <v>200</v>
       </c>
       <c r="E174">
-        <v>25540</v>
+        <v>25196</v>
       </c>
       <c r="F174" t="str">
         <v>OK_MIXTO</v>
@@ -7041,19 +7041,19 @@
         <v>200</v>
       </c>
       <c r="E175">
-        <v>21480</v>
+        <v>18175</v>
       </c>
       <c r="F175" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G175">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H175">
         <v>4</v>
       </c>
       <c r="I175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J175" t="str">
         <v>suelos_alicatados</v>
@@ -7079,7 +7079,7 @@
         <v>200</v>
       </c>
       <c r="E176">
-        <v>18229</v>
+        <v>14295</v>
       </c>
       <c r="F176" t="str">
         <v>OK_MIXTO</v>
@@ -7088,10 +7088,10 @@
         <v>6</v>
       </c>
       <c r="H176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I176">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J176" t="str">
         <v>carpinteria</v>
@@ -7117,19 +7117,19 @@
         <v>200</v>
       </c>
       <c r="E177">
-        <v>19885</v>
+        <v>22279</v>
       </c>
       <c r="F177" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G177">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I177">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J177" t="str">
         <v>suelos_alicatados</v>
@@ -7155,19 +7155,19 @@
         <v>200</v>
       </c>
       <c r="E178">
-        <v>27083</v>
+        <v>21234</v>
       </c>
       <c r="F178" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G178">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J178" t="str">
         <v>suelos_alicatados</v>
@@ -7193,7 +7193,7 @@
         <v>200</v>
       </c>
       <c r="E179">
-        <v>13209</v>
+        <v>12035</v>
       </c>
       <c r="F179" t="str">
         <v>OK_MIXTO</v>
@@ -7231,7 +7231,7 @@
         <v>200</v>
       </c>
       <c r="E180">
-        <v>13291</v>
+        <v>12883</v>
       </c>
       <c r="F180" t="str">
         <v>OK_MIXTO</v>
@@ -7240,10 +7240,10 @@
         <v>6</v>
       </c>
       <c r="H180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I180">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J180" t="str">
         <v>suelos_alicatados</v>
@@ -7269,16 +7269,16 @@
         <v>200</v>
       </c>
       <c r="E181">
-        <v>17694</v>
+        <v>21734</v>
       </c>
       <c r="F181" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G181">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I181">
         <v>5</v>
@@ -7307,7 +7307,7 @@
         <v>200</v>
       </c>
       <c r="E182">
-        <v>9645</v>
+        <v>9646</v>
       </c>
       <c r="F182" t="str">
         <v>OK_MIXTO</v>
@@ -7345,7 +7345,7 @@
         <v>200</v>
       </c>
       <c r="E183">
-        <v>14876</v>
+        <v>12168</v>
       </c>
       <c r="F183" t="str">
         <v>OK_MIXTO</v>
@@ -7383,19 +7383,19 @@
         <v>200</v>
       </c>
       <c r="E184">
-        <v>10591</v>
+        <v>9275</v>
       </c>
       <c r="F184" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G184">
         <v>3</v>
       </c>
       <c r="H184">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I184">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J184" t="str">
         <v>cerrajeria</v>
@@ -7404,7 +7404,7 @@
         <v>SI</v>
       </c>
       <c r="L184" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="185">
@@ -7421,19 +7421,19 @@
         <v>200</v>
       </c>
       <c r="E185">
-        <v>11897</v>
+        <v>12658</v>
       </c>
       <c r="F185" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G185">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H185">
         <v>3</v>
       </c>
       <c r="I185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J185" t="str">
         <v>cerrajeria</v>
@@ -7459,19 +7459,19 @@
         <v>200</v>
       </c>
       <c r="E186">
-        <v>13553</v>
+        <v>21350</v>
       </c>
       <c r="F186" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G186">
+        <v>7</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186">
         <v>6</v>
-      </c>
-      <c r="H186">
-        <v>2</v>
-      </c>
-      <c r="I186">
-        <v>4</v>
       </c>
       <c r="J186" t="str">
         <v>cerrajeria</v>
@@ -7497,16 +7497,16 @@
         <v>200</v>
       </c>
       <c r="E187">
-        <v>11595</v>
+        <v>10868</v>
       </c>
       <c r="F187" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G187">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I187">
         <v>3</v>
@@ -7535,7 +7535,7 @@
         <v>200</v>
       </c>
       <c r="E188">
-        <v>12098</v>
+        <v>11591</v>
       </c>
       <c r="F188" t="str">
         <v>OK_MIXTO</v>
@@ -7573,7 +7573,7 @@
         <v>200</v>
       </c>
       <c r="E189">
-        <v>10614</v>
+        <v>11385</v>
       </c>
       <c r="F189" t="str">
         <v>OK_MIXTO</v>
@@ -7611,16 +7611,16 @@
         <v>200</v>
       </c>
       <c r="E190">
-        <v>16044</v>
+        <v>16311</v>
       </c>
       <c r="F190" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G190">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H190">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I190">
         <v>6</v>
@@ -7649,19 +7649,19 @@
         <v>200</v>
       </c>
       <c r="E191">
-        <v>10036</v>
+        <v>8861</v>
       </c>
       <c r="F191" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H191">
         <v>3</v>
       </c>
       <c r="I191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J191" t="str">
         <v>cerrajeria</v>
@@ -7687,7 +7687,7 @@
         <v>200</v>
       </c>
       <c r="E192">
-        <v>14277</v>
+        <v>16250</v>
       </c>
       <c r="F192" t="str">
         <v>OK_MIXTO</v>
@@ -7725,7 +7725,7 @@
         <v>200</v>
       </c>
       <c r="E193">
-        <v>8680</v>
+        <v>8951</v>
       </c>
       <c r="F193" t="str">
         <v>OK_MIXTO</v>
@@ -7763,19 +7763,19 @@
         <v>200</v>
       </c>
       <c r="E194">
-        <v>13909</v>
+        <v>13179</v>
       </c>
       <c r="F194" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G194">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H194">
         <v>1</v>
       </c>
       <c r="I194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J194" t="str">
         <v>cerrajeria</v>
@@ -7801,16 +7801,16 @@
         <v>200</v>
       </c>
       <c r="E195">
-        <v>18996</v>
+        <v>16636</v>
       </c>
       <c r="F195" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G195">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I195">
         <v>3</v>
@@ -7839,16 +7839,16 @@
         <v>200</v>
       </c>
       <c r="E196">
-        <v>24953</v>
+        <v>17490</v>
       </c>
       <c r="F196" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G196">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H196">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I196">
         <v>6</v>
@@ -7877,7 +7877,7 @@
         <v>200</v>
       </c>
       <c r="E197">
-        <v>13829</v>
+        <v>12094</v>
       </c>
       <c r="F197" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -7915,7 +7915,7 @@
         <v>200</v>
       </c>
       <c r="E198">
-        <v>13360</v>
+        <v>14661</v>
       </c>
       <c r="F198" t="str">
         <v>OK_MIXTO</v>
@@ -7953,7 +7953,7 @@
         <v>200</v>
       </c>
       <c r="E199">
-        <v>9245</v>
+        <v>9661</v>
       </c>
       <c r="F199" t="str">
         <v>OK_MIXTO</v>
@@ -7991,19 +7991,19 @@
         <v>200</v>
       </c>
       <c r="E200">
-        <v>27994</v>
+        <v>25689</v>
       </c>
       <c r="F200" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G200">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H200">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I200">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J200" t="str">
         <v>cerrajeria</v>
@@ -8029,7 +8029,7 @@
         <v>200</v>
       </c>
       <c r="E201">
-        <v>7900</v>
+        <v>8188</v>
       </c>
       <c r="F201" t="str">
         <v>OK_MIXTO</v>
@@ -8067,7 +8067,7 @@
         <v>200</v>
       </c>
       <c r="E202">
-        <v>9374</v>
+        <v>9936</v>
       </c>
       <c r="F202" t="str">
         <v>OK_MIXTO</v>
@@ -8105,19 +8105,19 @@
         <v>200</v>
       </c>
       <c r="E203">
-        <v>18025</v>
+        <v>22695</v>
       </c>
       <c r="F203" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G203">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H203">
         <v>4</v>
       </c>
       <c r="I203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J203" t="str">
         <v>jardineria</v>
@@ -8143,19 +8143,19 @@
         <v>200</v>
       </c>
       <c r="E204">
-        <v>13893</v>
+        <v>12480</v>
       </c>
       <c r="F204" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G204">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H204">
         <v>1</v>
       </c>
       <c r="I204">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J204" t="str">
         <v>jardineria</v>
@@ -8181,7 +8181,7 @@
         <v>200</v>
       </c>
       <c r="E205">
-        <v>11379</v>
+        <v>11525</v>
       </c>
       <c r="F205" t="str">
         <v>OK_MIXTO</v>
@@ -8219,7 +8219,7 @@
         <v>200</v>
       </c>
       <c r="E206">
-        <v>16224</v>
+        <v>18360</v>
       </c>
       <c r="F206" t="str">
         <v>OK_MIXTO</v>
@@ -8257,7 +8257,7 @@
         <v>200</v>
       </c>
       <c r="E207">
-        <v>11903</v>
+        <v>12400</v>
       </c>
       <c r="F207" t="str">
         <v>OK_MIXTO</v>
@@ -8295,16 +8295,16 @@
         <v>200</v>
       </c>
       <c r="E208">
-        <v>13463</v>
+        <v>13069</v>
       </c>
       <c r="F208" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G208">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H208">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I208">
         <v>3</v>
@@ -8333,19 +8333,19 @@
         <v>200</v>
       </c>
       <c r="E209">
-        <v>11995</v>
+        <v>12860</v>
       </c>
       <c r="F209" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G209">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H209">
         <v>2</v>
       </c>
       <c r="I209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J209" t="str">
         <v>jardineria</v>
@@ -8371,7 +8371,7 @@
         <v>200</v>
       </c>
       <c r="E210">
-        <v>19612</v>
+        <v>22090</v>
       </c>
       <c r="F210" t="str">
         <v>OK_MIXTO</v>
@@ -8380,10 +8380,10 @@
         <v>12</v>
       </c>
       <c r="H210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I210">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J210" t="str">
         <v>jardineria</v>
@@ -8409,7 +8409,7 @@
         <v>200</v>
       </c>
       <c r="E211">
-        <v>19320</v>
+        <v>19049</v>
       </c>
       <c r="F211" t="str">
         <v>OK_MIXTO</v>
@@ -8447,7 +8447,7 @@
         <v>200</v>
       </c>
       <c r="E212">
-        <v>19653</v>
+        <v>19795</v>
       </c>
       <c r="F212" t="str">
         <v>OK_MIXTO</v>
@@ -8485,7 +8485,7 @@
         <v>200</v>
       </c>
       <c r="E213">
-        <v>15894</v>
+        <v>15772</v>
       </c>
       <c r="F213" t="str">
         <v>OK_MIXTO</v>
@@ -8494,10 +8494,10 @@
         <v>6</v>
       </c>
       <c r="H213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J213" t="str">
         <v>jardineria</v>
@@ -8523,19 +8523,19 @@
         <v>200</v>
       </c>
       <c r="E214">
-        <v>12229</v>
+        <v>16356</v>
       </c>
       <c r="F214" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G214">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I214">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J214" t="str">
         <v>carpinteria</v>
@@ -8561,19 +8561,19 @@
         <v>200</v>
       </c>
       <c r="E215">
-        <v>11301</v>
+        <v>8371</v>
       </c>
       <c r="F215" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G215">
         <v>3</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J215" t="str">
         <v>jardineria</v>
@@ -8599,7 +8599,7 @@
         <v>200</v>
       </c>
       <c r="E216">
-        <v>11799</v>
+        <v>10688</v>
       </c>
       <c r="F216" t="str">
         <v>OK_MIXTO</v>
@@ -8637,7 +8637,7 @@
         <v>200</v>
       </c>
       <c r="E217">
-        <v>17963</v>
+        <v>16222</v>
       </c>
       <c r="F217" t="str">
         <v>OK_MIXTO</v>
@@ -8675,19 +8675,19 @@
         <v>200</v>
       </c>
       <c r="E218">
-        <v>22283</v>
+        <v>18157</v>
       </c>
       <c r="F218" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G218">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H218">
         <v>5</v>
       </c>
       <c r="I218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J218" t="str">
         <v>energia_solar</v>
@@ -8713,16 +8713,16 @@
         <v>200</v>
       </c>
       <c r="E219">
-        <v>27072</v>
+        <v>28187</v>
       </c>
       <c r="F219" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G219">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I219">
         <v>6</v>
@@ -8751,7 +8751,7 @@
         <v>200</v>
       </c>
       <c r="E220">
-        <v>14526</v>
+        <v>16899</v>
       </c>
       <c r="F220" t="str">
         <v>OK_MIXTO</v>
@@ -8789,19 +8789,19 @@
         <v>200</v>
       </c>
       <c r="E221">
-        <v>11940</v>
+        <v>8876</v>
       </c>
       <c r="F221" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G221">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J221" t="str">
         <v>jardineria</v>
@@ -8827,19 +8827,19 @@
         <v>200</v>
       </c>
       <c r="E222">
-        <v>19161</v>
+        <v>16657</v>
       </c>
       <c r="F222" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G222">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H222">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I222">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J222" t="str">
         <v>energia_solar</v>
@@ -8865,25 +8865,25 @@
         <v>200</v>
       </c>
       <c r="E223">
-        <v>24926</v>
+        <v>29759</v>
       </c>
       <c r="F223" t="str">
-        <v>OK_MIXTO</v>
+        <v>VACIO</v>
       </c>
       <c r="G223">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I223">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J223" t="str">
-        <v>energia_solar</v>
+        <v/>
       </c>
       <c r="K223" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L223" t="str">
         <v/>
@@ -8903,19 +8903,19 @@
         <v>200</v>
       </c>
       <c r="E224">
-        <v>21299</v>
+        <v>31238</v>
       </c>
       <c r="F224" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G224">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H224">
         <v>4</v>
       </c>
       <c r="I224">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J224" t="str">
         <v>energia_solar</v>
@@ -8941,19 +8941,19 @@
         <v>200</v>
       </c>
       <c r="E225">
-        <v>18309</v>
+        <v>21604</v>
       </c>
       <c r="F225" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G225">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H225">
         <v>1</v>
       </c>
       <c r="I225">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J225" t="str">
         <v>energia_solar</v>
@@ -8979,7 +8979,7 @@
         <v>200</v>
       </c>
       <c r="E226">
-        <v>15262</v>
+        <v>14196</v>
       </c>
       <c r="F226" t="str">
         <v>OK_MIXTO</v>
@@ -8988,10 +8988,10 @@
         <v>6</v>
       </c>
       <c r="H226">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J226" t="str">
         <v>energia_solar</v>
@@ -9017,7 +9017,7 @@
         <v>200</v>
       </c>
       <c r="E227">
-        <v>26574</v>
+        <v>21766</v>
       </c>
       <c r="F227" t="str">
         <v>OK_MIXTO</v>
@@ -9026,10 +9026,10 @@
         <v>10</v>
       </c>
       <c r="H227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I227">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J227" t="str">
         <v>energia_solar</v>
@@ -9055,16 +9055,16 @@
         <v>200</v>
       </c>
       <c r="E228">
-        <v>12920</v>
+        <v>14452</v>
       </c>
       <c r="F228" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G228">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I228">
         <v>2</v>
@@ -9093,7 +9093,7 @@
         <v>200</v>
       </c>
       <c r="E229">
-        <v>27662</v>
+        <v>28184</v>
       </c>
       <c r="F229" t="str">
         <v>OK_MIXTO</v>
@@ -9102,10 +9102,10 @@
         <v>13</v>
       </c>
       <c r="H229">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I229">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J229" t="str">
         <v>energia_solar</v>
@@ -9131,19 +9131,19 @@
         <v>200</v>
       </c>
       <c r="E230">
-        <v>28543</v>
+        <v>29962</v>
       </c>
       <c r="F230" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G230">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H230">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I230">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J230" t="str">
         <v>energia_solar</v>
@@ -9169,19 +9169,19 @@
         <v>200</v>
       </c>
       <c r="E231">
-        <v>16423</v>
+        <v>17064</v>
       </c>
       <c r="F231" t="str">
-        <v>OK_CATALOGO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G231">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H231">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" t="str">
         <v>energia_solar</v>
@@ -9207,7 +9207,7 @@
         <v>200</v>
       </c>
       <c r="E232">
-        <v>15479</v>
+        <v>14757</v>
       </c>
       <c r="F232" t="str">
         <v>OK_MIXTO</v>
@@ -9216,10 +9216,10 @@
         <v>6</v>
       </c>
       <c r="H232">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I232">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J232" t="str">
         <v>energia_solar</v>
@@ -9245,19 +9245,19 @@
         <v>200</v>
       </c>
       <c r="E233">
-        <v>19104</v>
+        <v>15728</v>
       </c>
       <c r="F233" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G233">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J233" t="str">
         <v>gestoria_tramites</v>
@@ -9283,7 +9283,7 @@
         <v>200</v>
       </c>
       <c r="E234">
-        <v>28545</v>
+        <v>25399</v>
       </c>
       <c r="F234" t="str">
         <v>OK_MIXTO</v>
@@ -9321,16 +9321,16 @@
         <v>200</v>
       </c>
       <c r="E235">
-        <v>16965</v>
+        <v>14458</v>
       </c>
       <c r="F235" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G235">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H235">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I235">
         <v>2</v>
@@ -9359,7 +9359,7 @@
         <v>200</v>
       </c>
       <c r="E236">
-        <v>27042</v>
+        <v>28600</v>
       </c>
       <c r="F236" t="str">
         <v>VACIO</v>
@@ -9397,19 +9397,19 @@
         <v>200</v>
       </c>
       <c r="E237">
-        <v>15549</v>
+        <v>15834</v>
       </c>
       <c r="F237" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G237">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H237">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I237">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J237" t="str">
         <v>energia_solar</v>
@@ -9418,7 +9418,7 @@
         <v>SI</v>
       </c>
       <c r="L237" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="238">
@@ -9435,7 +9435,7 @@
         <v>200</v>
       </c>
       <c r="E238">
-        <v>19379</v>
+        <v>22114</v>
       </c>
       <c r="F238" t="str">
         <v>OK_MIXTO</v>
@@ -9473,7 +9473,7 @@
         <v>200</v>
       </c>
       <c r="E239">
-        <v>16657</v>
+        <v>13905</v>
       </c>
       <c r="F239" t="str">
         <v>OK_MIXTO</v>
@@ -9511,7 +9511,7 @@
         <v>200</v>
       </c>
       <c r="E240">
-        <v>26750</v>
+        <v>27870</v>
       </c>
       <c r="F240" t="str">
         <v>VACIO</v>
@@ -9549,7 +9549,7 @@
         <v>200</v>
       </c>
       <c r="E241">
-        <v>24774</v>
+        <v>18552</v>
       </c>
       <c r="F241" t="str">
         <v>OK_MIXTO</v>
@@ -9558,10 +9558,10 @@
         <v>9</v>
       </c>
       <c r="H241">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I241">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J241" t="str">
         <v>energia_solar</v>
@@ -9587,16 +9587,16 @@
         <v>200</v>
       </c>
       <c r="E242">
-        <v>14422</v>
+        <v>16630</v>
       </c>
       <c r="F242" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G242">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H242">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I242">
         <v>6</v>
@@ -9625,7 +9625,7 @@
         <v>200</v>
       </c>
       <c r="E243">
-        <v>13341</v>
+        <v>13143</v>
       </c>
       <c r="F243" t="str">
         <v>OK_MIXTO</v>
@@ -9634,10 +9634,10 @@
         <v>6</v>
       </c>
       <c r="H243">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J243" t="str">
         <v>telecomunicaciones</v>
@@ -9663,19 +9663,19 @@
         <v>200</v>
       </c>
       <c r="E244">
-        <v>14481</v>
+        <v>16583</v>
       </c>
       <c r="F244" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G244">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H244">
         <v>2</v>
       </c>
       <c r="I244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J244" t="str">
         <v>telecomunicaciones</v>
@@ -9701,19 +9701,19 @@
         <v>200</v>
       </c>
       <c r="E245">
-        <v>14907</v>
+        <v>14373</v>
       </c>
       <c r="F245" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G245">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H245">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I245">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J245" t="str">
         <v>telecomunicaciones</v>
@@ -9739,16 +9739,16 @@
         <v>200</v>
       </c>
       <c r="E246">
-        <v>20566</v>
+        <v>15223</v>
       </c>
       <c r="F246" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G246">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H246">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I246">
         <v>6</v>
@@ -9777,16 +9777,16 @@
         <v>200</v>
       </c>
       <c r="E247">
-        <v>11838</v>
+        <v>14063</v>
       </c>
       <c r="F247" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G247">
+        <v>6</v>
+      </c>
+      <c r="H247">
         <v>5</v>
-      </c>
-      <c r="H247">
-        <v>4</v>
       </c>
       <c r="I247">
         <v>1</v>
@@ -9815,16 +9815,16 @@
         <v>200</v>
       </c>
       <c r="E248">
-        <v>17335</v>
+        <v>16912</v>
       </c>
       <c r="F248" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G248">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H248">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I248">
         <v>5</v>
@@ -9853,7 +9853,7 @@
         <v>200</v>
       </c>
       <c r="E249">
-        <v>11249</v>
+        <v>13942</v>
       </c>
       <c r="F249" t="str">
         <v>OK_MIXTO</v>
@@ -9862,10 +9862,10 @@
         <v>4</v>
       </c>
       <c r="H249">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J249" t="str">
         <v>telecomunicaciones</v>
@@ -9891,7 +9891,7 @@
         <v>200</v>
       </c>
       <c r="E250">
-        <v>13412</v>
+        <v>16425</v>
       </c>
       <c r="F250" t="str">
         <v>OK_MIXTO</v>
@@ -9929,16 +9929,16 @@
         <v>200</v>
       </c>
       <c r="E251">
-        <v>9063</v>
+        <v>10655</v>
       </c>
       <c r="F251" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G251">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H251">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I251">
         <v>1</v>
@@ -9967,19 +9967,19 @@
         <v>200</v>
       </c>
       <c r="E252">
-        <v>28323</v>
+        <v>24939</v>
       </c>
       <c r="F252" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G252">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H252">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I252">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J252" t="str">
         <v>telecomunicaciones</v>
@@ -10005,7 +10005,7 @@
         <v>200</v>
       </c>
       <c r="E253">
-        <v>17616</v>
+        <v>19690</v>
       </c>
       <c r="F253" t="str">
         <v>OK_MIXTO</v>
@@ -10014,10 +10014,10 @@
         <v>10</v>
       </c>
       <c r="H253">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I253">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J253" t="str">
         <v>telecomunicaciones</v>
@@ -10043,19 +10043,19 @@
         <v>200</v>
       </c>
       <c r="E254">
-        <v>22499</v>
+        <v>25187</v>
       </c>
       <c r="F254" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G254">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H254">
         <v>4</v>
       </c>
       <c r="I254">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J254" t="str">
         <v>telecomunicaciones</v>
@@ -10081,7 +10081,7 @@
         <v>200</v>
       </c>
       <c r="E255">
-        <v>19615</v>
+        <v>16889</v>
       </c>
       <c r="F255" t="str">
         <v>OK_MIXTO</v>
@@ -10119,16 +10119,16 @@
         <v>200</v>
       </c>
       <c r="E256">
-        <v>14204</v>
+        <v>14354</v>
       </c>
       <c r="F256" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I256">
         <v>4</v>
@@ -10157,19 +10157,19 @@
         <v>200</v>
       </c>
       <c r="E257">
-        <v>20360</v>
+        <v>18400</v>
       </c>
       <c r="F257" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G257">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H257">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I257">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J257" t="str">
         <v>telecomunicaciones</v>
@@ -10195,19 +10195,19 @@
         <v>200</v>
       </c>
       <c r="E258">
-        <v>9752</v>
+        <v>10176</v>
       </c>
       <c r="F258" t="str">
-        <v>OK_CATALOGO</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G258">
         <v>6</v>
       </c>
       <c r="H258">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J258" t="str">
         <v>telecomunicaciones</v>
@@ -10233,19 +10233,19 @@
         <v>200</v>
       </c>
       <c r="E259">
-        <v>18137</v>
+        <v>23532</v>
       </c>
       <c r="F259" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G259">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H259">
         <v>1</v>
       </c>
       <c r="I259">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J259" t="str">
         <v>telecomunicaciones</v>
@@ -10271,19 +10271,19 @@
         <v>200</v>
       </c>
       <c r="E260">
-        <v>18738</v>
+        <v>16712</v>
       </c>
       <c r="F260" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G260">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H260">
         <v>1</v>
       </c>
       <c r="I260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J260" t="str">
         <v>telecomunicaciones</v>
@@ -10309,19 +10309,19 @@
         <v>200</v>
       </c>
       <c r="E261">
-        <v>19992</v>
+        <v>20565</v>
       </c>
       <c r="F261" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G261">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H261">
         <v>4</v>
       </c>
       <c r="I261">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J261" t="str">
         <v>telecomunicaciones</v>
@@ -10347,7 +10347,7 @@
         <v>200</v>
       </c>
       <c r="E262">
-        <v>16127</v>
+        <v>13378</v>
       </c>
       <c r="F262" t="str">
         <v>OK_MIXTO</v>
@@ -10356,10 +10356,10 @@
         <v>5</v>
       </c>
       <c r="H262">
+        <v>3</v>
+      </c>
+      <c r="I262">
         <v>2</v>
-      </c>
-      <c r="I262">
-        <v>3</v>
       </c>
       <c r="J262" t="str">
         <v>cristaleria</v>
@@ -10385,19 +10385,19 @@
         <v>200</v>
       </c>
       <c r="E263">
-        <v>14743</v>
+        <v>17628</v>
       </c>
       <c r="F263" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G263">
+        <v>7</v>
+      </c>
+      <c r="H263">
+        <v>2</v>
+      </c>
+      <c r="I263">
         <v>5</v>
-      </c>
-      <c r="H263">
-        <v>1</v>
-      </c>
-      <c r="I263">
-        <v>4</v>
       </c>
       <c r="J263" t="str">
         <v>cristaleria</v>
@@ -10423,19 +10423,19 @@
         <v>200</v>
       </c>
       <c r="E264">
-        <v>14252</v>
+        <v>12682</v>
       </c>
       <c r="F264" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G264">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H264">
         <v>1</v>
       </c>
       <c r="I264">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J264" t="str">
         <v>cristaleria</v>
@@ -10461,7 +10461,7 @@
         <v>200</v>
       </c>
       <c r="E265">
-        <v>16826</v>
+        <v>20436</v>
       </c>
       <c r="F265" t="str">
         <v>OK_MIXTO</v>
@@ -10499,7 +10499,7 @@
         <v>200</v>
       </c>
       <c r="E266">
-        <v>13500</v>
+        <v>17374</v>
       </c>
       <c r="F266" t="str">
         <v>OK_MIXTO</v>
@@ -10537,16 +10537,16 @@
         <v>200</v>
       </c>
       <c r="E267">
-        <v>24287</v>
+        <v>19459</v>
       </c>
       <c r="F267" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G267">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H267">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I267">
         <v>5</v>
@@ -10575,19 +10575,19 @@
         <v>200</v>
       </c>
       <c r="E268">
-        <v>16017</v>
+        <v>19265</v>
       </c>
       <c r="F268" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G268">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H268">
         <v>3</v>
       </c>
       <c r="I268">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J268" t="str">
         <v>cristaleria</v>
@@ -10613,7 +10613,7 @@
         <v>200</v>
       </c>
       <c r="E269">
-        <v>18952</v>
+        <v>20719</v>
       </c>
       <c r="F269" t="str">
         <v>OK_MIXTO</v>
@@ -10651,7 +10651,7 @@
         <v>200</v>
       </c>
       <c r="E270">
-        <v>9770</v>
+        <v>9830</v>
       </c>
       <c r="F270" t="str">
         <v>OK_MIXTO</v>
@@ -10689,16 +10689,16 @@
         <v>200</v>
       </c>
       <c r="E271">
-        <v>10620</v>
+        <v>11536</v>
       </c>
       <c r="F271" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G271">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H271">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I271">
         <v>3</v>
@@ -10727,7 +10727,7 @@
         <v>200</v>
       </c>
       <c r="E272">
-        <v>11705</v>
+        <v>12201</v>
       </c>
       <c r="F272" t="str">
         <v>OK_MIXTO</v>
@@ -10765,19 +10765,19 @@
         <v>200</v>
       </c>
       <c r="E273">
-        <v>16776</v>
+        <v>20048</v>
       </c>
       <c r="F273" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G273">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H273">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I273">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J273" t="str">
         <v>cristaleria</v>
@@ -10803,7 +10803,7 @@
         <v>200</v>
       </c>
       <c r="E274">
-        <v>11506</v>
+        <v>10390</v>
       </c>
       <c r="F274" t="str">
         <v>OK_MIXTO</v>
@@ -10841,7 +10841,7 @@
         <v>200</v>
       </c>
       <c r="E275">
-        <v>16845</v>
+        <v>12997</v>
       </c>
       <c r="F275" t="str">
         <v>OK_MIXTO</v>
@@ -10879,19 +10879,19 @@
         <v>200</v>
       </c>
       <c r="E276">
-        <v>13259</v>
+        <v>12060</v>
       </c>
       <c r="F276" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G276">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H276">
         <v>3</v>
       </c>
       <c r="I276">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J276" t="str">
         <v>cristaleria</v>
@@ -10917,7 +10917,7 @@
         <v>200</v>
       </c>
       <c r="E277">
-        <v>14632</v>
+        <v>12832</v>
       </c>
       <c r="F277" t="str">
         <v>OK_MIXTO</v>
@@ -10926,10 +10926,10 @@
         <v>6</v>
       </c>
       <c r="H277">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J277" t="str">
         <v>cristaleria</v>
@@ -10955,19 +10955,19 @@
         <v>200</v>
       </c>
       <c r="E278">
-        <v>14603</v>
+        <v>16616</v>
       </c>
       <c r="F278" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G278">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H278">
         <v>2</v>
       </c>
       <c r="I278">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J278" t="str">
         <v>cristaleria</v>
@@ -10993,7 +10993,7 @@
         <v>200</v>
       </c>
       <c r="E279">
-        <v>18634</v>
+        <v>16328</v>
       </c>
       <c r="F279" t="str">
         <v>OK_MIXTO</v>
@@ -11031,19 +11031,19 @@
         <v>200</v>
       </c>
       <c r="E280">
-        <v>19479</v>
+        <v>13863</v>
       </c>
       <c r="F280" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G280">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H280">
         <v>3</v>
       </c>
       <c r="I280">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J280" t="str">
         <v>carpinteria</v>
@@ -11069,7 +11069,7 @@
         <v>200</v>
       </c>
       <c r="E281">
-        <v>12780</v>
+        <v>18509</v>
       </c>
       <c r="F281" t="str">
         <v>OK_MIXTO</v>
@@ -11084,7 +11084,7 @@
         <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>mecanica_especializada</v>
+        <v>mecanica</v>
       </c>
       <c r="K281" t="str">
         <v>NO</v>
@@ -11107,16 +11107,16 @@
         <v>200</v>
       </c>
       <c r="E282">
-        <v>20856</v>
+        <v>19544</v>
       </c>
       <c r="F282" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G282">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H282">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I282">
         <v>5</v>
@@ -11145,19 +11145,19 @@
         <v>200</v>
       </c>
       <c r="E283">
-        <v>21072</v>
+        <v>18026</v>
       </c>
       <c r="F283" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G283">
         <v>7</v>
       </c>
       <c r="H283">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I283">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J283" t="str">
         <v>impermeabilizacion</v>
@@ -11183,19 +11183,19 @@
         <v>200</v>
       </c>
       <c r="E284">
-        <v>19773</v>
+        <v>20402</v>
       </c>
       <c r="F284" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G284">
         <v>12</v>
       </c>
       <c r="H284">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I284">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J284" t="str">
         <v>impermeabilizacion</v>
@@ -11204,7 +11204,7 @@
         <v>SI</v>
       </c>
       <c r="L284" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="285">
@@ -11221,7 +11221,7 @@
         <v>200</v>
       </c>
       <c r="E285">
-        <v>22310</v>
+        <v>27361</v>
       </c>
       <c r="F285" t="str">
         <v>OK_MIXTO</v>
@@ -11259,16 +11259,16 @@
         <v>200</v>
       </c>
       <c r="E286">
-        <v>14910</v>
+        <v>12621</v>
       </c>
       <c r="F286" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G286">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H286">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I286">
         <v>5</v>
@@ -11297,19 +11297,19 @@
         <v>200</v>
       </c>
       <c r="E287">
-        <v>24995</v>
+        <v>24362</v>
       </c>
       <c r="F287" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G287">
         <v>8</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I287">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J287" t="str">
         <v>impermeabilizacion</v>
@@ -11335,19 +11335,19 @@
         <v>200</v>
       </c>
       <c r="E288">
-        <v>24891</v>
+        <v>28646</v>
       </c>
       <c r="F288" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G288">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H288">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I288">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J288" t="str">
         <v>impermeabilizacion</v>
@@ -11373,19 +11373,19 @@
         <v>200</v>
       </c>
       <c r="E289">
-        <v>16826</v>
+        <v>19305</v>
       </c>
       <c r="F289" t="str">
         <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G289">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H289">
         <v>0</v>
       </c>
       <c r="I289">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J289" t="str">
         <v>impermeabilizacion</v>
@@ -11411,19 +11411,19 @@
         <v>200</v>
       </c>
       <c r="E290">
-        <v>22462</v>
+        <v>19241</v>
       </c>
       <c r="F290" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G290">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H290">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I290">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J290" t="str">
         <v>impermeabilizacion</v>
@@ -11449,19 +11449,19 @@
         <v>200</v>
       </c>
       <c r="E291">
-        <v>24574</v>
+        <v>26522</v>
       </c>
       <c r="F291" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G291">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H291">
         <v>4</v>
       </c>
       <c r="I291">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J291" t="str">
         <v>impermeabilizacion</v>
@@ -11487,19 +11487,19 @@
         <v>200</v>
       </c>
       <c r="E292">
-        <v>20037</v>
+        <v>20131</v>
       </c>
       <c r="F292" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G292">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H292">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I292">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J292" t="str">
         <v>impermeabilizacion</v>
@@ -11525,25 +11525,25 @@
         <v>200</v>
       </c>
       <c r="E293">
-        <v>18275</v>
+        <v>21245</v>
       </c>
       <c r="F293" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G293">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H293">
         <v>3</v>
       </c>
       <c r="I293">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J293" t="str">
-        <v>impermeabilizacion</v>
+        <v>tejados_cubiertas</v>
       </c>
       <c r="K293" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L293" t="str">
         <v/>
@@ -11563,16 +11563,16 @@
         <v>200</v>
       </c>
       <c r="E294">
-        <v>14186</v>
+        <v>13211</v>
       </c>
       <c r="F294" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G294">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H294">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I294">
         <v>3</v>
@@ -11601,19 +11601,19 @@
         <v>200</v>
       </c>
       <c r="E295">
-        <v>19574</v>
+        <v>22224</v>
       </c>
       <c r="F295" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G295">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H295">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I295">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J295" t="str">
         <v>impermeabilizacion</v>
@@ -11639,19 +11639,19 @@
         <v>200</v>
       </c>
       <c r="E296">
-        <v>18406</v>
+        <v>12180</v>
       </c>
       <c r="F296" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G296">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I296">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J296" t="str">
         <v>impermeabilizacion</v>
@@ -11677,19 +11677,19 @@
         <v>200</v>
       </c>
       <c r="E297">
-        <v>23931</v>
+        <v>26590</v>
       </c>
       <c r="F297" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G297">
         <v>10</v>
       </c>
       <c r="H297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I297">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J297" t="str">
         <v>impermeabilizacion</v>
@@ -11715,19 +11715,19 @@
         <v>200</v>
       </c>
       <c r="E298">
-        <v>18099</v>
+        <v>19449</v>
       </c>
       <c r="F298" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G298">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H298">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I298">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J298" t="str">
         <v>impermeabilizacion</v>
@@ -11753,19 +11753,19 @@
         <v>200</v>
       </c>
       <c r="E299">
-        <v>25358</v>
+        <v>24750</v>
       </c>
       <c r="F299" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G299">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H299">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I299">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J299" t="str">
         <v>impermeabilizacion</v>
@@ -11791,19 +11791,19 @@
         <v>200</v>
       </c>
       <c r="E300">
-        <v>20838</v>
+        <v>20889</v>
       </c>
       <c r="F300" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G300">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H300">
         <v>2</v>
       </c>
       <c r="I300">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J300" t="str">
         <v>impermeabilizacion</v>
@@ -11829,19 +11829,19 @@
         <v>200</v>
       </c>
       <c r="E301">
-        <v>13112</v>
+        <v>17405</v>
       </c>
       <c r="F301" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G301">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H301">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I301">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J301" t="str">
         <v>tejados_cubiertas</v>
@@ -11867,19 +11867,19 @@
         <v>200</v>
       </c>
       <c r="E302">
-        <v>14193</v>
+        <v>17931</v>
       </c>
       <c r="F302" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G302">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H302">
         <v>1</v>
       </c>
       <c r="I302">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J302" t="str">
         <v>contra_incendios</v>
@@ -11905,19 +11905,19 @@
         <v>200</v>
       </c>
       <c r="E303">
-        <v>18704</v>
+        <v>21296</v>
       </c>
       <c r="F303" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G303">
         <v>6</v>
       </c>
       <c r="H303">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I303">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J303" t="str">
         <v>contra_incendios</v>
@@ -11943,16 +11943,16 @@
         <v>200</v>
       </c>
       <c r="E304">
-        <v>22345</v>
+        <v>22840</v>
       </c>
       <c r="F304" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G304">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I304">
         <v>7</v>
@@ -11981,7 +11981,7 @@
         <v>200</v>
       </c>
       <c r="E305">
-        <v>20328</v>
+        <v>13397</v>
       </c>
       <c r="F305" t="str">
         <v>OK_MIXTO</v>
@@ -12019,19 +12019,19 @@
         <v>200</v>
       </c>
       <c r="E306">
-        <v>22382</v>
+        <v>25258</v>
       </c>
       <c r="F306" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G306">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H306">
         <v>1</v>
       </c>
       <c r="I306">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J306" t="str">
         <v>contra_incendios</v>
@@ -12057,19 +12057,19 @@
         <v>200</v>
       </c>
       <c r="E307">
-        <v>25614</v>
+        <v>25282</v>
       </c>
       <c r="F307" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G307">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H307">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I307">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J307" t="str">
         <v>contra_incendios</v>
@@ -12095,19 +12095,19 @@
         <v>200</v>
       </c>
       <c r="E308">
-        <v>23611</v>
+        <v>22025</v>
       </c>
       <c r="F308" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G308">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H308">
         <v>2</v>
       </c>
       <c r="I308">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J308" t="str">
         <v>contra_incendios</v>
@@ -12133,19 +12133,19 @@
         <v>200</v>
       </c>
       <c r="E309">
-        <v>23447</v>
+        <v>23206</v>
       </c>
       <c r="F309" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G309">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H309">
         <v>3</v>
       </c>
       <c r="I309">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J309" t="str">
         <v>contra_incendios</v>
@@ -12171,19 +12171,19 @@
         <v>200</v>
       </c>
       <c r="E310">
-        <v>17453</v>
+        <v>19213</v>
       </c>
       <c r="F310" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G310">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H310">
         <v>9</v>
       </c>
       <c r="I310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J310" t="str">
         <v>contra_incendios</v>
@@ -12192,7 +12192,7 @@
         <v>SI</v>
       </c>
       <c r="L310" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="311">
@@ -12209,19 +12209,19 @@
         <v>200</v>
       </c>
       <c r="E311">
-        <v>15048</v>
+        <v>21519</v>
       </c>
       <c r="F311" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G311">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H311">
         <v>2</v>
       </c>
       <c r="I311">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J311" t="str">
         <v>contra_incendios</v>
@@ -12247,19 +12247,19 @@
         <v>200</v>
       </c>
       <c r="E312">
-        <v>12864</v>
+        <v>14179</v>
       </c>
       <c r="F312" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G312">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H312">
         <v>5</v>
       </c>
       <c r="I312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J312" t="str">
         <v>contra_incendios</v>
@@ -12285,16 +12285,16 @@
         <v>200</v>
       </c>
       <c r="E313">
-        <v>29515</v>
+        <v>30750</v>
       </c>
       <c r="F313" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G313">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H313">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I313">
         <v>6</v>
@@ -12323,7 +12323,7 @@
         <v>200</v>
       </c>
       <c r="E314">
-        <v>13027</v>
+        <v>11137</v>
       </c>
       <c r="F314" t="str">
         <v>OK_MIXTO</v>
@@ -12361,19 +12361,19 @@
         <v>200</v>
       </c>
       <c r="E315">
-        <v>28685</v>
+        <v>19074</v>
       </c>
       <c r="F315" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G315">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H315">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I315">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J315" t="str">
         <v>contra_incendios</v>
@@ -12399,7 +12399,7 @@
         <v>200</v>
       </c>
       <c r="E316">
-        <v>15997</v>
+        <v>14787</v>
       </c>
       <c r="F316" t="str">
         <v>OK_MIXTO</v>
@@ -12408,10 +12408,10 @@
         <v>6</v>
       </c>
       <c r="H316">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I316">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J316" t="str">
         <v>climatizacion</v>
@@ -12437,7 +12437,7 @@
         <v>200</v>
       </c>
       <c r="E317">
-        <v>16341</v>
+        <v>15413</v>
       </c>
       <c r="F317" t="str">
         <v>OK_MIXTO</v>
@@ -12475,16 +12475,16 @@
         <v>200</v>
       </c>
       <c r="E318">
-        <v>22069</v>
+        <v>27597</v>
       </c>
       <c r="F318" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G318">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H318">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I318">
         <v>5</v>
@@ -12513,19 +12513,19 @@
         <v>200</v>
       </c>
       <c r="E319">
-        <v>28353</v>
+        <v>23542</v>
       </c>
       <c r="F319" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G319">
         <v>8</v>
       </c>
       <c r="H319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I319">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J319" t="str">
         <v>contra_incendios</v>
@@ -12551,19 +12551,19 @@
         <v>200</v>
       </c>
       <c r="E320">
-        <v>15892</v>
+        <v>12125</v>
       </c>
       <c r="F320" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G320">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H320">
         <v>3</v>
       </c>
       <c r="I320">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J320" t="str">
         <v>contra_incendios</v>
@@ -12589,7 +12589,7 @@
         <v>200</v>
       </c>
       <c r="E321">
-        <v>28010</v>
+        <v>28229</v>
       </c>
       <c r="F321" t="str">
         <v>OK_MIXTO</v>
@@ -12598,10 +12598,10 @@
         <v>12</v>
       </c>
       <c r="H321">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I321">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J321" t="str">
         <v>contra_incendios</v>
@@ -12627,19 +12627,19 @@
         <v>200</v>
       </c>
       <c r="E322">
-        <v>24590</v>
+        <v>29034</v>
       </c>
       <c r="F322" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G322">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H322">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I322">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J322" t="str">
         <v>fachadas</v>
@@ -12665,19 +12665,19 @@
         <v>200</v>
       </c>
       <c r="E323">
-        <v>28670</v>
+        <v>26997</v>
       </c>
       <c r="F323" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G323">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H323">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I323">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J323" t="str">
         <v>fachadas</v>
@@ -12703,19 +12703,19 @@
         <v>200</v>
       </c>
       <c r="E324">
-        <v>15043</v>
+        <v>16878</v>
       </c>
       <c r="F324" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G324">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H324">
         <v>1</v>
       </c>
       <c r="I324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J324" t="str">
         <v>fachadas</v>
@@ -12741,7 +12741,7 @@
         <v>200</v>
       </c>
       <c r="E325">
-        <v>16340</v>
+        <v>18927</v>
       </c>
       <c r="F325" t="str">
         <v>OK_MIXTO</v>
@@ -12779,16 +12779,16 @@
         <v>200</v>
       </c>
       <c r="E326">
-        <v>27038</v>
+        <v>21715</v>
       </c>
       <c r="F326" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G326">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H326">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I326">
         <v>8</v>
@@ -12817,7 +12817,7 @@
         <v>200</v>
       </c>
       <c r="E327">
-        <v>13395</v>
+        <v>19464</v>
       </c>
       <c r="F327" t="str">
         <v>OK_MIXTO</v>
@@ -12855,19 +12855,19 @@
         <v>200</v>
       </c>
       <c r="E328">
-        <v>22078</v>
+        <v>19269</v>
       </c>
       <c r="F328" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G328">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H328">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I328">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J328" t="str">
         <v>fachadas</v>
@@ -12893,7 +12893,7 @@
         <v>200</v>
       </c>
       <c r="E329">
-        <v>12207</v>
+        <v>11995</v>
       </c>
       <c r="F329" t="str">
         <v>OK_MIXTO</v>
@@ -12931,19 +12931,19 @@
         <v>200</v>
       </c>
       <c r="E330">
-        <v>28037</v>
+        <v>21730</v>
       </c>
       <c r="F330" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G330">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H330">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I330">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J330" t="str">
         <v>fachadas</v>
@@ -12969,16 +12969,16 @@
         <v>200</v>
       </c>
       <c r="E331">
-        <v>21175</v>
+        <v>20598</v>
       </c>
       <c r="F331" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G331">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H331">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I331">
         <v>5</v>
@@ -13007,7 +13007,7 @@
         <v>200</v>
       </c>
       <c r="E332">
-        <v>24230</v>
+        <v>25459</v>
       </c>
       <c r="F332" t="str">
         <v>OK_MIXTO</v>
@@ -13016,10 +13016,10 @@
         <v>10</v>
       </c>
       <c r="H332">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I332">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J332" t="str">
         <v>fachadas</v>
@@ -13045,7 +13045,7 @@
         <v>200</v>
       </c>
       <c r="E333">
-        <v>16640</v>
+        <v>15577</v>
       </c>
       <c r="F333" t="str">
         <v>OK_MIXTO</v>
@@ -13083,19 +13083,19 @@
         <v>200</v>
       </c>
       <c r="E334">
-        <v>12744</v>
+        <v>22695</v>
       </c>
       <c r="F334" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G334">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H334">
         <v>3</v>
       </c>
       <c r="I334">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J334" t="str">
         <v>fachadas</v>
@@ -13121,19 +13121,19 @@
         <v>200</v>
       </c>
       <c r="E335">
-        <v>15136</v>
+        <v>19168</v>
       </c>
       <c r="F335" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G335">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H335">
         <v>1</v>
       </c>
       <c r="I335">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J335" t="str">
         <v>fachadas</v>
@@ -13159,7 +13159,7 @@
         <v>200</v>
       </c>
       <c r="E336">
-        <v>17287</v>
+        <v>22449</v>
       </c>
       <c r="F336" t="str">
         <v>OK_MIXTO</v>
@@ -13168,16 +13168,16 @@
         <v>7</v>
       </c>
       <c r="H336">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I336">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J336" t="str">
-        <v>cristaleria</v>
+        <v>fachadas</v>
       </c>
       <c r="K336" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L336" t="str">
         <v/>
@@ -13197,19 +13197,19 @@
         <v>200</v>
       </c>
       <c r="E337">
-        <v>20135</v>
+        <v>20611</v>
       </c>
       <c r="F337" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G337">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H337">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I337">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J337" t="str">
         <v>fachadas</v>
@@ -13235,7 +13235,7 @@
         <v>200</v>
       </c>
       <c r="E338">
-        <v>12201</v>
+        <v>12033</v>
       </c>
       <c r="F338" t="str">
         <v>OK_MIXTO</v>
@@ -13273,19 +13273,19 @@
         <v>200</v>
       </c>
       <c r="E339">
-        <v>13639</v>
+        <v>15682</v>
       </c>
       <c r="F339" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G339">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H339">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I339">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J339" t="str">
         <v>electricidad</v>
@@ -13311,19 +13311,19 @@
         <v>200</v>
       </c>
       <c r="E340">
-        <v>13454</v>
+        <v>16537</v>
       </c>
       <c r="F340" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G340">
+        <v>8</v>
+      </c>
+      <c r="H340">
+        <v>2</v>
+      </c>
+      <c r="I340">
         <v>6</v>
-      </c>
-      <c r="H340">
-        <v>1</v>
-      </c>
-      <c r="I340">
-        <v>5</v>
       </c>
       <c r="J340" t="str">
         <v>fachadas</v>
@@ -13349,19 +13349,19 @@
         <v>200</v>
       </c>
       <c r="E341">
-        <v>17913</v>
+        <v>17615</v>
       </c>
       <c r="F341" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G341">
         <v>5</v>
       </c>
       <c r="H341">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J341" t="str">
         <v>energia_solar</v>
@@ -13387,7 +13387,7 @@
         <v>403</v>
       </c>
       <c r="E342">
-        <v>217</v>
+        <v>141</v>
       </c>
       <c r="F342" t="str">
         <v>ERROR_TECNICO</v>
@@ -13425,19 +13425,19 @@
         <v>200</v>
       </c>
       <c r="E343">
-        <v>14501</v>
+        <v>20922</v>
       </c>
       <c r="F343" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G343">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H343">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I343">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J343" t="str">
         <v>mantenimiento_general</v>
@@ -13463,19 +13463,19 @@
         <v>200</v>
       </c>
       <c r="E344">
-        <v>8488</v>
+        <v>8460</v>
       </c>
       <c r="F344" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G344">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J344" t="str">
         <v>electricidad</v>
@@ -13501,19 +13501,19 @@
         <v>200</v>
       </c>
       <c r="E345">
-        <v>17433</v>
+        <v>16318</v>
       </c>
       <c r="F345" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G345">
+        <v>9</v>
+      </c>
+      <c r="H345">
+        <v>3</v>
+      </c>
+      <c r="I345">
         <v>6</v>
-      </c>
-      <c r="H345">
-        <v>3</v>
-      </c>
-      <c r="I345">
-        <v>3</v>
       </c>
       <c r="J345" t="str">
         <v>mantenimiento_general</v>
@@ -13539,19 +13539,19 @@
         <v>200</v>
       </c>
       <c r="E346">
-        <v>15329</v>
+        <v>13107</v>
       </c>
       <c r="F346" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G346">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H346">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I346">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J346" t="str">
         <v>mantenimiento_general</v>
@@ -13577,7 +13577,7 @@
         <v>403</v>
       </c>
       <c r="E347">
-        <v>194</v>
+        <v>252</v>
       </c>
       <c r="F347" t="str">
         <v>ERROR_TECNICO</v>
@@ -13615,16 +13615,16 @@
         <v>200</v>
       </c>
       <c r="E348">
-        <v>15647</v>
+        <v>15236</v>
       </c>
       <c r="F348" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G348">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H348">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I348">
         <v>5</v>
@@ -13653,25 +13653,25 @@
         <v>200</v>
       </c>
       <c r="E349">
-        <v>17474</v>
+        <v>22284</v>
       </c>
       <c r="F349" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G349">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H349">
+        <v>9</v>
+      </c>
+      <c r="I349">
         <v>4</v>
       </c>
-      <c r="I349">
-        <v>2</v>
-      </c>
       <c r="J349" t="str">
-        <v>mantenimiento_general</v>
+        <v>fontaneria</v>
       </c>
       <c r="K349" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="L349" t="str">
         <v/>
@@ -13691,19 +13691,19 @@
         <v>200</v>
       </c>
       <c r="E350">
-        <v>12075</v>
+        <v>11405</v>
       </c>
       <c r="F350" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G350">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H350">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I350">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J350" t="str">
         <v>cerrajeria</v>
@@ -13712,7 +13712,7 @@
         <v>NO</v>
       </c>
       <c r="L350" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="351">
@@ -13729,19 +13729,19 @@
         <v>200</v>
       </c>
       <c r="E351">
-        <v>14155</v>
+        <v>18355</v>
       </c>
       <c r="F351" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G351">
+        <v>7</v>
+      </c>
+      <c r="H351">
+        <v>1</v>
+      </c>
+      <c r="I351">
         <v>6</v>
-      </c>
-      <c r="H351">
-        <v>3</v>
-      </c>
-      <c r="I351">
-        <v>3</v>
       </c>
       <c r="J351" t="str">
         <v>pintura</v>
@@ -13767,19 +13767,19 @@
         <v>200</v>
       </c>
       <c r="E352">
-        <v>20660</v>
+        <v>18212</v>
       </c>
       <c r="F352" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G352">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H352">
         <v>4</v>
       </c>
       <c r="I352">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J352" t="str">
         <v>albanileria</v>
@@ -13805,7 +13805,7 @@
         <v>200</v>
       </c>
       <c r="E353">
-        <v>13256</v>
+        <v>12107</v>
       </c>
       <c r="F353" t="str">
         <v>OK_MIXTO</v>
@@ -13814,10 +13814,10 @@
         <v>6</v>
       </c>
       <c r="H353">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J353" t="str">
         <v>mantenimiento_general</v>
@@ -13843,7 +13843,7 @@
         <v>200</v>
       </c>
       <c r="E354">
-        <v>13715</v>
+        <v>13012</v>
       </c>
       <c r="F354" t="str">
         <v>OK_MIXTO</v>
@@ -13881,16 +13881,16 @@
         <v>200</v>
       </c>
       <c r="E355">
-        <v>18255</v>
+        <v>16453</v>
       </c>
       <c r="F355" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G355">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H355">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I355">
         <v>4</v>
@@ -13919,7 +13919,7 @@
         <v>200</v>
       </c>
       <c r="E356">
-        <v>11192</v>
+        <v>11525</v>
       </c>
       <c r="F356" t="str">
         <v>OK_MIXTO</v>
@@ -13957,7 +13957,7 @@
         <v>200</v>
       </c>
       <c r="E357">
-        <v>14259</v>
+        <v>13697</v>
       </c>
       <c r="F357" t="str">
         <v>OK_MIXTO</v>
@@ -13995,7 +13995,7 @@
         <v>200</v>
       </c>
       <c r="E358">
-        <v>14662</v>
+        <v>12335</v>
       </c>
       <c r="F358" t="str">
         <v>OK_MIXTO</v>
@@ -14004,10 +14004,10 @@
         <v>4</v>
       </c>
       <c r="H358">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I358">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J358" t="str">
         <v>cerrajeria</v>
@@ -14033,16 +14033,16 @@
         <v>200</v>
       </c>
       <c r="E359">
-        <v>17078</v>
+        <v>15887</v>
       </c>
       <c r="F359" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G359">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H359">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I359">
         <v>2</v>
@@ -14071,19 +14071,19 @@
         <v>200</v>
       </c>
       <c r="E360">
-        <v>15029</v>
+        <v>12781</v>
       </c>
       <c r="F360" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G360">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H360">
         <v>3</v>
       </c>
       <c r="I360">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J360" t="str">
         <v>electricidad</v>
@@ -14109,19 +14109,19 @@
         <v>200</v>
       </c>
       <c r="E361">
-        <v>13528</v>
+        <v>13767</v>
       </c>
       <c r="F361" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G361">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H361">
         <v>4</v>
       </c>
       <c r="I361">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J361" t="str">
         <v>jardineria</v>
@@ -14147,7 +14147,7 @@
         <v>200</v>
       </c>
       <c r="E362">
-        <v>19336</v>
+        <v>18550</v>
       </c>
       <c r="F362" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14185,19 +14185,19 @@
         <v>200</v>
       </c>
       <c r="E363">
-        <v>25072</v>
+        <v>26975</v>
       </c>
       <c r="F363" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G363">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H363">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I363">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J363" t="str">
         <v>reforma_integral</v>
@@ -14223,19 +14223,19 @@
         <v>200</v>
       </c>
       <c r="E364">
-        <v>39276</v>
+        <v>43249</v>
       </c>
       <c r="F364" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G364">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H364">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I364">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J364" t="str">
         <v>reforma_integral</v>
@@ -14261,19 +14261,19 @@
         <v>200</v>
       </c>
       <c r="E365">
-        <v>51505</v>
+        <v>37525</v>
       </c>
       <c r="F365" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G365">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H365">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I365">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J365" t="str">
         <v>reforma_integral</v>
@@ -14299,19 +14299,19 @@
         <v>200</v>
       </c>
       <c r="E366">
-        <v>35903</v>
+        <v>27232</v>
       </c>
       <c r="F366" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G366">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H366">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I366">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J366" t="str">
         <v>reforma_integral</v>
@@ -14337,19 +14337,19 @@
         <v>200</v>
       </c>
       <c r="E367">
-        <v>35312</v>
+        <v>34946</v>
       </c>
       <c r="F367" t="str">
-        <v>OK_MIXTO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G367">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H367">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I367">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J367" t="str">
         <v>reforma_integral</v>
@@ -14358,7 +14358,7 @@
         <v>NO</v>
       </c>
       <c r="L367" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
     </row>
     <row r="368">
@@ -14375,19 +14375,19 @@
         <v>200</v>
       </c>
       <c r="E368">
-        <v>44682</v>
+        <v>35748</v>
       </c>
       <c r="F368" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G368">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H368">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I368">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J368" t="str">
         <v>reforma_integral</v>
@@ -14413,19 +14413,19 @@
         <v>200</v>
       </c>
       <c r="E369">
-        <v>41117</v>
+        <v>44710</v>
       </c>
       <c r="F369" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G369">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H369">
+        <v>10</v>
+      </c>
+      <c r="I369">
         <v>12</v>
-      </c>
-      <c r="I369">
-        <v>7</v>
       </c>
       <c r="J369" t="str">
         <v>reforma_integral</v>
@@ -14451,19 +14451,19 @@
         <v>200</v>
       </c>
       <c r="E370">
-        <v>28815</v>
+        <v>33209</v>
       </c>
       <c r="F370" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G370">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H370">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I370">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J370" t="str">
         <v>reforma_integral</v>
@@ -14489,19 +14489,19 @@
         <v>200</v>
       </c>
       <c r="E371">
-        <v>28638</v>
+        <v>35835</v>
       </c>
       <c r="F371" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G371">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H371">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I371">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J371" t="str">
         <v>reforma_integral</v>
@@ -14527,7 +14527,7 @@
         <v>200</v>
       </c>
       <c r="E372">
-        <v>25543</v>
+        <v>26346</v>
       </c>
       <c r="F372" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14565,19 +14565,19 @@
         <v>200</v>
       </c>
       <c r="E373">
-        <v>29034</v>
+        <v>31721</v>
       </c>
       <c r="F373" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G373">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H373">
+        <v>8</v>
+      </c>
+      <c r="I373">
         <v>7</v>
-      </c>
-      <c r="I373">
-        <v>6</v>
       </c>
       <c r="J373" t="str">
         <v>reforma_integral</v>
@@ -14603,7 +14603,7 @@
         <v>200</v>
       </c>
       <c r="E374">
-        <v>26057</v>
+        <v>27063</v>
       </c>
       <c r="F374" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14641,19 +14641,19 @@
         <v>200</v>
       </c>
       <c r="E375">
-        <v>20010</v>
+        <v>28564</v>
       </c>
       <c r="F375" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G375">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H375">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I375">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J375" t="str">
         <v>reforma_integral</v>
@@ -14679,19 +14679,19 @@
         <v>200</v>
       </c>
       <c r="E376">
-        <v>32454</v>
+        <v>35084</v>
       </c>
       <c r="F376" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G376">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H376">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I376">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J376" t="str">
         <v>reforma_integral</v>
@@ -14717,7 +14717,7 @@
         <v>200</v>
       </c>
       <c r="E377">
-        <v>25042</v>
+        <v>27506</v>
       </c>
       <c r="F377" t="str">
         <v>SOLO_SUGERIDAS</v>
@@ -14755,19 +14755,19 @@
         <v>200</v>
       </c>
       <c r="E378">
-        <v>28523</v>
+        <v>33912</v>
       </c>
       <c r="F378" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G378">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H378">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I378">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J378" t="str">
         <v>reforma_integral</v>
@@ -14793,16 +14793,16 @@
         <v>200</v>
       </c>
       <c r="E379">
-        <v>27052</v>
+        <v>32568</v>
       </c>
       <c r="F379" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G379">
+        <v>12</v>
+      </c>
+      <c r="H379">
         <v>6</v>
-      </c>
-      <c r="H379">
-        <v>0</v>
       </c>
       <c r="I379">
         <v>6</v>
@@ -14831,19 +14831,19 @@
         <v>200</v>
       </c>
       <c r="E380">
-        <v>36703</v>
+        <v>41686</v>
       </c>
       <c r="F380" t="str">
-        <v>SOLO_SUGERIDAS</v>
+        <v>OK_MIXTO</v>
       </c>
       <c r="G380">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H380">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I380">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J380" t="str">
         <v>reforma_integral</v>
@@ -14869,16 +14869,16 @@
         <v>200</v>
       </c>
       <c r="E381">
-        <v>39299</v>
+        <v>42779</v>
       </c>
       <c r="F381" t="str">
-        <v>OK_MIXTO</v>
+        <v>SOLO_SUGERIDAS</v>
       </c>
       <c r="G381">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H381">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I381">
         <v>12</v>
@@ -14907,7 +14907,7 @@
         <v>200</v>
       </c>
       <c r="E382">
-        <v>11121</v>
+        <v>10760</v>
       </c>
       <c r="F382" t="str">
         <v>OK_MIXTO</v>
@@ -14945,19 +14945,19 @@
         <v>200</v>
       </c>
       <c r="E383">
-        <v>13369</v>
+        <v>14694</v>
       </c>
       <c r="F383" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G383">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H383">
         <v>3</v>
       </c>
       <c r="I383">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J383" t="str">
         <v>persianas</v>
@@ -14983,7 +14983,7 @@
         <v>200</v>
       </c>
       <c r="E384">
-        <v>12193</v>
+        <v>12039</v>
       </c>
       <c r="F384" t="str">
         <v>OK_MIXTO</v>
@@ -15021,19 +15021,19 @@
         <v>200</v>
       </c>
       <c r="E385">
-        <v>13653</v>
+        <v>11106</v>
       </c>
       <c r="F385" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G385">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H385">
         <v>2</v>
       </c>
       <c r="I385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J385" t="str">
         <v>persianas</v>
@@ -15059,19 +15059,19 @@
         <v>200</v>
       </c>
       <c r="E386">
-        <v>17762</v>
+        <v>17289</v>
       </c>
       <c r="F386" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G386">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H386">
         <v>1</v>
       </c>
       <c r="I386">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J386" t="str">
         <v>persianas</v>
@@ -15097,25 +15097,25 @@
         <v>200</v>
       </c>
       <c r="E387">
-        <v>12210</v>
+        <v>11829</v>
       </c>
       <c r="F387" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G387">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H387">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I387">
         <v>3</v>
       </c>
       <c r="J387" t="str">
-        <v>carpinteria</v>
+        <v>persianas</v>
       </c>
       <c r="K387" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="L387" t="str">
         <v/>
@@ -15135,7 +15135,7 @@
         <v>200</v>
       </c>
       <c r="E388">
-        <v>18663</v>
+        <v>20245</v>
       </c>
       <c r="F388" t="str">
         <v>OK_MIXTO</v>
@@ -15173,19 +15173,19 @@
         <v>200</v>
       </c>
       <c r="E389">
-        <v>15963</v>
+        <v>14468</v>
       </c>
       <c r="F389" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G389">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H389">
         <v>3</v>
       </c>
       <c r="I389">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J389" t="str">
         <v>carpinteria</v>
@@ -15211,7 +15211,7 @@
         <v>200</v>
       </c>
       <c r="E390">
-        <v>19468</v>
+        <v>12547</v>
       </c>
       <c r="F390" t="str">
         <v>OK_MIXTO</v>
@@ -15249,19 +15249,19 @@
         <v>200</v>
       </c>
       <c r="E391">
-        <v>11230</v>
+        <v>12954</v>
       </c>
       <c r="F391" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G391">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H391">
         <v>4</v>
       </c>
       <c r="I391">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J391" t="str">
         <v>persianas</v>
@@ -15287,19 +15287,19 @@
         <v>200</v>
       </c>
       <c r="E392">
-        <v>15346</v>
+        <v>14335</v>
       </c>
       <c r="F392" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G392">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H392">
         <v>1</v>
       </c>
       <c r="I392">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J392" t="str">
         <v>persianas</v>
@@ -15325,7 +15325,7 @@
         <v>200</v>
       </c>
       <c r="E393">
-        <v>16266</v>
+        <v>11996</v>
       </c>
       <c r="F393" t="str">
         <v>OK_MIXTO</v>
@@ -15334,10 +15334,10 @@
         <v>4</v>
       </c>
       <c r="H393">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I393">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J393" t="str">
         <v>persianas</v>
@@ -15363,16 +15363,16 @@
         <v>200</v>
       </c>
       <c r="E394">
-        <v>21306</v>
+        <v>16084</v>
       </c>
       <c r="F394" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G394">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H394">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I394">
         <v>5</v>
@@ -15401,19 +15401,19 @@
         <v>200</v>
       </c>
       <c r="E395">
-        <v>18005</v>
+        <v>18962</v>
       </c>
       <c r="F395" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G395">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H395">
         <v>2</v>
       </c>
       <c r="I395">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J395" t="str">
         <v>persianas</v>
@@ -15439,16 +15439,16 @@
         <v>200</v>
       </c>
       <c r="E396">
-        <v>12212</v>
+        <v>12718</v>
       </c>
       <c r="F396" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G396">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H396">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I396">
         <v>2</v>
@@ -15477,19 +15477,19 @@
         <v>200</v>
       </c>
       <c r="E397">
-        <v>14211</v>
+        <v>18211</v>
       </c>
       <c r="F397" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G397">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H397">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I397">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J397" t="str">
         <v>carpinteria</v>
@@ -15515,7 +15515,7 @@
         <v>200</v>
       </c>
       <c r="E398">
-        <v>12054</v>
+        <v>11276</v>
       </c>
       <c r="F398" t="str">
         <v>OK_MIXTO</v>
@@ -15553,7 +15553,7 @@
         <v>200</v>
       </c>
       <c r="E399">
-        <v>10946</v>
+        <v>11717</v>
       </c>
       <c r="F399" t="str">
         <v>OK_MIXTO</v>
@@ -15591,19 +15591,19 @@
         <v>200</v>
       </c>
       <c r="E400">
-        <v>16666</v>
+        <v>16863</v>
       </c>
       <c r="F400" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G400">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H400">
         <v>3</v>
       </c>
       <c r="I400">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J400" t="str">
         <v>cerrajeria</v>
@@ -15629,16 +15629,16 @@
         <v>200</v>
       </c>
       <c r="E401">
-        <v>22737</v>
+        <v>25526</v>
       </c>
       <c r="F401" t="str">
         <v>OK_MIXTO</v>
       </c>
       <c r="G401">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H401">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I401">
         <v>5</v>
@@ -15744,7 +15744,7 @@
         <v>55%</v>
       </c>
       <c r="K2">
-        <v>19284</v>
+        <v>19522</v>
       </c>
     </row>
     <row r="3">
@@ -15776,10 +15776,10 @@
         <v>95%</v>
       </c>
       <c r="J3" t="str">
-        <v>85%</v>
+        <v>80%</v>
       </c>
       <c r="K3">
-        <v>15879</v>
+        <v>15718</v>
       </c>
     </row>
     <row r="4">
@@ -15793,7 +15793,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -15805,16 +15805,16 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
-        <v>95%</v>
+        <v>90%</v>
       </c>
       <c r="J4" t="str">
         <v>80%</v>
       </c>
       <c r="K4">
-        <v>13705</v>
+        <v>13346</v>
       </c>
     </row>
     <row r="5">
@@ -15828,28 +15828,28 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>95%</v>
+        <v>85%</v>
       </c>
       <c r="J5" t="str">
-        <v>80%</v>
+        <v>70%</v>
       </c>
       <c r="K5">
-        <v>20142</v>
+        <v>19454</v>
       </c>
     </row>
     <row r="6">
@@ -15863,10 +15863,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -15875,16 +15875,16 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>90%</v>
+        <v>95%</v>
       </c>
       <c r="J6" t="str">
         <v>90%</v>
       </c>
       <c r="K6">
-        <v>20694</v>
+        <v>20440</v>
       </c>
     </row>
     <row r="7">
@@ -15919,7 +15919,7 @@
         <v>85%</v>
       </c>
       <c r="K7">
-        <v>15266</v>
+        <v>15408</v>
       </c>
     </row>
     <row r="8">
@@ -15933,7 +15933,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -15945,16 +15945,16 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>100%</v>
+        <v>95%</v>
       </c>
       <c r="J8" t="str">
         <v>75%</v>
       </c>
       <c r="K8">
-        <v>16894</v>
+        <v>16277</v>
       </c>
     </row>
     <row r="9">
@@ -15965,31 +15965,31 @@
         <v>20</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>16</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
-        <v>85%</v>
+        <v>80%</v>
       </c>
       <c r="J9" t="str">
-        <v>85%</v>
+        <v>80%</v>
       </c>
       <c r="K9">
-        <v>21066</v>
+        <v>21105</v>
       </c>
     </row>
     <row r="10">
@@ -16003,10 +16003,10 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -16018,13 +16018,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>90%</v>
+        <v>95%</v>
       </c>
       <c r="J10" t="str">
-        <v>75%</v>
+        <v>80%</v>
       </c>
       <c r="K10">
-        <v>18598</v>
+        <v>19722</v>
       </c>
     </row>
     <row r="11">
@@ -16038,13 +16038,13 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -16053,13 +16053,13 @@
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>100%</v>
+        <v>90%</v>
       </c>
       <c r="J11" t="str">
         <v>75%</v>
       </c>
       <c r="K11">
-        <v>16893</v>
+        <v>15848</v>
       </c>
     </row>
     <row r="12">
@@ -16076,7 +16076,7 @@
         <v>16</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -16085,16 +16085,16 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>80%</v>
       </c>
       <c r="J12" t="str">
-        <v>95%</v>
+        <v>90%</v>
       </c>
       <c r="K12">
-        <v>20224</v>
+        <v>20705</v>
       </c>
     </row>
     <row r="13">
@@ -16108,10 +16108,10 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -16123,13 +16123,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>95%</v>
+        <v>100%</v>
       </c>
       <c r="J13" t="str">
         <v>85%</v>
       </c>
       <c r="K13">
-        <v>15492</v>
+        <v>15689</v>
       </c>
     </row>
     <row r="14">
@@ -16143,10 +16143,10 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -16155,16 +16155,16 @@
         <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
-        <v>90%</v>
+        <v>80%</v>
       </c>
       <c r="J14" t="str">
-        <v>30%</v>
+        <v>25%</v>
       </c>
       <c r="K14">
-        <v>13357</v>
+        <v>13313</v>
       </c>
     </row>
     <row r="15">
@@ -16196,10 +16196,10 @@
         <v>100%</v>
       </c>
       <c r="J15" t="str">
-        <v>70%</v>
+        <v>75%</v>
       </c>
       <c r="K15">
-        <v>15269</v>
+        <v>14781</v>
       </c>
     </row>
     <row r="16">
@@ -16213,10 +16213,10 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -16228,13 +16228,13 @@
         <v>0</v>
       </c>
       <c r="I16" t="str">
-        <v>90%</v>
+        <v>100%</v>
       </c>
       <c r="J16" t="str">
-        <v>70%</v>
+        <v>75%</v>
       </c>
       <c r="K16">
-        <v>14117</v>
+        <v>13813</v>
       </c>
     </row>
     <row r="17">
@@ -16266,10 +16266,10 @@
         <v>95%</v>
       </c>
       <c r="J17" t="str">
-        <v>95%</v>
+        <v>90%</v>
       </c>
       <c r="K17">
-        <v>17992</v>
+        <v>17959</v>
       </c>
     </row>
     <row r="18">
@@ -16283,10 +16283,10 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -16295,16 +16295,16 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="str">
-        <v>65%</v>
+        <v>70%</v>
       </c>
       <c r="J18" t="str">
         <v>0%</v>
       </c>
       <c r="K18">
-        <v>31969</v>
+        <v>33260</v>
       </c>
     </row>
     <row r="19">
@@ -16318,10 +16318,10 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -16330,16 +16330,16 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="str">
-        <v>90%</v>
+        <v>95%</v>
       </c>
       <c r="J19" t="str">
         <v>75%</v>
       </c>
       <c r="K19">
-        <v>17499</v>
+        <v>16135</v>
       </c>
     </row>
     <row r="20">
@@ -16356,7 +16356,7 @@
         <v>19</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -16365,7 +16365,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="str">
         <v>95%</v>
@@ -16374,7 +16374,7 @@
         <v>70%</v>
       </c>
       <c r="K20">
-        <v>17528</v>
+        <v>18192</v>
       </c>
     </row>
     <row r="21">
@@ -16385,10 +16385,10 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -16409,7 +16409,7 @@
         <v>100%</v>
       </c>
       <c r="K21">
-        <v>16493</v>
+        <v>16920</v>
       </c>
     </row>
     <row r="22">
@@ -16420,31 +16420,31 @@
         <v>400</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>367</v>
       </c>
       <c r="E22">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I22" t="str">
         <v>92%</v>
       </c>
       <c r="J22" t="str">
-        <v>74%</v>
+        <v>73%</v>
       </c>
       <c r="K22">
-        <v>17918</v>
+        <v>17880</v>
       </c>
     </row>
   </sheetData>
@@ -16456,7 +16456,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H18"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -16496,19 +16496,19 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>235</v>
+        <v>7</v>
       </c>
       <c r="B2" t="str">
-        <v>Energía Solar</v>
+        <v>Fontanería</v>
       </c>
       <c r="C2" t="str">
-        <v>Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético</v>
+        <v>Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad</v>
       </c>
       <c r="D2">
         <v>200</v>
       </c>
       <c r="E2">
-        <v>27042</v>
+        <v>23251</v>
       </c>
       <c r="F2" t="str">
         <v>VACIO</v>
@@ -16517,90 +16517,428 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>{"transcript":"Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
+        <v>{"transcript":"Instalación completa de baño nuevo con lavabo empotrado, inodoro suspendido, ducha y griferías cromadas de buena calidad","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>239</v>
+        <v>22</v>
       </c>
       <c r="B3" t="str">
-        <v>Energía Solar</v>
+        <v>Electricidad</v>
       </c>
       <c r="C3" t="str">
-        <v>Proyecto de comunidad energética solar en barrio, 20 viviendas participantes, gestoría incluida</v>
+        <v>Instalación de enchufe en terraza con protección IP exterior y toma de tierra</v>
       </c>
       <c r="D3">
         <v>200</v>
       </c>
       <c r="E3">
-        <v>26750</v>
+        <v>19466</v>
       </c>
       <c r="F3" t="str">
-        <v>VACIO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
       <c r="H3" t="str">
-        <v>{"transcript":"Proyecto de comunidad energética solar en barrio, 20 viviendas participantes, gestoría incluida","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calcu</v>
+        <v xml:space="preserve">{"transcript":"Instalación de enchufe en terraza con protección IP exterior y toma de tierra","quote":{"resumen":{"texto_original":"Instalación de enchufe en terraza con protección IP exterior y toma de tierra","tipo_presupuesto":"servicio","requiere_revision_general":false,"alertas":["Verificar si </v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>341</v>
+        <v>104</v>
       </c>
       <c r="B4" t="str">
-        <v>Mantenimiento General</v>
+        <v>Climatización</v>
       </c>
       <c r="C4" t="str">
-        <v>Contrato de mantenimiento mensual de edificio de oficinas, electricidad, fontanería y carpintería</v>
+        <v>Reparar aire acondicionado que no enfría, revisar gas y compresor de la unidad exterior</v>
       </c>
       <c r="D4">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="E4">
-        <v>217</v>
+        <v>16666</v>
       </c>
       <c r="F4" t="str">
-        <v>ERROR_TECNICO</v>
+        <v>PRECIO_INVALIDO</v>
       </c>
       <c r="G4" t="str">
-        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
+        <v>Partida de catálogo con precio 0 o nulo</v>
       </c>
       <c r="H4" t="str">
-        <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
+        <v>{"transcript":"Reparar aire acondicionado que no enfría, revisar gas y compresor de la unidad exterior","quote":{"resumen":{"texto_original":"Reparar aire acondicionado que no enfría, revisar gas y compresor de la unidad exterior","tipo_presupuesto":"mantenimiento_recurrente","requiere_revision_gene</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
+        <v>106</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Climatización</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados</v>
+      </c>
+      <c r="D5">
+        <v>200</v>
+      </c>
+      <c r="E5">
+        <v>25232</v>
+      </c>
+      <c r="F5" t="str">
+        <v>VACIO</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>{"transcript":"Instalación de suelo radiante con bomba de calor en planta baja de 90 metros cuadrados","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calculos":{"su</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>122</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Tejados/Cubiertas</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Cambio completo de cubierta plana en piso ático, impermeabilización con lámina líquida</v>
+      </c>
+      <c r="D6">
+        <v>200</v>
+      </c>
+      <c r="E6">
+        <v>24035</v>
+      </c>
+      <c r="F6" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H6" t="str">
+        <v>{"transcript":"Cambio completo de cubierta plana en piso ático, impermeabilización con lámina líquida","quote":{"resumen":{"texto_original":"Cambio completo de cubierta plana en piso ático, impermeabilización con lámina líquida","tipo_presupuesto":"reforma","requiere_revision_general":true,"alertas"</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>167</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Suelos y Alicatados</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Alicatar piscina con gresite azul, vaciado y colocación en paredes y fondo, 40 metros cuadrados</v>
+      </c>
+      <c r="D7">
+        <v>200</v>
+      </c>
+      <c r="E7">
+        <v>21349</v>
+      </c>
+      <c r="F7" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H7" t="str">
+        <v>{"transcript":"Alicatar piscina con gresite azul, vaciado y colocación en paredes y fondo, 40 metros cuadrados","quote":{"resumen":{"texto_original":"Alicatar piscina con gresite azul, vaciado y colocación en paredes y fondo, 40 metros cuadrados","tipo_presupuesto":"reforma","requiere_revision_gener</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>183</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Cerrajería</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Apertura de urgencia de puerta de casa, me he quedado encerrado fuera sin llaves</v>
+      </c>
+      <c r="D8">
+        <v>200</v>
+      </c>
+      <c r="E8">
+        <v>9275</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H8" t="str">
+        <v>{"transcript":"Apertura de urgencia de puerta de casa, me he quedado encerrado fuera sin llaves","quote":{"resumen":{"texto_original":"Apertura de urgencia de puerta de casa, me he quedado encerrado fuera sin llaves","tipo_presupuesto":"servicio","requiere_revision_general":false,"alertas":["Servici</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>222</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Energía Solar</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Presupuesto para instalación solar con baterías de litio para desconectarse de la red eléctrica</v>
+      </c>
+      <c r="D9">
+        <v>200</v>
+      </c>
+      <c r="E9">
+        <v>29759</v>
+      </c>
+      <c r="F9" t="str">
+        <v>VACIO</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>{"transcript":"Presupuesto para instalación solar con baterías de litio para desconectarse de la red eléctrica","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calcu</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>235</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Energía Solar</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético</v>
+      </c>
+      <c r="D10">
+        <v>200</v>
+      </c>
+      <c r="E10">
+        <v>28600</v>
+      </c>
+      <c r="F10" t="str">
+        <v>VACIO</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>{"transcript":"Instalar sistema híbrido solar y aerotermia para vivienda eficiente, cálculo de ahorro energético","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"cal</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>236</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Energía Solar</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Monitorizar producción de instalación fotovoltaica con aplicación y alertas de fallo</v>
+      </c>
+      <c r="D11">
+        <v>200</v>
+      </c>
+      <c r="E11">
+        <v>15834</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H11" t="str">
+        <v>{"transcript":"Monitorizar producción de instalación fotovoltaica con aplicación y alertas de fallo","quote":{"resumen":{"texto_original":"Monitorizar producción de instalación fotovoltaica con aplicación y alertas de fallo","tipo_presupuesto":"servicio","requiere_revision_general":false,"alertas":[</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>239</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Energía Solar</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Proyecto de comunidad energética solar en barrio, 20 viviendas participantes, gestoría incluida</v>
+      </c>
+      <c r="D12">
+        <v>200</v>
+      </c>
+      <c r="E12">
+        <v>27870</v>
+      </c>
+      <c r="F12" t="str">
+        <v>VACIO</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>{"transcript":"Proyecto de comunidad energética solar en barrio, 20 viviendas participantes, gestoría incluida","quote":{"resumen":{"texto_original":"","tipo_presupuesto":"","requiere_revision_general":true,"alertas":["No se pudo interpretar el dictado"]},"oficios_detectados":[],"partidas":[],"calcu</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>283</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Impermeabilización</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Impermeabilizar sótano con humedades del terreno, sistema de drenaje interior y bomba de achique</v>
+      </c>
+      <c r="D13">
+        <v>200</v>
+      </c>
+      <c r="E13">
+        <v>20402</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H13" t="str">
+        <v>{"transcript":"Impermeabilizar sótano con humedades del terreno, sistema de drenaje interior y bomba de achique","quote":{"resumen":{"texto_original":"Impermeabilizar sótano con humedades del terreno, sistema de drenaje interior y bomba de achique","tipo_presupuesto":"reforma","requiere_revision_gen</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>309</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Contra Incendios</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Mantenimiento anual de sistema de detección y alarma contra incendios de hotel de 30 habitaciones</v>
+      </c>
+      <c r="D14">
+        <v>200</v>
+      </c>
+      <c r="E14">
+        <v>19213</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H14" t="str">
+        <v>{"transcript":"Mantenimiento anual de sistema de detección y alarma contra incendios de hotel de 30 habitaciones","quote":{"resumen":{"texto_original":"Mantenimiento anual de sistema de detección y alarma contra incendios de hotel de 30 habitaciones","tipo_presupuesto":"mantenimiento_recurrente","re</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>341</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Mantenimiento General</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Contrato de mantenimiento mensual de edificio de oficinas, electricidad, fontanería y carpintería</v>
+      </c>
+      <c r="D15">
+        <v>403</v>
+      </c>
+      <c r="E15">
+        <v>141</v>
+      </c>
+      <c r="F15" t="str">
+        <v>ERROR_TECNICO</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
+      </c>
+      <c r="H15" t="str">
+        <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
         <v>346</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B16" t="str">
         <v>Mantenimiento General</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C16" t="str">
         <v>Contrato anual de mantenimiento de comunidad de vecinos, incluye piscina, jardines y zonas comunes</v>
       </c>
-      <c r="D5">
+      <c r="D16">
         <v>403</v>
       </c>
-      <c r="E5">
-        <v>194</v>
-      </c>
-      <c r="F5" t="str">
+      <c r="E16">
+        <v>252</v>
+      </c>
+      <c r="F16" t="str">
         <v>ERROR_TECNICO</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G16" t="str">
         <v>Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H16" t="str">
         <v>{"error":"Tu plan actual no permite generar contratos de mantenimiento. Actualiza al Plan Empresa+ para acceder a este módulo.","plan_restriction":true,"required_plan":"empresa_plus","plan":"basico"}</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>349</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Mantenimiento General</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Cambiar cerradura de portal que está averiada y revisar timbre y portero automático</v>
+      </c>
+      <c r="D17">
+        <v>200</v>
+      </c>
+      <c r="E17">
+        <v>11405</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H17" t="str">
+        <v>{"transcript":"Cambiar cerradura de portal que está averiada y revisar timbre y portero automático","quote":{"resumen":{"texto_original":"Cambiar cerradura de portal que está averiada y revisar timbre y portero automático","tipo_presupuesto":"mantenimiento","requiere_revision_general":false,"alertas</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>366</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Reformas Integrales</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Reforma de ático dúplex de 100 metros cuadrados con escalera interior y terraza acristalada</v>
+      </c>
+      <c r="D18">
+        <v>200</v>
+      </c>
+      <c r="E18">
+        <v>34946</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PRECIO_INVALIDO</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Partida de catálogo con precio 0 o nulo</v>
+      </c>
+      <c r="H18" t="str">
+        <v>{"transcript":"Reforma de ático dúplex de 100 metros cuadrados con escalera interior y terraza acristalada","quote":{"resumen":{"texto_original":"Reforma de ático dúplex de 100 metros cuadrados con escalera interior y terraza acristalada","tipo_presupuesto":"reforma","requiere_revision_general":true</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
   </ignoredErrors>
 </worksheet>
 </file>